--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -160,15 +160,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4387,23 +4412,23 @@
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,5),"")</f>
         <v/>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,5),"")</f>
         <v/>
       </c>
-      <c r="D40" s="25">
+      <c r="D40" s="31">
         <f>IFERROR($B40/$C40,"")</f>
         <v/>
       </c>
-      <c r="E40" s="28">
+      <c r="E40" s="32">
         <f>IFERROR(TDIST(ABS($D40),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="33">
         <f>IF($B40="","","Predicted handle time for a contact with every driver at zero — before 17:00, under the limit, a brand-new agent, no transfers. Read it as the starting point the four effects are added to, not as a prediction.")</f>
         <v/>
       </c>
@@ -4414,27 +4439,27 @@
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,4),"")</f>
         <v/>
       </c>
-      <c r="C41" s="25">
+      <c r="C41" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,4),"")</f>
         <v/>
       </c>
-      <c r="D41" s="25">
+      <c r="D41" s="31">
         <f>IFERROR($B41/$C41,"")</f>
         <v/>
       </c>
-      <c r="E41" s="28">
+      <c r="E41" s="32">
         <f>IFERROR(TDIST(ABS($D41),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F41" s="25">
+      <c r="F41" s="31">
         <f>IFERROR(1/(1-INDEX(LINEST($B$11:$B$34,$J$11:$L$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="22">
+      <c r="G41" s="34">
         <f>IFERROR($B41*(MAX($B$11:$B$34)-MIN($B$11:$B$34)),"")</f>
         <v/>
       </c>
@@ -4442,7 +4467,7 @@
         <f>IF($E41="","",IF($E41&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G41)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="33">
         <f>IF($B41="","","Seconds the after-17:00 flag adds once the other three are held still. Compare it with the p-value beside it before you repeat it out loud.")</f>
         <v/>
       </c>
@@ -4453,27 +4478,27 @@
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B42" s="25">
+      <c r="B42" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,3),"")</f>
         <v/>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,3),"")</f>
         <v/>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="31">
         <f>IFERROR($B42/$C42,"")</f>
         <v/>
       </c>
-      <c r="E42" s="28">
+      <c r="E42" s="32">
         <f>IFERROR(TDIST(ABS($D42),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F42" s="25">
+      <c r="F42" s="31">
         <f>IFERROR(1/(1-INDEX(LINEST($C$11:$C$34,$M$11:$O$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="22">
+      <c r="G42" s="34">
         <f>IFERROR($B42*(MAX($C$11:$C$34)-MIN($C$11:$C$34)),"")</f>
         <v/>
       </c>
@@ -4481,7 +4506,7 @@
         <f>IF($E42="","",IF($E42&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G42)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I42" s="31">
+      <c r="I42" s="33">
         <f>IF($B42="","","Seconds the $50 authority limit adds once the other three are held still. This is the queue, not the money.")</f>
         <v/>
       </c>
@@ -4492,27 +4517,27 @@
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B43" s="25">
+      <c r="B43" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,2),"")</f>
         <v/>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,2),"")</f>
         <v/>
       </c>
-      <c r="D43" s="25">
+      <c r="D43" s="31">
         <f>IFERROR($B43/$C43,"")</f>
         <v/>
       </c>
-      <c r="E43" s="28">
+      <c r="E43" s="32">
         <f>IFERROR(TDIST(ABS($D43),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F43" s="25">
+      <c r="F43" s="31">
         <f>IFERROR(1/(1-INDEX(LINEST($D$11:$D$34,$P$11:$R$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="22">
+      <c r="G43" s="34">
         <f>IFERROR($B43*(MAX($D$11:$D$34)-MIN($D$11:$D$34)),"")</f>
         <v/>
       </c>
@@ -4520,7 +4545,7 @@
         <f>IF($E43="","",IF($E43&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G43)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I43" s="31">
+      <c r="I43" s="33">
         <f>IF($B43="","","Seconds per extra month of tenure — negative means longer-serving agents are quicker. Small per month, so read the range column, not this one.")</f>
         <v/>
       </c>
@@ -4531,27 +4556,27 @@
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B44" s="25">
+      <c r="B44" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,1),"")</f>
         <v/>
       </c>
-      <c r="C44" s="25">
+      <c r="C44" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,1),"")</f>
         <v/>
       </c>
-      <c r="D44" s="25">
+      <c r="D44" s="31">
         <f>IFERROR($B44/$C44,"")</f>
         <v/>
       </c>
-      <c r="E44" s="28">
+      <c r="E44" s="32">
         <f>IFERROR(TDIST(ABS($D44),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F44" s="25">
+      <c r="F44" s="31">
         <f>IFERROR(1/(1-INDEX(LINEST($E$11:$E$34,$S$11:$U$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="22">
+      <c r="G44" s="34">
         <f>IFERROR($B44*(MAX($E$11:$E$34)-MIN($E$11:$E$34)),"")</f>
         <v/>
       </c>
@@ -4559,7 +4584,7 @@
         <f>IF($E44="","",IF($E44&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G44)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="33">
         <f>IF($B44="","","Seconds each extra transfer adds once the other three are held still. Compare it with the 50.7 seconds the single-driver tab gave you.")</f>
         <v/>
       </c>
@@ -4977,30 +5002,30 @@
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B10" s="32" t="n">
+      <c r="B10" s="35" t="n">
         <v>-3.05</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="35" t="n">
         <v>0.24</v>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="37">
         <f>IFERROR(EXP($B10),"")</f>
         <v/>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="37">
         <f>IFERROR(EXP($B10-1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="G10" s="33">
+      <c r="G10" s="37">
         <f>IFERROR(EXP($B10+1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="H10" s="34">
+      <c r="H10" s="38">
         <f>"Baseline odds of a reopen with every driver at zero: "&amp;TEXT($E10,"0.000")&amp;" to 1, which is "&amp;TEXT($E10/(1+$E10),"0.0%")&amp;" probability."</f>
         <v/>
       </c>
@@ -5011,30 +5036,30 @@
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="39" t="n">
         <v>1.16</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="39" t="n">
         <v>0.21</v>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="41">
         <f>IFERROR(EXP($B11),"")</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="41">
         <f>IFERROR(EXP($B11-1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="41">
         <f>IFERROR(EXP($B11+1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="33">
         <f>"Raising the adjustment after 17:00 multiplies the odds of a reopen by "&amp;TEXT($E11,"0.00")&amp;". This is the posting-batch effect, and it is the largest single driver in the model."</f>
         <v/>
       </c>
@@ -5045,30 +5070,30 @@
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="39" t="n">
         <v>0.83</v>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="39" t="n">
         <v>0.22</v>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="D12" s="40" t="inlineStr">
         <is>
           <t>0.0002</t>
         </is>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="41">
         <f>IFERROR(EXP($B12),"")</f>
         <v/>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="41">
         <f>IFERROR(EXP($B12-1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="41">
         <f>IFERROR(EXP($B12+1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="33">
         <f>"Clearing the $50 authority limit multiplies the odds of a reopen by "&amp;TEXT($E12,"0.00")&amp;", because the case waits in a queue for approval."</f>
         <v/>
       </c>
@@ -5079,30 +5104,30 @@
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="39" t="n">
         <v>-0.038</v>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="39" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="40" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="41">
         <f>IFERROR(EXP($B13),"")</f>
         <v/>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="41">
         <f>IFERROR(EXP($B13-1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="41">
         <f>IFERROR(EXP($B13+1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="33">
         <f>"Each extra month of tenure multiplies the odds by "&amp;TEXT($E13,"0.000")&amp;" — so a 24-month agent runs at "&amp;TEXT($E13^24,"0.00")&amp;" times the odds of a first-week agent."</f>
         <v/>
       </c>
@@ -5113,30 +5138,30 @@
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="39" t="n">
         <v>0.61</v>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="39" t="n">
         <v>0.12</v>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="40" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="41">
         <f>IFERROR(EXP($B14),"")</f>
         <v/>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="41">
         <f>IFERROR(EXP($B14-1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="41">
         <f>IFERROR(EXP($B14+1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="33">
         <f>"Each extra transfer multiplies the odds of a reopen by "&amp;TEXT($E14,"0.00")&amp;". Multiply by how common transfers are before you rank it against the others."</f>
         <v/>
       </c>
@@ -5232,15 +5257,15 @@
       <c r="F19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="42">
         <f>IF($B19="","",$B$10+$B$11*$B19+$B$12*$C19+$B$13*$D19+$B$14*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="43">
         <f>IFERROR(1/(1+EXP(-$G19)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="44">
         <f>IF($H19="","",IF($H19&gt;=$B$45,1,0))</f>
         <v/>
       </c>
@@ -6055,7 +6080,7 @@
           <t>Flag a contact at this probability or above</t>
         </is>
       </c>
-      <c r="B45" s="38" t="n">
+      <c r="B45" s="45" t="n">
         <v>0.2</v>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -6070,7 +6095,7 @@
           <t>AUC the tool reported</t>
         </is>
       </c>
-      <c r="B46" s="39" t="n">
+      <c r="B46" s="46" t="n">
         <v>0.74</v>
       </c>
       <c r="C46" s="10" t="inlineStr">

--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -145,8 +145,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,6 +155,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -184,20 +183,14 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1367,26 +1360,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="21" t="n">
+      <c r="B12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="15" t="n">
         <v>506</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="20">
         <f>IF($C12="","",$B$41+$B$40*$B12)</f>
         <v/>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="20">
         <f>IF($D12="","",$C12-$D12)</f>
         <v/>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="21">
         <f>IF($E12="","",IF(ABS($E12)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1400,551 +1393,551 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="21" t="n">
+      <c r="B13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="15" t="n">
         <v>344</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="20">
         <f>IF($C13="","",$B$41+$B$40*$B13)</f>
         <v/>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="20">
         <f>IF($D13="","",$C13-$D13)</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="21">
         <f>IF($E13="","",IF(ABS($E13)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="15" t="n">
         <v>479</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="20">
         <f>IF($C14="","",$B$41+$B$40*$B14)</f>
         <v/>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="20">
         <f>IF($D14="","",$C14-$D14)</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="21">
         <f>IF($E14="","",IF(ABS($E14)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="15" t="n">
         <v>422</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="20">
         <f>IF($C15="","",$B$41+$B$40*$B15)</f>
         <v/>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="20">
         <f>IF($D15="","",$C15-$D15)</f>
         <v/>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="21">
         <f>IF($E15="","",IF(ABS($E15)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="15" t="n">
         <v>452</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <f>IF($C16="","",$B$41+$B$40*$B16)</f>
         <v/>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="20">
         <f>IF($D16="","",$C16-$D16)</f>
         <v/>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="21">
         <f>IF($E16="","",IF(ABS($E16)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="15" t="n">
         <v>374</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="20">
         <f>IF($C17="","",$B$41+$B$40*$B17)</f>
         <v/>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="20">
         <f>IF($D17="","",$C17-$D17)</f>
         <v/>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="21">
         <f>IF($E17="","",IF(ABS($E17)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="21" t="n">
+      <c r="B18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="15" t="n">
         <v>451</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="20">
         <f>IF($C18="","",$B$41+$B$40*$B18)</f>
         <v/>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="20">
         <f>IF($D18="","",$C18-$D18)</f>
         <v/>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="21">
         <f>IF($E18="","",IF(ABS($E18)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="21" t="n">
+      <c r="B19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="15" t="n">
         <v>360</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="20">
         <f>IF($C19="","",$B$41+$B$40*$B19)</f>
         <v/>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="20">
         <f>IF($D19="","",$C19-$D19)</f>
         <v/>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="21">
         <f>IF($E19="","",IF(ABS($E19)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="21" t="n">
+      <c r="B20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="15" t="n">
         <v>260</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="20">
         <f>IF($C20="","",$B$41+$B$40*$B20)</f>
         <v/>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="20">
         <f>IF($D20="","",$C20-$D20)</f>
         <v/>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="21">
         <f>IF($E20="","",IF(ABS($E20)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="21" t="n">
+      <c r="B21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="15" t="n">
         <v>415</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="20">
         <f>IF($C21="","",$B$41+$B$40*$B21)</f>
         <v/>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="20">
         <f>IF($D21="","",$C21-$D21)</f>
         <v/>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="21">
         <f>IF($E21="","",IF(ABS($E21)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B22" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="15" t="n">
         <v>555</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="20">
         <f>IF($C22="","",$B$41+$B$40*$B22)</f>
         <v/>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="20">
         <f>IF($D22="","",$C22-$D22)</f>
         <v/>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="21">
         <f>IF($E22="","",IF(ABS($E22)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="21" t="n">
+      <c r="B23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="15" t="n">
         <v>393</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="20">
         <f>IF($C23="","",$B$41+$B$40*$B23)</f>
         <v/>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="20">
         <f>IF($D23="","",$C23-$D23)</f>
         <v/>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="21">
         <f>IF($E23="","",IF(ABS($E23)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="21" t="n">
+      <c r="B24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="15" t="n">
         <v>454</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="20">
         <f>IF($C24="","",$B$41+$B$40*$B24)</f>
         <v/>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="20">
         <f>IF($D24="","",$C24-$D24)</f>
         <v/>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="21">
         <f>IF($E24="","",IF(ABS($E24)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="21" t="n">
+      <c r="B25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="15" t="n">
         <v>257</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="20">
         <f>IF($C25="","",$B$41+$B$40*$B25)</f>
         <v/>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="20">
         <f>IF($D25="","",$C25-$D25)</f>
         <v/>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="21">
         <f>IF($E25="","",IF(ABS($E25)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="21" t="n">
+      <c r="B26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="15" t="n">
         <v>544</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="20">
         <f>IF($C26="","",$B$41+$B$40*$B26)</f>
         <v/>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="20">
         <f>IF($D26="","",$C26-$D26)</f>
         <v/>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="21">
         <f>IF($E26="","",IF(ABS($E26)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="21" t="n">
+      <c r="B27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="15" t="n">
         <v>482</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="20">
         <f>IF($C27="","",$B$41+$B$40*$B27)</f>
         <v/>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="20">
         <f>IF($D27="","",$C27-$D27)</f>
         <v/>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="21">
         <f>IF($E27="","",IF(ABS($E27)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="21" t="n">
+      <c r="B28" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="15" t="n">
         <v>403</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="20">
         <f>IF($C28="","",$B$41+$B$40*$B28)</f>
         <v/>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="20">
         <f>IF($D28="","",$C28-$D28)</f>
         <v/>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="21">
         <f>IF($E28="","",IF(ABS($E28)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="15" t="n">
         <v>433</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="20">
         <f>IF($C29="","",$B$41+$B$40*$B29)</f>
         <v/>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="20">
         <f>IF($D29="","",$C29-$D29)</f>
         <v/>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="21">
         <f>IF($E29="","",IF(ABS($E29)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="21" t="n">
+      <c r="C30" s="15" t="n">
         <v>483</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="20">
         <f>IF($C30="","",$B$41+$B$40*$B30)</f>
         <v/>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="20">
         <f>IF($D30="","",$C30-$D30)</f>
         <v/>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="21">
         <f>IF($E30="","",IF(ABS($E30)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="21" t="n">
+      <c r="B31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="15" t="n">
         <v>261</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="20">
         <f>IF($C31="","",$B$41+$B$40*$B31)</f>
         <v/>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="20">
         <f>IF($D31="","",$C31-$D31)</f>
         <v/>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="21">
         <f>IF($E31="","",IF(ABS($E31)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="21" t="n">
+      <c r="B32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="15" t="n">
         <v>424</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="20">
         <f>IF($C32="","",$B$41+$B$40*$B32)</f>
         <v/>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="20">
         <f>IF($D32="","",$C32-$D32)</f>
         <v/>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="21">
         <f>IF($E32="","",IF(ABS($E32)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="21" t="n">
+      <c r="B33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="15" t="n">
         <v>359</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="20">
         <f>IF($C33="","",$B$41+$B$40*$B33)</f>
         <v/>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="20">
         <f>IF($D33="","",$C33-$D33)</f>
         <v/>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="21">
         <f>IF($E33="","",IF(ABS($E33)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="21" t="n">
+      <c r="B34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="15" t="n">
         <v>505</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="20">
         <f>IF($C34="","",$B$41+$B$40*$B34)</f>
         <v/>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="20">
         <f>IF($D34="","",$C34-$D34)</f>
         <v/>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="21">
         <f>IF($E34="","",IF(ABS($E34)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1995,7 +1988,7 @@
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="22">
         <f>COUNT($C$11:$C$34)</f>
         <v/>
       </c>
@@ -2011,7 +2004,7 @@
           <t>Slope — seconds per extra transfer</t>
         </is>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="23">
         <f>SLOPE($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2027,7 +2020,7 @@
           <t>Intercept — seconds at zero transfers</t>
         </is>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="23">
         <f>INTERCEPT($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2043,7 +2036,7 @@
           <t>R² — share of the spread the line explains</t>
         </is>
       </c>
-      <c r="B42" s="26">
+      <c r="B42" s="24">
         <f>RSQ($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2059,7 +2052,7 @@
           <t>Correlation r</t>
         </is>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="25">
         <f>CORREL($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2075,7 +2068,7 @@
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B44" s="25">
+      <c r="B44" s="23">
         <f>STEYX($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2091,7 +2084,7 @@
           <t>Standard error of the slope</t>
         </is>
       </c>
-      <c r="B45" s="25">
+      <c r="B45" s="23">
         <f>INDEX(LINEST($C$11:$C$34,$B$11:$B$34,TRUE,TRUE),2,1)</f>
         <v/>
       </c>
@@ -2107,7 +2100,7 @@
           <t>t-stat for the slope</t>
         </is>
       </c>
-      <c r="B46" s="25">
+      <c r="B46" s="23">
         <f>IFERROR($B$40/$B$45,"")</f>
         <v/>
       </c>
@@ -2123,7 +2116,7 @@
           <t>Degrees of freedom</t>
         </is>
       </c>
-      <c r="B47" s="24">
+      <c r="B47" s="22">
         <f>IFERROR(COUNT($C$11:$C$34)-2,"")</f>
         <v/>
       </c>
@@ -2139,7 +2132,7 @@
           <t>p-value for the slope</t>
         </is>
       </c>
-      <c r="B48" s="28">
+      <c r="B48" s="26">
         <f>IFERROR(TDIST(ABS($B$46),$B$47,2),"")</f>
         <v/>
       </c>
@@ -2163,13 +2156,13 @@
       <c r="F50" s="7" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="29">
+      <c r="A51" s="27">
         <f>"Handle time in seconds  =  "&amp;TEXT($B$41,"0.0")&amp;"  +  "&amp;TEXT($B$40,"0.0")&amp;" × transfers.      One more transfer is worth about "&amp;TEXT($B$40,"0")&amp;" seconds, and this one driver explains "&amp;TEXT($B$42,"0%")&amp;" of the spread in handle time "&amp;"(p = "&amp;TEXT($B$48,"0.000")&amp;", n = "&amp;TEXT($B$39,"0")&amp;")."</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="29">
+      <c r="A52" s="27">
         <f>IF($B$48="","",IF($B$48&gt;=0.05,"NOT PROVEN — at this sample size the slope is not distinguishable from a flat line. Collect more rows before you build anything on it.",IF($B$42&lt;0.3,"REAL BUT PARTIAL — the slope is significant (p = "&amp;TEXT($B$48,"0.000")&amp;") and the line still explains only "&amp;TEXT($B$42,"0%")&amp;" of the spread. Transfers are a genuine driver AND most of what moves handle time is not in this model.","REAL AND STRONG — significant, and the line explains "&amp;TEXT($B$42,"0%")&amp;" of the spread. Rare in support data; check the sample before you celebrate.")))</f>
         <v/>
       </c>
@@ -2357,7 +2350,7 @@
           <t>Smallest effect worth acting on (seconds)</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="28" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -2535,31 +2528,31 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="21" t="n">
+      <c r="B12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="E12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="21" t="n">
+      <c r="E12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="15" t="n">
         <v>506</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="20">
         <f>IF($F12="","",$B$40+$B$41*$B12+$B$42*$C12+$B$43*$D12+$B$44*$E12)</f>
         <v/>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="20">
         <f>IF($G12="","",$F12-$G12)</f>
         <v/>
       </c>
@@ -2620,31 +2613,31 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="21" t="n">
+      <c r="B13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E13" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="21" t="n">
+      <c r="E13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="15" t="n">
         <v>344</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="20">
         <f>IF($F13="","",$B$40+$B$41*$B13+$B$42*$C13+$B$43*$D13+$B$44*$E13)</f>
         <v/>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="20">
         <f>IF($G13="","",$F13-$G13)</f>
         <v/>
       </c>
@@ -2698,31 +2691,31 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="21" t="n">
+      <c r="B14" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="15" t="n">
         <v>479</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="20">
         <f>IF($F14="","",$B$40+$B$41*$B14+$B$42*$C14+$B$43*$D14+$B$44*$E14)</f>
         <v/>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="20">
         <f>IF($G14="","",$F14-$G14)</f>
         <v/>
       </c>
@@ -2776,31 +2769,31 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="21" t="n">
+      <c r="B15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="15" t="n">
         <v>422</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="20">
         <f>IF($F15="","",$B$40+$B$41*$B15+$B$42*$C15+$B$43*$D15+$B$44*$E15)</f>
         <v/>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="20">
         <f>IF($G15="","",$F15-$G15)</f>
         <v/>
       </c>
@@ -2854,31 +2847,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="21" t="n">
+      <c r="B16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="15" t="n">
         <v>452</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="20">
         <f>IF($F16="","",$B$40+$B$41*$B16+$B$42*$C16+$B$43*$D16+$B$44*$E16)</f>
         <v/>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="20">
         <f>IF($G16="","",$F16-$G16)</f>
         <v/>
       </c>
@@ -2932,31 +2925,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="21" t="n">
+      <c r="B17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E17" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="F17" s="15" t="n">
         <v>374</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="20">
         <f>IF($F17="","",$B$40+$B$41*$B17+$B$42*$C17+$B$43*$D17+$B$44*$E17)</f>
         <v/>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="20">
         <f>IF($G17="","",$F17-$G17)</f>
         <v/>
       </c>
@@ -3010,31 +3003,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="21" t="n">
+      <c r="B18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="21" t="n">
+      <c r="E18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="15" t="n">
         <v>451</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="20">
         <f>IF($F18="","",$B$40+$B$41*$B18+$B$42*$C18+$B$43*$D18+$B$44*$E18)</f>
         <v/>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="20">
         <f>IF($G18="","",$F18-$G18)</f>
         <v/>
       </c>
@@ -3088,31 +3081,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="21" t="n">
+      <c r="B19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="21" t="n">
+      <c r="E19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="15" t="n">
         <v>360</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="20">
         <f>IF($F19="","",$B$40+$B$41*$B19+$B$42*$C19+$B$43*$D19+$B$44*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="20">
         <f>IF($G19="","",$F19-$G19)</f>
         <v/>
       </c>
@@ -3166,31 +3159,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="21" t="n">
+      <c r="B20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="21" t="n">
+      <c r="E20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15" t="n">
         <v>260</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="20">
         <f>IF($F20="","",$B$40+$B$41*$B20+$B$42*$C20+$B$43*$D20+$B$44*$E20)</f>
         <v/>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="20">
         <f>IF($G20="","",$F20-$G20)</f>
         <v/>
       </c>
@@ -3244,31 +3237,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="21" t="n">
+      <c r="B21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="E21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="21" t="n">
+      <c r="E21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15" t="n">
         <v>415</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="20">
         <f>IF($F21="","",$B$40+$B$41*$B21+$B$42*$C21+$B$43*$D21+$B$44*$E21)</f>
         <v/>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="20">
         <f>IF($G21="","",$F21-$G21)</f>
         <v/>
       </c>
@@ -3322,31 +3315,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="21" t="n">
+      <c r="B22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="21" t="n">
+      <c r="F22" s="15" t="n">
         <v>555</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="20">
         <f>IF($F22="","",$B$40+$B$41*$B22+$B$42*$C22+$B$43*$D22+$B$44*$E22)</f>
         <v/>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="20">
         <f>IF($G22="","",$F22-$G22)</f>
         <v/>
       </c>
@@ -3400,31 +3393,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="21" t="n">
+      <c r="B23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="21" t="n">
+      <c r="E23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="15" t="n">
         <v>393</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="20">
         <f>IF($F23="","",$B$40+$B$41*$B23+$B$42*$C23+$B$43*$D23+$B$44*$E23)</f>
         <v/>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="20">
         <f>IF($G23="","",$F23-$G23)</f>
         <v/>
       </c>
@@ -3478,31 +3471,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="21" t="n">
+      <c r="B24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="21" t="n">
+      <c r="E24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15" t="n">
         <v>454</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="20">
         <f>IF($F24="","",$B$40+$B$41*$B24+$B$42*$C24+$B$43*$D24+$B$44*$E24)</f>
         <v/>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="20">
         <f>IF($G24="","",$F24-$G24)</f>
         <v/>
       </c>
@@ -3556,31 +3549,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="21" t="n">
+      <c r="B25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="E25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="21" t="n">
+      <c r="E25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15" t="n">
         <v>257</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="20">
         <f>IF($F25="","",$B$40+$B$41*$B25+$B$42*$C25+$B$43*$D25+$B$44*$E25)</f>
         <v/>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="20">
         <f>IF($G25="","",$F25-$G25)</f>
         <v/>
       </c>
@@ -3634,31 +3627,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="21" t="n">
+      <c r="B26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="E26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="21" t="n">
+      <c r="E26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="15" t="n">
         <v>544</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="20">
         <f>IF($F26="","",$B$40+$B$41*$B26+$B$42*$C26+$B$43*$D26+$B$44*$E26)</f>
         <v/>
       </c>
-      <c r="H26" s="22">
+      <c r="H26" s="20">
         <f>IF($G26="","",$F26-$G26)</f>
         <v/>
       </c>
@@ -3712,31 +3705,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="21" t="n">
+      <c r="B27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="21" t="n">
+      <c r="E27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="15" t="n">
         <v>482</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="20">
         <f>IF($F27="","",$B$40+$B$41*$B27+$B$42*$C27+$B$43*$D27+$B$44*$E27)</f>
         <v/>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="20">
         <f>IF($G27="","",$F27-$G27)</f>
         <v/>
       </c>
@@ -3790,31 +3783,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="21" t="n">
+      <c r="B28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="21" t="n">
+      <c r="E28" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="15" t="n">
         <v>403</v>
       </c>
-      <c r="G28" s="22">
+      <c r="G28" s="20">
         <f>IF($F28="","",$B$40+$B$41*$B28+$B$42*$C28+$B$43*$D28+$B$44*$E28)</f>
         <v/>
       </c>
-      <c r="H28" s="22">
+      <c r="H28" s="20">
         <f>IF($G28="","",$F28-$G28)</f>
         <v/>
       </c>
@@ -3868,31 +3861,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="21" t="n">
+      <c r="B29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="20" t="n">
+      <c r="E29" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="21" t="n">
+      <c r="F29" s="15" t="n">
         <v>433</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="20">
         <f>IF($F29="","",$B$40+$B$41*$B29+$B$42*$C29+$B$43*$D29+$B$44*$E29)</f>
         <v/>
       </c>
-      <c r="H29" s="22">
+      <c r="H29" s="20">
         <f>IF($G29="","",$F29-$G29)</f>
         <v/>
       </c>
@@ -3946,31 +3939,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="21" t="n">
+      <c r="B30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E30" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="21" t="n">
+      <c r="F30" s="15" t="n">
         <v>483</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="20">
         <f>IF($F30="","",$B$40+$B$41*$B30+$B$42*$C30+$B$43*$D30+$B$44*$E30)</f>
         <v/>
       </c>
-      <c r="H30" s="22">
+      <c r="H30" s="20">
         <f>IF($G30="","",$F30-$G30)</f>
         <v/>
       </c>
@@ -4024,31 +4017,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="21" t="n">
+      <c r="B31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="21" t="n">
+      <c r="E31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="15" t="n">
         <v>261</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="20">
         <f>IF($F31="","",$B$40+$B$41*$B31+$B$42*$C31+$B$43*$D31+$B$44*$E31)</f>
         <v/>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="20">
         <f>IF($G31="","",$F31-$G31)</f>
         <v/>
       </c>
@@ -4102,31 +4095,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="21" t="n">
+      <c r="B32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="15" t="n">
         <v>53</v>
       </c>
-      <c r="E32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="21" t="n">
+      <c r="E32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="15" t="n">
         <v>424</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="20">
         <f>IF($F32="","",$B$40+$B$41*$B32+$B$42*$C32+$B$43*$D32+$B$44*$E32)</f>
         <v/>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="20">
         <f>IF($G32="","",$F32-$G32)</f>
         <v/>
       </c>
@@ -4180,31 +4173,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="21" t="n">
+      <c r="B33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="E33" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="21" t="n">
+      <c r="E33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="15" t="n">
         <v>359</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="20">
         <f>IF($F33="","",$B$40+$B$41*$B33+$B$42*$C33+$B$43*$D33+$B$44*$E33)</f>
         <v/>
       </c>
-      <c r="H33" s="22">
+      <c r="H33" s="20">
         <f>IF($G33="","",$F33-$G33)</f>
         <v/>
       </c>
@@ -4258,31 +4251,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="21" t="n">
+      <c r="B34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="21" t="n">
+      <c r="E34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="15" t="n">
         <v>505</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="20">
         <f>IF($F34="","",$B$40+$B$41*$B34+$B$42*$C34+$B$43*$D34+$B$44*$E34)</f>
         <v/>
       </c>
-      <c r="H34" s="22">
+      <c r="H34" s="20">
         <f>IF($G34="","",$F34-$G34)</f>
         <v/>
       </c>
@@ -4407,184 +4400,184 @@
       </c>
     </row>
     <row r="40" ht="84" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,5),"")</f>
         <v/>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,5),"")</f>
         <v/>
       </c>
-      <c r="D40" s="31">
+      <c r="D40" s="30">
         <f>IFERROR($B40/$C40,"")</f>
         <v/>
       </c>
-      <c r="E40" s="32">
+      <c r="E40" s="31">
         <f>IFERROR(TDIST(ABS($D40),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="I40" s="33">
+      <c r="I40" s="32">
         <f>IF($B40="","","Predicted handle time for a contact with every driver at zero — before 17:00, under the limit, a brand-new agent, no transfers. Read it as the starting point the four effects are added to, not as a prediction.")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B41" s="31">
+      <c r="B41" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,4),"")</f>
         <v/>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,4),"")</f>
         <v/>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="30">
         <f>IFERROR($B41/$C41,"")</f>
         <v/>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="31">
         <f>IFERROR(TDIST(ABS($D41),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($B$11:$B$34,$J$11:$L$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="33">
         <f>IFERROR($B41*(MAX($B$11:$B$34)-MIN($B$11:$B$34)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="29">
+      <c r="H41" s="27">
         <f>IF($E41="","",IF($E41&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G41)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="32">
         <f>IF($B41="","","Seconds the after-17:00 flag adds once the other three are held still. Compare it with the p-value beside it before you repeat it out loud.")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="30" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,3),"")</f>
         <v/>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,3),"")</f>
         <v/>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="30">
         <f>IFERROR($B42/$C42,"")</f>
         <v/>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="31">
         <f>IFERROR(TDIST(ABS($D42),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($C$11:$C$34,$M$11:$O$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="33">
         <f>IFERROR($B42*(MAX($C$11:$C$34)-MIN($C$11:$C$34)),"")</f>
         <v/>
       </c>
-      <c r="H42" s="29">
+      <c r="H42" s="27">
         <f>IF($E42="","",IF($E42&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G42)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="32">
         <f>IF($B42="","","Seconds the $50 authority limit adds once the other three are held still. This is the queue, not the money.")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="30" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B43" s="31">
+      <c r="B43" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,2),"")</f>
         <v/>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,2),"")</f>
         <v/>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="30">
         <f>IFERROR($B43/$C43,"")</f>
         <v/>
       </c>
-      <c r="E43" s="32">
+      <c r="E43" s="31">
         <f>IFERROR(TDIST(ABS($D43),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F43" s="31">
+      <c r="F43" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($D$11:$D$34,$P$11:$R$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="33">
         <f>IFERROR($B43*(MAX($D$11:$D$34)-MIN($D$11:$D$34)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="29">
+      <c r="H43" s="27">
         <f>IF($E43="","",IF($E43&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G43)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I43" s="33">
+      <c r="I43" s="32">
         <f>IF($B43="","","Seconds per extra month of tenure — negative means longer-serving agents are quicker. Small per month, so read the range column, not this one.")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="30" t="inlineStr">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B44" s="31">
+      <c r="B44" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,1),"")</f>
         <v/>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,1),"")</f>
         <v/>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="30">
         <f>IFERROR($B44/$C44,"")</f>
         <v/>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="31">
         <f>IFERROR(TDIST(ABS($D44),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($E$11:$E$34,$S$11:$U$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="33">
         <f>IFERROR($B44*(MAX($E$11:$E$34)-MIN($E$11:$E$34)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="29">
+      <c r="H44" s="27">
         <f>IF($E44="","",IF($E44&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G44)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I44" s="33">
+      <c r="I44" s="32">
         <f>IF($B44="","","Seconds each extra transfer adds once the other three are held still. Compare it with the 50.7 seconds the single-driver tab gave you.")</f>
         <v/>
       </c>
@@ -4641,7 +4634,7 @@
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B49" s="24">
+      <c r="B49" s="22">
         <f>COUNT($F$11:$F$34)</f>
         <v/>
       </c>
@@ -4657,7 +4650,7 @@
           <t>Predictors (k)</t>
         </is>
       </c>
-      <c r="B50" s="24">
+      <c r="B50" s="22">
         <f>4</f>
         <v/>
       </c>
@@ -4673,7 +4666,7 @@
           <t>R²</t>
         </is>
       </c>
-      <c r="B51" s="26">
+      <c r="B51" s="24">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,1),"")</f>
         <v/>
       </c>
@@ -4689,7 +4682,7 @@
           <t>Adjusted R²</t>
         </is>
       </c>
-      <c r="B52" s="26">
+      <c r="B52" s="24">
         <f>IFERROR(1-(1-$B$51)*($B$49-1)/($B$49-$B$50-1),"")</f>
         <v/>
       </c>
@@ -4705,7 +4698,7 @@
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B53" s="25">
+      <c r="B53" s="23">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,2),"")</f>
         <v/>
       </c>
@@ -4721,7 +4714,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="B54" s="25">
+      <c r="B54" s="23">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,1),"")</f>
         <v/>
       </c>
@@ -4737,7 +4730,7 @@
           <t>Degrees of freedom (residual)</t>
         </is>
       </c>
-      <c r="B55" s="24">
+      <c r="B55" s="22">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,2),"")</f>
         <v/>
       </c>
@@ -4753,7 +4746,7 @@
           <t>p-value for F</t>
         </is>
       </c>
-      <c r="B56" s="28">
+      <c r="B56" s="26">
         <f>IFERROR(FDIST($B$54,$B$50,$B$55),"")</f>
         <v/>
       </c>
@@ -4769,7 +4762,7 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B57" s="23">
+      <c r="B57" s="21">
         <f>IF($B$56="","",IF($B$56&gt;=0.05,"NO MODEL — these four together explain nothing",IF($B$52&lt;0.3,"USABLE BUT WEAK — read the effect sizes, not the R²","USABLE — now go and look at the residual chart")))</f>
         <v/>
       </c>
@@ -4997,171 +4990,171 @@
       <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="34" t="n">
         <v>-3.05</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="34" t="n">
         <v>0.24</v>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="36">
         <f>IFERROR(EXP($B10),"")</f>
         <v/>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="36">
         <f>IFERROR(EXP($B10-1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="36">
         <f>IFERROR(EXP($B10+1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="37">
         <f>"Baseline odds of a reopen with every driver at zero: "&amp;TEXT($E10,"0.000")&amp;" to 1, which is "&amp;TEXT($E10/(1+$E10),"0.0%")&amp;" probability."</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B11" s="39" t="n">
+      <c r="B11" s="34" t="n">
         <v>1.16</v>
       </c>
-      <c r="C11" s="39" t="n">
+      <c r="C11" s="34" t="n">
         <v>0.21</v>
       </c>
-      <c r="D11" s="40" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="38">
         <f>IFERROR(EXP($B11),"")</f>
         <v/>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="38">
         <f>IFERROR(EXP($B11-1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="38">
         <f>IFERROR(EXP($B11+1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="32">
         <f>"Raising the adjustment after 17:00 multiplies the odds of a reopen by "&amp;TEXT($E11,"0.00")&amp;". This is the posting-batch effect, and it is the largest single driver in the model."</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B12" s="39" t="n">
+      <c r="B12" s="34" t="n">
         <v>0.83</v>
       </c>
-      <c r="C12" s="39" t="n">
+      <c r="C12" s="34" t="n">
         <v>0.22</v>
       </c>
-      <c r="D12" s="40" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>0.0002</t>
         </is>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="38">
         <f>IFERROR(EXP($B12),"")</f>
         <v/>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="38">
         <f>IFERROR(EXP($B12-1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="38">
         <f>IFERROR(EXP($B12+1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="32">
         <f>"Clearing the $50 authority limit multiplies the odds of a reopen by "&amp;TEXT($E12,"0.00")&amp;", because the case waits in a queue for approval."</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="84" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B13" s="39" t="n">
+      <c r="B13" s="34" t="n">
         <v>-0.038</v>
       </c>
-      <c r="C13" s="39" t="n">
+      <c r="C13" s="34" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="D13" s="40" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="38">
         <f>IFERROR(EXP($B13),"")</f>
         <v/>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="38">
         <f>IFERROR(EXP($B13-1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="38">
         <f>IFERROR(EXP($B13+1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="32">
         <f>"Each extra month of tenure multiplies the odds by "&amp;TEXT($E13,"0.000")&amp;" — so a 24-month agent runs at "&amp;TEXT($E13^24,"0.00")&amp;" times the odds of a first-week agent."</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B14" s="39" t="n">
+      <c r="B14" s="34" t="n">
         <v>0.61</v>
       </c>
-      <c r="C14" s="39" t="n">
+      <c r="C14" s="34" t="n">
         <v>0.12</v>
       </c>
-      <c r="D14" s="40" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="38">
         <f>IFERROR(EXP($B14),"")</f>
         <v/>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="38">
         <f>IFERROR(EXP($B14-1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="38">
         <f>IFERROR(EXP($B14+1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="32">
         <f>"Each extra transfer multiplies the odds of a reopen by "&amp;TEXT($E14,"0.00")&amp;". Multiply by how common transfers are before you rank it against the others."</f>
         <v/>
       </c>
@@ -5257,797 +5250,797 @@
       <c r="F19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="42">
+      <c r="G19" s="39">
         <f>IF($B19="","",$B$10+$B$11*$B19+$B$12*$C19+$B$13*$D19+$B$14*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="43">
+      <c r="H19" s="40">
         <f>IFERROR(1/(1+EXP(-$G19)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="41">
         <f>IF($H19="","",IF($H19&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="21" t="n">
+      <c r="B20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="E20" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="27">
+      <c r="E20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="25">
         <f>IF($B20="","",$B$10+$B$11*$B20+$B$12*$C20+$B$13*$D20+$B$14*$E20)</f>
         <v/>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="24">
         <f>IFERROR(1/(1+EXP(-$G20)),"")</f>
         <v/>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="22">
         <f>IF($H20="","",IF($H20&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="21" t="n">
+      <c r="B21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E21" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="27">
+      <c r="E21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="25">
         <f>IF($B21="","",$B$10+$B$11*$B21+$B$12*$C21+$B$13*$D21+$B$14*$E21)</f>
         <v/>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="24">
         <f>IFERROR(1/(1+EXP(-$G21)),"")</f>
         <v/>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="22">
         <f>IF($H21="","",IF($H21&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="21" t="n">
+      <c r="B22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="27">
+      <c r="F22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="25">
         <f>IF($B22="","",$B$10+$B$11*$B22+$B$12*$C22+$B$13*$D22+$B$14*$E22)</f>
         <v/>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="24">
         <f>IFERROR(1/(1+EXP(-$G22)),"")</f>
         <v/>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="22">
         <f>IF($H22="","",IF($H22&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="21" t="n">
+      <c r="B23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="27">
+      <c r="F23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="25">
         <f>IF($B23="","",$B$10+$B$11*$B23+$B$12*$C23+$B$13*$D23+$B$14*$E23)</f>
         <v/>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="24">
         <f>IFERROR(1/(1+EXP(-$G23)),"")</f>
         <v/>
       </c>
-      <c r="I23" s="24">
+      <c r="I23" s="22">
         <f>IF($H23="","",IF($H23&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="21" t="n">
+      <c r="B24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E24" s="20" t="n">
+      <c r="E24" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="27">
+      <c r="F24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="25">
         <f>IF($B24="","",$B$10+$B$11*$B24+$B$12*$C24+$B$13*$D24+$B$14*$E24)</f>
         <v/>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="24">
         <f>IFERROR(1/(1+EXP(-$G24)),"")</f>
         <v/>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="22">
         <f>IF($H24="","",IF($H24&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="21" t="n">
+      <c r="B25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="E25" s="20" t="n">
+      <c r="E25" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="27">
+      <c r="F25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="25">
         <f>IF($B25="","",$B$10+$B$11*$B25+$B$12*$C25+$B$13*$D25+$B$14*$E25)</f>
         <v/>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="24">
         <f>IFERROR(1/(1+EXP(-$G25)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="24">
+      <c r="I25" s="22">
         <f>IF($H25="","",IF($H25&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="21" t="n">
+      <c r="B26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="27">
+      <c r="E26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="25">
         <f>IF($B26="","",$B$10+$B$11*$B26+$B$12*$C26+$B$13*$D26+$B$14*$E26)</f>
         <v/>
       </c>
-      <c r="H26" s="26">
+      <c r="H26" s="24">
         <f>IFERROR(1/(1+EXP(-$G26)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="24">
+      <c r="I26" s="22">
         <f>IF($H26="","",IF($H26&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="21" t="n">
+      <c r="B27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="27">
+      <c r="E27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="25">
         <f>IF($B27="","",$B$10+$B$11*$B27+$B$12*$C27+$B$13*$D27+$B$14*$E27)</f>
         <v/>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="24">
         <f>IFERROR(1/(1+EXP(-$G27)),"")</f>
         <v/>
       </c>
-      <c r="I27" s="24">
+      <c r="I27" s="22">
         <f>IF($H27="","",IF($H27&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="21" t="n">
+      <c r="B28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="E28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="27">
+      <c r="E28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="25">
         <f>IF($B28="","",$B$10+$B$11*$B28+$B$12*$C28+$B$13*$D28+$B$14*$E28)</f>
         <v/>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="24">
         <f>IFERROR(1/(1+EXP(-$G28)),"")</f>
         <v/>
       </c>
-      <c r="I28" s="24">
+      <c r="I28" s="22">
         <f>IF($H28="","",IF($H28&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="21" t="n">
+      <c r="B29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="E29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="27">
+      <c r="E29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="25">
         <f>IF($B29="","",$B$10+$B$11*$B29+$B$12*$C29+$B$13*$D29+$B$14*$E29)</f>
         <v/>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="24">
         <f>IFERROR(1/(1+EXP(-$G29)),"")</f>
         <v/>
       </c>
-      <c r="I29" s="24">
+      <c r="I29" s="22">
         <f>IF($H29="","",IF($H29&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="21" t="n">
+      <c r="B30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E30" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="27">
+      <c r="F30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="25">
         <f>IF($B30="","",$B$10+$B$11*$B30+$B$12*$C30+$B$13*$D30+$B$14*$E30)</f>
         <v/>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="24">
         <f>IFERROR(1/(1+EXP(-$G30)),"")</f>
         <v/>
       </c>
-      <c r="I30" s="24">
+      <c r="I30" s="22">
         <f>IF($H30="","",IF($H30&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="21" t="n">
+      <c r="B31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="27">
+      <c r="E31" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="25">
         <f>IF($B31="","",$B$10+$B$11*$B31+$B$12*$C31+$B$13*$D31+$B$14*$E31)</f>
         <v/>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="24">
         <f>IFERROR(1/(1+EXP(-$G31)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="24">
+      <c r="I31" s="22">
         <f>IF($H31="","",IF($H31&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="21" t="n">
+      <c r="B32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="27">
+      <c r="E32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="25">
         <f>IF($B32="","",$B$10+$B$11*$B32+$B$12*$C32+$B$13*$D32+$B$14*$E32)</f>
         <v/>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="24">
         <f>IFERROR(1/(1+EXP(-$G32)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="24">
+      <c r="I32" s="22">
         <f>IF($H32="","",IF($H32&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="21" t="n">
+      <c r="B33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="E33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="27">
+      <c r="E33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="25">
         <f>IF($B33="","",$B$10+$B$11*$B33+$B$12*$C33+$B$13*$D33+$B$14*$E33)</f>
         <v/>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="24">
         <f>IFERROR(1/(1+EXP(-$G33)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="24">
+      <c r="I33" s="22">
         <f>IF($H33="","",IF($H33&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="21" t="n">
+      <c r="B34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="E34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="27">
+      <c r="E34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="25">
         <f>IF($B34="","",$B$10+$B$11*$B34+$B$12*$C34+$B$13*$D34+$B$14*$E34)</f>
         <v/>
       </c>
-      <c r="H34" s="26">
+      <c r="H34" s="24">
         <f>IFERROR(1/(1+EXP(-$G34)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="24">
+      <c r="I34" s="22">
         <f>IF($H34="","",IF($H34&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="21" t="n">
+      <c r="B35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E35" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="27">
+      <c r="E35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="25">
         <f>IF($B35="","",$B$10+$B$11*$B35+$B$12*$C35+$B$13*$D35+$B$14*$E35)</f>
         <v/>
       </c>
-      <c r="H35" s="26">
+      <c r="H35" s="24">
         <f>IFERROR(1/(1+EXP(-$G35)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="24">
+      <c r="I35" s="22">
         <f>IF($H35="","",IF($H35&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="21" t="n">
+      <c r="B36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="27">
+      <c r="E36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="25">
         <f>IF($B36="","",$B$10+$B$11*$B36+$B$12*$C36+$B$13*$D36+$B$14*$E36)</f>
         <v/>
       </c>
-      <c r="H36" s="26">
+      <c r="H36" s="24">
         <f>IFERROR(1/(1+EXP(-$G36)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="24">
+      <c r="I36" s="22">
         <f>IF($H36="","",IF($H36&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="21" t="n">
+      <c r="B37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="20" t="n">
+      <c r="E37" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="27">
+      <c r="F37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="25">
         <f>IF($B37="","",$B$10+$B$11*$B37+$B$12*$C37+$B$13*$D37+$B$14*$E37)</f>
         <v/>
       </c>
-      <c r="H37" s="26">
+      <c r="H37" s="24">
         <f>IFERROR(1/(1+EXP(-$G37)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="24">
+      <c r="I37" s="22">
         <f>IF($H37="","",IF($H37&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="21" t="n">
+      <c r="B38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E38" s="20" t="n">
+      <c r="E38" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="27">
+      <c r="F38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="25">
         <f>IF($B38="","",$B$10+$B$11*$B38+$B$12*$C38+$B$13*$D38+$B$14*$E38)</f>
         <v/>
       </c>
-      <c r="H38" s="26">
+      <c r="H38" s="24">
         <f>IFERROR(1/(1+EXP(-$G38)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="24">
+      <c r="I38" s="22">
         <f>IF($H38="","",IF($H38&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="21" t="n">
+      <c r="B39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="27">
+      <c r="E39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="25">
         <f>IF($B39="","",$B$10+$B$11*$B39+$B$12*$C39+$B$13*$D39+$B$14*$E39)</f>
         <v/>
       </c>
-      <c r="H39" s="26">
+      <c r="H39" s="24">
         <f>IFERROR(1/(1+EXP(-$G39)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="24">
+      <c r="I39" s="22">
         <f>IF($H39="","",IF($H39&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="21" t="n">
+      <c r="B40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="15" t="n">
         <v>53</v>
       </c>
-      <c r="E40" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="27">
+      <c r="E40" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="25">
         <f>IF($B40="","",$B$10+$B$11*$B40+$B$12*$C40+$B$13*$D40+$B$14*$E40)</f>
         <v/>
       </c>
-      <c r="H40" s="26">
+      <c r="H40" s="24">
         <f>IFERROR(1/(1+EXP(-$G40)),"")</f>
         <v/>
       </c>
-      <c r="I40" s="24">
+      <c r="I40" s="22">
         <f>IF($H40="","",IF($H40&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="21" t="n">
+      <c r="B41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="E41" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="27">
+      <c r="E41" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25">
         <f>IF($B41="","",$B$10+$B$11*$B41+$B$12*$C41+$B$13*$D41+$B$14*$E41)</f>
         <v/>
       </c>
-      <c r="H41" s="26">
+      <c r="H41" s="24">
         <f>IFERROR(1/(1+EXP(-$G41)),"")</f>
         <v/>
       </c>
-      <c r="I41" s="24">
+      <c r="I41" s="22">
         <f>IF($H41="","",IF($H41&gt;=$B$45,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="21" t="n">
+      <c r="B42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="27">
+      <c r="E42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="25">
         <f>IF($B42="","",$B$10+$B$11*$B42+$B$12*$C42+$B$13*$D42+$B$14*$E42)</f>
         <v/>
       </c>
-      <c r="H42" s="26">
+      <c r="H42" s="24">
         <f>IFERROR(1/(1+EXP(-$G42)),"")</f>
         <v/>
       </c>
-      <c r="I42" s="24">
+      <c r="I42" s="22">
         <f>IF($H42="","",IF($H42&gt;=$B$45,1,0))</f>
         <v/>
       </c>
@@ -6080,7 +6073,7 @@
           <t>Flag a contact at this probability or above</t>
         </is>
       </c>
-      <c r="B45" s="45" t="n">
+      <c r="B45" s="42" t="n">
         <v>0.2</v>
       </c>
       <c r="C45" s="10" t="inlineStr">
@@ -6095,7 +6088,7 @@
           <t>AUC the tool reported</t>
         </is>
       </c>
-      <c r="B46" s="46" t="n">
+      <c r="B46" s="43" t="n">
         <v>0.74</v>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -6153,15 +6146,15 @@
           <t>Flagged — predicted reopen</t>
         </is>
       </c>
-      <c r="B50" s="22">
+      <c r="B50" s="20">
         <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=1))</f>
         <v/>
       </c>
-      <c r="C50" s="22">
+      <c r="C50" s="20">
         <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=0))</f>
         <v/>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="20">
         <f>SUM($B50:$C50)</f>
         <v/>
       </c>
@@ -6172,15 +6165,15 @@
           <t>Not flagged</t>
         </is>
       </c>
-      <c r="B51" s="22">
+      <c r="B51" s="20">
         <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=1))</f>
         <v/>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="20">
         <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=0))</f>
         <v/>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="20">
         <f>SUM($B51:$C51)</f>
         <v/>
       </c>
@@ -6191,15 +6184,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B52" s="22">
+      <c r="B52" s="20">
         <f>SUM($B$50:$B$51)</f>
         <v/>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="20">
         <f>SUM($C$50:$C$51)</f>
         <v/>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="20">
         <f>SUM($D$50:$D$51)</f>
         <v/>
       </c>
@@ -6256,7 +6249,7 @@
           <t>Sensitivity — reopens you caught</t>
         </is>
       </c>
-      <c r="B57" s="26">
+      <c r="B57" s="24">
         <f>IFERROR($B$50/($B$50+$B$51),"")</f>
         <v/>
       </c>
@@ -6272,7 +6265,7 @@
           <t>Specificity — quiet contacts left alone</t>
         </is>
       </c>
-      <c r="B58" s="26">
+      <c r="B58" s="24">
         <f>IFERROR($C$51/($C$51+$C$50),"")</f>
         <v/>
       </c>
@@ -6288,7 +6281,7 @@
           <t>Precision — flags that were right</t>
         </is>
       </c>
-      <c r="B59" s="26">
+      <c r="B59" s="24">
         <f>IFERROR($B$50/($B$50+$C$50),"")</f>
         <v/>
       </c>
@@ -6304,7 +6297,7 @@
           <t>Accuracy — rows called correctly</t>
         </is>
       </c>
-      <c r="B60" s="26">
+      <c r="B60" s="24">
         <f>IFERROR(($B$50+$C$51)/($B$50+$C$50+$B$51+$C$51),"")</f>
         <v/>
       </c>
@@ -6320,7 +6313,7 @@
           <t>Base rate — share that actually reopened</t>
         </is>
       </c>
-      <c r="B61" s="26">
+      <c r="B61" s="24">
         <f>IFERROR(($B$50+$B$51)/($B$50+$C$50+$B$51+$C$51),"")</f>
         <v/>
       </c>
@@ -6336,7 +6329,7 @@
           <t>Verdict at this threshold</t>
         </is>
       </c>
-      <c r="B62" s="23">
+      <c r="B62" s="21">
         <f>IF($B$50+$B$51=0,"NO REOPENS IN THE SAMPLE",IF($B$50/($B$50+$B$51)&lt;0.5,"MISSES MORE THAN HALF — lower the threshold",IF($B$50/($B$50+$C$50)&lt;0.2,"TOO MANY FALSE ALARMS — raise the threshold","USABLE FOR TARGETING — check it against the cost of a flag")))</f>
         <v/>
       </c>

--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -189,8 +189,8 @@
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -643,12 +643,12 @@
     <author>Template</author>
   </authors>
   <commentList>
-    <comment ref="B45" authorId="0" shapeId="0">
+    <comment ref="B46" authorId="0" shapeId="0">
       <text>
         <t>Not 0.5. Roughly one billing adjustment in seven reopens, so at 0.5 the model flags nobody and still beats the base rate by predicting 'no' every time. Set the threshold from what a flag COSTS you: a quality check on a flagged contact takes about four minutes, so you can afford to be wrong often.</t>
       </text>
     </comment>
-    <comment ref="B46" authorId="0" shapeId="0">
+    <comment ref="B47" authorId="0" shapeId="0">
       <text>
         <t>Straight off the tool's output — Minitab calls it the concordance or the area under the ROC curve. It is threshold-free: 0.5 is a coin toss, 0.7 is useful for targeting, 0.8 is strong for support data. It says nothing about whether the probabilities themselves are calibrated.</t>
       </text>
@@ -4864,7 +4864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -5259,7 +5259,7 @@
         <v/>
       </c>
       <c r="I19" s="41">
-        <f>IF($H19="","",IF($H19&gt;=$B$45,1,0))</f>
+        <f>IF($H19="","",IF($H19&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5293,7 +5293,7 @@
         <v/>
       </c>
       <c r="I20" s="22">
-        <f>IF($H20="","",IF($H20&gt;=$B$45,1,0))</f>
+        <f>IF($H20="","",IF($H20&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5327,7 +5327,7 @@
         <v/>
       </c>
       <c r="I21" s="22">
-        <f>IF($H21="","",IF($H21&gt;=$B$45,1,0))</f>
+        <f>IF($H21="","",IF($H21&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="I22" s="22">
-        <f>IF($H22="","",IF($H22&gt;=$B$45,1,0))</f>
+        <f>IF($H22="","",IF($H22&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5395,7 +5395,7 @@
         <v/>
       </c>
       <c r="I23" s="22">
-        <f>IF($H23="","",IF($H23&gt;=$B$45,1,0))</f>
+        <f>IF($H23="","",IF($H23&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
         <v/>
       </c>
       <c r="I24" s="22">
-        <f>IF($H24="","",IF($H24&gt;=$B$45,1,0))</f>
+        <f>IF($H24="","",IF($H24&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5463,7 +5463,7 @@
         <v/>
       </c>
       <c r="I25" s="22">
-        <f>IF($H25="","",IF($H25&gt;=$B$45,1,0))</f>
+        <f>IF($H25="","",IF($H25&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5497,7 +5497,7 @@
         <v/>
       </c>
       <c r="I26" s="22">
-        <f>IF($H26="","",IF($H26&gt;=$B$45,1,0))</f>
+        <f>IF($H26="","",IF($H26&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
         <v/>
       </c>
       <c r="I27" s="22">
-        <f>IF($H27="","",IF($H27&gt;=$B$45,1,0))</f>
+        <f>IF($H27="","",IF($H27&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
         <v/>
       </c>
       <c r="I28" s="22">
-        <f>IF($H28="","",IF($H28&gt;=$B$45,1,0))</f>
+        <f>IF($H28="","",IF($H28&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
         <v/>
       </c>
       <c r="I29" s="22">
-        <f>IF($H29="","",IF($H29&gt;=$B$45,1,0))</f>
+        <f>IF($H29="","",IF($H29&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
         <v/>
       </c>
       <c r="I30" s="22">
-        <f>IF($H30="","",IF($H30&gt;=$B$45,1,0))</f>
+        <f>IF($H30="","",IF($H30&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
         <v/>
       </c>
       <c r="I31" s="22">
-        <f>IF($H31="","",IF($H31&gt;=$B$45,1,0))</f>
+        <f>IF($H31="","",IF($H31&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
         <v/>
       </c>
       <c r="I32" s="22">
-        <f>IF($H32="","",IF($H32&gt;=$B$45,1,0))</f>
+        <f>IF($H32="","",IF($H32&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
         <v/>
       </c>
       <c r="I33" s="22">
-        <f>IF($H33="","",IF($H33&gt;=$B$45,1,0))</f>
+        <f>IF($H33="","",IF($H33&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
         <v/>
       </c>
       <c r="I34" s="22">
-        <f>IF($H34="","",IF($H34&gt;=$B$45,1,0))</f>
+        <f>IF($H34="","",IF($H34&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5803,7 +5803,7 @@
         <v/>
       </c>
       <c r="I35" s="22">
-        <f>IF($H35="","",IF($H35&gt;=$B$45,1,0))</f>
+        <f>IF($H35="","",IF($H35&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
         <v/>
       </c>
       <c r="I36" s="22">
-        <f>IF($H36="","",IF($H36&gt;=$B$45,1,0))</f>
+        <f>IF($H36="","",IF($H36&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5871,7 +5871,7 @@
         <v/>
       </c>
       <c r="I37" s="22">
-        <f>IF($H37="","",IF($H37&gt;=$B$45,1,0))</f>
+        <f>IF($H37="","",IF($H37&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
         <v/>
       </c>
       <c r="I38" s="22">
-        <f>IF($H38="","",IF($H38&gt;=$B$45,1,0))</f>
+        <f>IF($H38="","",IF($H38&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
         <v/>
       </c>
       <c r="I39" s="22">
-        <f>IF($H39="","",IF($H39&gt;=$B$45,1,0))</f>
+        <f>IF($H39="","",IF($H39&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
         <v/>
       </c>
       <c r="I40" s="22">
-        <f>IF($H40="","",IF($H40&gt;=$B$45,1,0))</f>
+        <f>IF($H40="","",IF($H40&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
         <v/>
       </c>
       <c r="I41" s="22">
-        <f>IF($H41="","",IF($H41&gt;=$B$45,1,0))</f>
+        <f>IF($H41="","",IF($H41&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
@@ -6041,136 +6041,118 @@
         <v/>
       </c>
       <c r="I42" s="22">
-        <f>IF($H42="","",IF($H42&gt;=$B$45,1,0))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="45" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+        <f>IF($H42="","",IF($H42&gt;=$B$46,1,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="45" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>The logit is the straight-line part — intercept plus each coefficient times its column. The probability is that logit squashed into 0-1 by 1/(1+EXP(−logit)), which is the whole reason this is not a linear regression: a line would happily predict a 130% chance of reopening.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>STEP 3 — the threshold you choose, and what it costs you</t>
         </is>
       </c>
-      <c r="B44" s="7" t="n"/>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="n"/>
-      <c r="G44" s="7" t="n"/>
-      <c r="H44" s="7" t="n"/>
-      <c r="I44" s="7" t="n"/>
-    </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="n"/>
+      <c r="I45" s="7" t="n"/>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>Flag a contact at this probability or above</t>
         </is>
       </c>
-      <c r="B45" s="42" t="n">
+      <c r="B46" s="42" t="n">
         <v>0.2</v>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>Not 0.5. Roughly one billing adjustment in seven reopens, so at 0.5 the model flags nobody and still beats the base rate by predicting 'no' every time. Set the threshold from what a flag COSTS you: a quality check on a flagged contact takes about four minutes, so you can afford to be wrong often.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="45" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="47" ht="45" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>AUC the tool reported</t>
         </is>
       </c>
-      <c r="B46" s="43" t="n">
+      <c r="B47" s="43" t="n">
         <v>0.74</v>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C47" s="10" t="inlineStr">
         <is>
           <t>Straight off the tool's output — Minitab calls it the concordance or the area under the ROC curve. It is threshold-free: 0.5 is a coin toss, 0.7 is useful for targeting, 0.8 is strong for support data. It says nothing about whether the probabilities themselves are calibrated.</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>STEP 4 — the classification table at that threshold</t>
         </is>
       </c>
-      <c r="B48" s="7" t="n"/>
-      <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
-      <c r="E48" s="7" t="n"/>
-      <c r="F48" s="7" t="n"/>
-      <c r="G48" s="7" t="n"/>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="7" t="n"/>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="7" t="n"/>
+      <c r="I49" s="7" t="n"/>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>What the model said</t>
         </is>
       </c>
-      <c r="B49" s="12" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>Actually reopened</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>Did not reopen</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr"/>
-      <c r="F49" s="12" t="inlineStr"/>
-      <c r="G49" s="12" t="inlineStr"/>
-      <c r="H49" s="12" t="inlineStr"/>
-      <c r="I49" s="12" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Flagged — predicted reopen</t>
-        </is>
-      </c>
-      <c r="B50" s="20">
-        <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=1))</f>
-        <v/>
-      </c>
-      <c r="C50" s="20">
-        <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=0))</f>
-        <v/>
-      </c>
-      <c r="D50" s="20">
-        <f>SUM($B50:$C50)</f>
-        <v/>
-      </c>
+      <c r="E50" s="12" t="inlineStr"/>
+      <c r="F50" s="12" t="inlineStr"/>
+      <c r="G50" s="12" t="inlineStr"/>
+      <c r="H50" s="12" t="inlineStr"/>
+      <c r="I50" s="12" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Not flagged</t>
+          <t>Flagged — predicted reopen</t>
         </is>
       </c>
       <c r="B51" s="20">
-        <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=1))</f>
+        <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=1))</f>
         <v/>
       </c>
       <c r="C51" s="20">
-        <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=0))</f>
+        <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=0))</f>
         <v/>
       </c>
       <c r="D51" s="20">
@@ -6181,203 +6163,222 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
+          <t>Not flagged</t>
+        </is>
+      </c>
+      <c r="B52" s="20">
+        <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=1))</f>
+        <v/>
+      </c>
+      <c r="C52" s="20">
+        <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=0))</f>
+        <v/>
+      </c>
+      <c r="D52" s="20">
+        <f>SUM($B52:$C52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B52" s="20">
-        <f>SUM($B$50:$B$51)</f>
-        <v/>
-      </c>
-      <c r="C52" s="20">
-        <f>SUM($C$50:$C$51)</f>
-        <v/>
-      </c>
-      <c r="D52" s="20">
-        <f>SUM($D$50:$D$51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
+      <c r="B53" s="20">
+        <f>SUM($B$51:$B$52)</f>
+        <v/>
+      </c>
+      <c r="C53" s="20">
+        <f>SUM($C$51:$C$52)</f>
+        <v/>
+      </c>
+      <c r="D53" s="20">
+        <f>SUM($D$51:$D$52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="45" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Top left is a contact you flagged that did reopen; top right is a false alarm; bottom left is the one you missed. There is no threshold that empties both off-diagonal cells, and choosing which of them to fill is a business decision, not a statistical one.</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>STEP 5 — what that table says about the model</t>
         </is>
       </c>
-      <c r="B55" s="7" t="n"/>
-      <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="n"/>
-      <c r="G55" s="7" t="n"/>
-      <c r="H55" s="7" t="n"/>
-      <c r="I55" s="7" t="n"/>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="7" t="n"/>
+      <c r="I56" s="7" t="n"/>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B57" s="12" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C56" s="12" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>What it tells you</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr"/>
-      <c r="E56" s="12" t="inlineStr"/>
-      <c r="F56" s="12" t="inlineStr"/>
-      <c r="G56" s="12" t="inlineStr"/>
-      <c r="H56" s="12" t="inlineStr"/>
-      <c r="I56" s="12" t="inlineStr"/>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Sensitivity — reopens you caught</t>
-        </is>
-      </c>
-      <c r="B57" s="24">
-        <f>IFERROR($B$50/($B$50+$B$51),"")</f>
-        <v/>
-      </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>Of the contacts that did reopen, the share the model flagged. This is the number the improvement is actually paid on: a reopen you never flagged is a reopen you never prevented.</t>
-        </is>
-      </c>
+      <c r="D57" s="12" t="inlineStr"/>
+      <c r="E57" s="12" t="inlineStr"/>
+      <c r="F57" s="12" t="inlineStr"/>
+      <c r="G57" s="12" t="inlineStr"/>
+      <c r="H57" s="12" t="inlineStr"/>
+      <c r="I57" s="12" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>Specificity — quiet contacts left alone</t>
+          <t>Sensitivity — reopens you caught</t>
         </is>
       </c>
       <c r="B58" s="24">
-        <f>IFERROR($C$51/($C$51+$C$50),"")</f>
+        <f>IFERROR($B$51/($B$51+$B$52),"")</f>
         <v/>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Of the contacts that did not reopen, the share the model correctly left alone. Falls as you lower the threshold; that is the trade.</t>
+          <t>Of the contacts that did reopen, the share the model flagged. This is the number the improvement is actually paid on: a reopen you never flagged is a reopen you never prevented.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
+          <t>Specificity — quiet contacts left alone</t>
+        </is>
+      </c>
+      <c r="B59" s="24">
+        <f>IFERROR($C$52/($C$52+$C$51),"")</f>
+        <v/>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>Of the contacts that did not reopen, the share the model correctly left alone. Falls as you lower the threshold; that is the trade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
           <t>Precision — flags that were right</t>
         </is>
       </c>
-      <c r="B59" s="24">
-        <f>IFERROR($B$50/($B$50+$C$50),"")</f>
-        <v/>
-      </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="B60" s="24">
+        <f>IFERROR($B$51/($B$51+$C$51),"")</f>
+        <v/>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
         <is>
           <t>Of the contacts you flagged, the share that really reopened. At a 14% base rate this is always the ugly number, and it is the one that decides whether the team trusts the flag.</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="45" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>Accuracy — rows called correctly</t>
         </is>
       </c>
-      <c r="B60" s="24">
-        <f>IFERROR(($B$50+$C$51)/($B$50+$C$50+$B$51+$C$51),"")</f>
-        <v/>
-      </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="B61" s="24">
+        <f>IFERROR(($B$51+$C$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
         <is>
           <t>The share of all rows called right. Almost useless on its own: predicting 'never reopens' for every row scores whatever the base rate below leaves it, and prevents nothing. Quote it only beside that base rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>Base rate — share that actually reopened</t>
-        </is>
-      </c>
-      <c r="B61" s="24">
-        <f>IFERROR(($B$50+$B$51)/($B$50+$C$50+$B$51+$C$51),"")</f>
-        <v/>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>What you would score by always guessing 'no'. Accuracy has to beat this by a wide margin before it means anything at all.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="8" t="inlineStr">
         <is>
+          <t>Base rate — share that actually reopened</t>
+        </is>
+      </c>
+      <c r="B62" s="24">
+        <f>IFERROR(($B$51+$B$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
+        <v/>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>What you would score by always guessing 'no'. Accuracy has to beat this by a wide margin before it means anything at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
           <t>Verdict at this threshold</t>
         </is>
       </c>
-      <c r="B62" s="21">
-        <f>IF($B$50+$B$51=0,"NO REOPENS IN THE SAMPLE",IF($B$50/($B$50+$B$51)&lt;0.5,"MISSES MORE THAN HALF — lower the threshold",IF($B$50/($B$50+$C$50)&lt;0.2,"TOO MANY FALSE ALARMS — raise the threshold","USABLE FOR TARGETING — check it against the cost of a flag")))</f>
-        <v/>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="B63" s="21">
+        <f>IF($B$51+$B$52=0,"NO REOPENS IN THE SAMPLE",IF($B$51/($B$51+$B$52)&lt;0.5,"MISSES MORE THAN HALF — lower the threshold",IF($B$51/($B$51+$C$51)&lt;0.2,"TOO MANY FALSE ALARMS — raise the threshold","USABLE FOR TARGETING — check it against the cost of a flag")))</f>
+        <v/>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>Sensitivity is what the model buys you; precision is what it costs the team. Move the threshold in step 3 and watch both move.</t>
         </is>
       </c>
     </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>THE DECISION RULE — before this leaves the room</t>
         </is>
       </c>
-      <c r="B64" s="7" t="n"/>
-      <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
-      <c r="E64" s="7" t="n"/>
-      <c r="F64" s="7" t="n"/>
-      <c r="G64" s="7" t="n"/>
-      <c r="H64" s="7" t="n"/>
-      <c r="I64" s="7" t="n"/>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
+      <c r="B65" s="7" t="n"/>
+      <c r="C65" s="7" t="n"/>
+      <c r="D65" s="7" t="n"/>
+      <c r="E65" s="7" t="n"/>
+      <c r="F65" s="7" t="n"/>
+      <c r="G65" s="7" t="n"/>
+      <c r="H65" s="7" t="n"/>
+      <c r="I65" s="7" t="n"/>
+    </row>
+    <row r="66" ht="45" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
         <is>
           <t>Never fit a straight line to a yes/no outcome. Linear regression on a 0/1 column predicts probabilities above 1 and below 0, and gets the error structure wrong on top of it. If your outcome is reopened, escalated, breached or churned, it is this tab or nothing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>Report odds ratios with their confidence intervals, never raw log-odds. 'Each transfer multiplies the odds of a reopen by 1.84 (95% CI 1.46 to 2.33)' is a sentence the Improve phase can act on. '0.61' is not. And an interval that includes 1.00 means you have not shown anything, however confident the point estimate looks.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="60" customHeight="1">
       <c r="A67" s="10" t="inlineStr">
         <is>
+          <t>Report odds ratios with their confidence intervals, never raw log-odds. 'Each transfer multiplies the odds of a reopen by 1.84 (95% CI 1.46 to 2.33)' is a sentence the Improve phase can act on. '0.61' is not. And an interval that includes 1.00 means you have not shown anything, however confident the point estimate looks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
           <t>The biggest odds ratio is not the biggest opportunity. Multiply each odds ratio by how COMMON that driver is. After-17:00 has the largest ratio here and applies to 46% of contacts; a rare driver with an odds ratio of 5 that touches 2% of volume moves almost nothing. Rank by ratio times prevalence and you will usually reorder the list.</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="75" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
+    <row r="69" ht="75" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>AUC and accuracy are not the same question, and neither is causation. AUC asks whether the model RANKS reopens above non-reopens; accuracy asks how many rows it called right at one threshold; and neither says the drivers cause the reopens. Before you change the 17:00 cut-off, confirm the posting-batch mechanism at the gemba or pilot the change against a control group (16-pilot-protocol.md) — the model chose your suspect, the pilot convicts it.</t>
         </is>
@@ -6388,32 +6389,32 @@
     <mergeCell ref="C61:I61"/>
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A66:I66"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="A56:I56"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A8:I8"/>
     <mergeCell ref="C62:I62"/>
-    <mergeCell ref="A53:I53"/>
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="C58:I58"/>
-    <mergeCell ref="C45:I45"/>
-    <mergeCell ref="A43:I43"/>
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A44:I44"/>
     <mergeCell ref="A67:I67"/>
-    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="C47:I47"/>
+    <mergeCell ref="C63:I63"/>
     <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A49:I49"/>
     <mergeCell ref="C59:I59"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A45:I45"/>
     <mergeCell ref="C46:I46"/>
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="C60:I60"/>
+    <mergeCell ref="A69:I69"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
+    <dataValidation sqref="B46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>

--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -145,6 +145,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,7 +157,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -182,6 +183,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1360,26 +1367,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="15" t="n">
+      <c r="B12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="21" t="n">
         <v>506</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="22">
         <f>IF($C12="","",$B$41+$B$40*$B12)</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="22">
         <f>IF($D12="","",$C12-$D12)</f>
         <v/>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="23">
         <f>IF($E12="","",IF(ABS($E12)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1393,551 +1400,551 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="15" t="n">
+      <c r="B13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="21" t="n">
         <v>344</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="22">
         <f>IF($C13="","",$B$41+$B$40*$B13)</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="22">
         <f>IF($D13="","",$C13-$D13)</f>
         <v/>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="23">
         <f>IF($E13="","",IF(ABS($E13)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="21" t="n">
         <v>479</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="22">
         <f>IF($C14="","",$B$41+$B$40*$B14)</f>
         <v/>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="22">
         <f>IF($D14="","",$C14-$D14)</f>
         <v/>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="23">
         <f>IF($E14="","",IF(ABS($E14)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="21" t="n">
         <v>422</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="22">
         <f>IF($C15="","",$B$41+$B$40*$B15)</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="22">
         <f>IF($D15="","",$C15-$D15)</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="23">
         <f>IF($E15="","",IF(ABS($E15)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="21" t="n">
         <v>452</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="22">
         <f>IF($C16="","",$B$41+$B$40*$B16)</f>
         <v/>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="22">
         <f>IF($D16="","",$C16-$D16)</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="23">
         <f>IF($E16="","",IF(ABS($E16)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="21" t="n">
         <v>374</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="22">
         <f>IF($C17="","",$B$41+$B$40*$B17)</f>
         <v/>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="22">
         <f>IF($D17="","",$C17-$D17)</f>
         <v/>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="23">
         <f>IF($E17="","",IF(ABS($E17)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="15" t="n">
+      <c r="B18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="21" t="n">
         <v>451</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="22">
         <f>IF($C18="","",$B$41+$B$40*$B18)</f>
         <v/>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="22">
         <f>IF($D18="","",$C18-$D18)</f>
         <v/>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="23">
         <f>IF($E18="","",IF(ABS($E18)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="15" t="n">
+      <c r="B19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="21" t="n">
         <v>360</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="22">
         <f>IF($C19="","",$B$41+$B$40*$B19)</f>
         <v/>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="22">
         <f>IF($D19="","",$C19-$D19)</f>
         <v/>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="23">
         <f>IF($E19="","",IF(ABS($E19)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="15" t="n">
+      <c r="B20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="21" t="n">
         <v>260</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="22">
         <f>IF($C20="","",$B$41+$B$40*$B20)</f>
         <v/>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="22">
         <f>IF($D20="","",$C20-$D20)</f>
         <v/>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="23">
         <f>IF($E20="","",IF(ABS($E20)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="15" t="n">
+      <c r="B21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="21" t="n">
         <v>415</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="22">
         <f>IF($C21="","",$B$41+$B$40*$B21)</f>
         <v/>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="22">
         <f>IF($D21="","",$C21-$D21)</f>
         <v/>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="23">
         <f>IF($E21="","",IF(ABS($E21)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
+      <c r="B22" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="21" t="n">
         <v>555</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="22">
         <f>IF($C22="","",$B$41+$B$40*$B22)</f>
         <v/>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="22">
         <f>IF($D22="","",$C22-$D22)</f>
         <v/>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="23">
         <f>IF($E22="","",IF(ABS($E22)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="15" t="n">
+      <c r="B23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="21" t="n">
         <v>393</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="22">
         <f>IF($C23="","",$B$41+$B$40*$B23)</f>
         <v/>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="22">
         <f>IF($D23="","",$C23-$D23)</f>
         <v/>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="23">
         <f>IF($E23="","",IF(ABS($E23)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="15" t="n">
+      <c r="B24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="21" t="n">
         <v>454</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="22">
         <f>IF($C24="","",$B$41+$B$40*$B24)</f>
         <v/>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="22">
         <f>IF($D24="","",$C24-$D24)</f>
         <v/>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="23">
         <f>IF($E24="","",IF(ABS($E24)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="15" t="n">
+      <c r="B25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="21" t="n">
         <v>257</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="22">
         <f>IF($C25="","",$B$41+$B$40*$B25)</f>
         <v/>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="22">
         <f>IF($D25="","",$C25-$D25)</f>
         <v/>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="23">
         <f>IF($E25="","",IF(ABS($E25)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="15" t="n">
+      <c r="B26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="21" t="n">
         <v>544</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="22">
         <f>IF($C26="","",$B$41+$B$40*$B26)</f>
         <v/>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="22">
         <f>IF($D26="","",$C26-$D26)</f>
         <v/>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="23">
         <f>IF($E26="","",IF(ABS($E26)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="15" t="n">
+      <c r="B27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="21" t="n">
         <v>482</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="22">
         <f>IF($C27="","",$B$41+$B$40*$B27)</f>
         <v/>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="22">
         <f>IF($D27="","",$C27-$D27)</f>
         <v/>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="23">
         <f>IF($E27="","",IF(ABS($E27)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="15" t="n">
+      <c r="B28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="21" t="n">
         <v>403</v>
       </c>
-      <c r="D28" s="20">
+      <c r="D28" s="22">
         <f>IF($C28="","",$B$41+$B$40*$B28)</f>
         <v/>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="22">
         <f>IF($D28="","",$C28-$D28)</f>
         <v/>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="23">
         <f>IF($E28="","",IF(ABS($E28)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="21" t="n">
         <v>433</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="22">
         <f>IF($C29="","",$B$41+$B$40*$B29)</f>
         <v/>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="22">
         <f>IF($D29="","",$C29-$D29)</f>
         <v/>
       </c>
-      <c r="F29" s="21">
+      <c r="F29" s="23">
         <f>IF($E29="","",IF(ABS($E29)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="15" t="n">
+      <c r="C30" s="21" t="n">
         <v>483</v>
       </c>
-      <c r="D30" s="20">
+      <c r="D30" s="22">
         <f>IF($C30="","",$B$41+$B$40*$B30)</f>
         <v/>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="22">
         <f>IF($D30="","",$C30-$D30)</f>
         <v/>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="23">
         <f>IF($E30="","",IF(ABS($E30)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="15" t="n">
+      <c r="B31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="21" t="n">
         <v>261</v>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="22">
         <f>IF($C31="","",$B$41+$B$40*$B31)</f>
         <v/>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="22">
         <f>IF($D31="","",$C31-$D31)</f>
         <v/>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="23">
         <f>IF($E31="","",IF(ABS($E31)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="15" t="n">
+      <c r="B32" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="21" t="n">
         <v>424</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="22">
         <f>IF($C32="","",$B$41+$B$40*$B32)</f>
         <v/>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="22">
         <f>IF($D32="","",$C32-$D32)</f>
         <v/>
       </c>
-      <c r="F32" s="21">
+      <c r="F32" s="23">
         <f>IF($E32="","",IF(ABS($E32)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="15" t="n">
+      <c r="B33" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="21" t="n">
         <v>359</v>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="22">
         <f>IF($C33="","",$B$41+$B$40*$B33)</f>
         <v/>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="22">
         <f>IF($D33="","",$C33-$D33)</f>
         <v/>
       </c>
-      <c r="F33" s="21">
+      <c r="F33" s="23">
         <f>IF($E33="","",IF(ABS($E33)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="15" t="n">
+      <c r="B34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="21" t="n">
         <v>505</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="22">
         <f>IF($C34="","",$B$41+$B$40*$B34)</f>
         <v/>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="22">
         <f>IF($D34="","",$C34-$D34)</f>
         <v/>
       </c>
-      <c r="F34" s="21">
+      <c r="F34" s="23">
         <f>IF($E34="","",IF(ABS($E34)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1988,7 +1995,7 @@
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="24">
         <f>COUNT($C$11:$C$34)</f>
         <v/>
       </c>
@@ -2004,7 +2011,7 @@
           <t>Slope — seconds per extra transfer</t>
         </is>
       </c>
-      <c r="B40" s="23">
+      <c r="B40" s="25">
         <f>SLOPE($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2020,7 +2027,7 @@
           <t>Intercept — seconds at zero transfers</t>
         </is>
       </c>
-      <c r="B41" s="23">
+      <c r="B41" s="25">
         <f>INTERCEPT($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2036,7 +2043,7 @@
           <t>R² — share of the spread the line explains</t>
         </is>
       </c>
-      <c r="B42" s="24">
+      <c r="B42" s="26">
         <f>RSQ($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2052,7 +2059,7 @@
           <t>Correlation r</t>
         </is>
       </c>
-      <c r="B43" s="25">
+      <c r="B43" s="27">
         <f>CORREL($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2068,7 +2075,7 @@
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B44" s="23">
+      <c r="B44" s="25">
         <f>STEYX($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2084,7 +2091,7 @@
           <t>Standard error of the slope</t>
         </is>
       </c>
-      <c r="B45" s="23">
+      <c r="B45" s="25">
         <f>INDEX(LINEST($C$11:$C$34,$B$11:$B$34,TRUE,TRUE),2,1)</f>
         <v/>
       </c>
@@ -2100,7 +2107,7 @@
           <t>t-stat for the slope</t>
         </is>
       </c>
-      <c r="B46" s="23">
+      <c r="B46" s="25">
         <f>IFERROR($B$40/$B$45,"")</f>
         <v/>
       </c>
@@ -2116,7 +2123,7 @@
           <t>Degrees of freedom</t>
         </is>
       </c>
-      <c r="B47" s="22">
+      <c r="B47" s="24">
         <f>IFERROR(COUNT($C$11:$C$34)-2,"")</f>
         <v/>
       </c>
@@ -2132,7 +2139,7 @@
           <t>p-value for the slope</t>
         </is>
       </c>
-      <c r="B48" s="26">
+      <c r="B48" s="28">
         <f>IFERROR(TDIST(ABS($B$46),$B$47,2),"")</f>
         <v/>
       </c>
@@ -2156,13 +2163,13 @@
       <c r="F50" s="7" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="27">
+      <c r="A51" s="29">
         <f>"Handle time in seconds  =  "&amp;TEXT($B$41,"0.0")&amp;"  +  "&amp;TEXT($B$40,"0.0")&amp;" × transfers.      One more transfer is worth about "&amp;TEXT($B$40,"0")&amp;" seconds, and this one driver explains "&amp;TEXT($B$42,"0%")&amp;" of the spread in handle time "&amp;"(p = "&amp;TEXT($B$48,"0.000")&amp;", n = "&amp;TEXT($B$39,"0")&amp;")."</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="27">
+      <c r="A52" s="29">
         <f>IF($B$48="","",IF($B$48&gt;=0.05,"NOT PROVEN — at this sample size the slope is not distinguishable from a flat line. Collect more rows before you build anything on it.",IF($B$42&lt;0.3,"REAL BUT PARTIAL — the slope is significant (p = "&amp;TEXT($B$48,"0.000")&amp;") and the line still explains only "&amp;TEXT($B$42,"0%")&amp;" of the spread. Transfers are a genuine driver AND most of what moves handle time is not in this model.","REAL AND STRONG — significant, and the line explains "&amp;TEXT($B$42,"0%")&amp;" of the spread. Rare in support data; check the sample before you celebrate.")))</f>
         <v/>
       </c>
@@ -2350,7 +2357,7 @@
           <t>Smallest effect worth acting on (seconds)</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="21" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -2528,31 +2535,31 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="15" t="n">
+      <c r="B12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="E12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="15" t="n">
+      <c r="E12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="21" t="n">
         <v>506</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="22">
         <f>IF($F12="","",$B$40+$B$41*$B12+$B$42*$C12+$B$43*$D12+$B$44*$E12)</f>
         <v/>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="22">
         <f>IF($G12="","",$F12-$G12)</f>
         <v/>
       </c>
@@ -2613,31 +2620,31 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="15" t="n">
+      <c r="B13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="21" t="n">
         <v>39</v>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="15" t="n">
+      <c r="E13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="21" t="n">
         <v>344</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="22">
         <f>IF($F13="","",$B$40+$B$41*$B13+$B$42*$C13+$B$43*$D13+$B$44*$E13)</f>
         <v/>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="22">
         <f>IF($G13="","",$F13-$G13)</f>
         <v/>
       </c>
@@ -2691,31 +2698,31 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="15" t="n">
+      <c r="B14" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="21" t="n">
         <v>39</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F14" s="21" t="n">
         <v>479</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="22">
         <f>IF($F14="","",$B$40+$B$41*$B14+$B$42*$C14+$B$43*$D14+$B$44*$E14)</f>
         <v/>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="22">
         <f>IF($G14="","",$F14-$G14)</f>
         <v/>
       </c>
@@ -2769,31 +2776,31 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15" t="n">
+      <c r="B15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="21" t="n">
         <v>33</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F15" s="21" t="n">
         <v>422</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="22">
         <f>IF($F15="","",$B$40+$B$41*$B15+$B$42*$C15+$B$43*$D15+$B$44*$E15)</f>
         <v/>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="22">
         <f>IF($G15="","",$F15-$G15)</f>
         <v/>
       </c>
@@ -2847,31 +2854,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="15" t="n">
+      <c r="B16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F16" s="21" t="n">
         <v>452</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="22">
         <f>IF($F16="","",$B$40+$B$41*$B16+$B$42*$C16+$B$43*$D16+$B$44*$E16)</f>
         <v/>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="22">
         <f>IF($G16="","",$F16-$G16)</f>
         <v/>
       </c>
@@ -2925,31 +2932,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="15" t="n">
+      <c r="B17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="21" t="n">
         <v>374</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="22">
         <f>IF($F17="","",$B$40+$B$41*$B17+$B$42*$C17+$B$43*$D17+$B$44*$E17)</f>
         <v/>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="22">
         <f>IF($G17="","",$F17-$G17)</f>
         <v/>
       </c>
@@ -3003,31 +3010,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15" t="n">
+      <c r="B18" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="n">
+      <c r="E18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="21" t="n">
         <v>451</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="22">
         <f>IF($F18="","",$B$40+$B$41*$B18+$B$42*$C18+$B$43*$D18+$B$44*$E18)</f>
         <v/>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="22">
         <f>IF($G18="","",$F18-$G18)</f>
         <v/>
       </c>
@@ -3081,31 +3088,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="15" t="n">
+      <c r="B19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="15" t="n">
+      <c r="E19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="21" t="n">
         <v>360</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="22">
         <f>IF($F19="","",$B$40+$B$41*$B19+$B$42*$C19+$B$43*$D19+$B$44*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="22">
         <f>IF($G19="","",$F19-$G19)</f>
         <v/>
       </c>
@@ -3159,31 +3166,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="15" t="n">
+      <c r="B20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="15" t="n">
+      <c r="E20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="21" t="n">
         <v>260</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="22">
         <f>IF($F20="","",$B$40+$B$41*$B20+$B$42*$C20+$B$43*$D20+$B$44*$E20)</f>
         <v/>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="22">
         <f>IF($G20="","",$F20-$G20)</f>
         <v/>
       </c>
@@ -3237,31 +3244,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15" t="n">
+      <c r="B21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="21" t="n">
         <v>28</v>
       </c>
-      <c r="E21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="15" t="n">
+      <c r="E21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="21" t="n">
         <v>415</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="22">
         <f>IF($F21="","",$B$40+$B$41*$B21+$B$42*$C21+$B$43*$D21+$B$44*$E21)</f>
         <v/>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="22">
         <f>IF($G21="","",$F21-$G21)</f>
         <v/>
       </c>
@@ -3315,31 +3322,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15" t="n">
+      <c r="B22" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="15" t="n">
+      <c r="F22" s="21" t="n">
         <v>555</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="22">
         <f>IF($F22="","",$B$40+$B$41*$B22+$B$42*$C22+$B$43*$D22+$B$44*$E22)</f>
         <v/>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="22">
         <f>IF($G22="","",$F22-$G22)</f>
         <v/>
       </c>
@@ -3393,31 +3400,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="15" t="n">
+      <c r="B23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="15" t="n">
+      <c r="E23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="21" t="n">
         <v>393</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="22">
         <f>IF($F23="","",$B$40+$B$41*$B23+$B$42*$C23+$B$43*$D23+$B$44*$E23)</f>
         <v/>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="22">
         <f>IF($G23="","",$F23-$G23)</f>
         <v/>
       </c>
@@ -3471,31 +3478,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="15" t="n">
+      <c r="B24" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="21" t="n">
         <v>39</v>
       </c>
-      <c r="E24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="15" t="n">
+      <c r="E24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="21" t="n">
         <v>454</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="22">
         <f>IF($F24="","",$B$40+$B$41*$B24+$B$42*$C24+$B$43*$D24+$B$44*$E24)</f>
         <v/>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="22">
         <f>IF($G24="","",$F24-$G24)</f>
         <v/>
       </c>
@@ -3549,31 +3556,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="15" t="n">
+      <c r="B25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="E25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="15" t="n">
+      <c r="E25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="21" t="n">
         <v>257</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="22">
         <f>IF($F25="","",$B$40+$B$41*$B25+$B$42*$C25+$B$43*$D25+$B$44*$E25)</f>
         <v/>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="22">
         <f>IF($G25="","",$F25-$G25)</f>
         <v/>
       </c>
@@ -3627,31 +3634,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="15" t="n">
+      <c r="B26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="E26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="15" t="n">
+      <c r="E26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="21" t="n">
         <v>544</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="22">
         <f>IF($F26="","",$B$40+$B$41*$B26+$B$42*$C26+$B$43*$D26+$B$44*$E26)</f>
         <v/>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="22">
         <f>IF($G26="","",$F26-$G26)</f>
         <v/>
       </c>
@@ -3705,31 +3712,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15" t="n">
+      <c r="B27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="E27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="15" t="n">
+      <c r="E27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="21" t="n">
         <v>482</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="22">
         <f>IF($F27="","",$B$40+$B$41*$B27+$B$42*$C27+$B$43*$D27+$B$44*$E27)</f>
         <v/>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="22">
         <f>IF($G27="","",$F27-$G27)</f>
         <v/>
       </c>
@@ -3783,31 +3790,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="15" t="n">
+      <c r="B28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="15" t="n">
+      <c r="E28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="21" t="n">
         <v>403</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="22">
         <f>IF($F28="","",$B$40+$B$41*$B28+$B$42*$C28+$B$43*$D28+$B$44*$E28)</f>
         <v/>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="22">
         <f>IF($G28="","",$F28-$G28)</f>
         <v/>
       </c>
@@ -3861,31 +3868,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="15" t="n">
+      <c r="B29" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="15" t="n">
+      <c r="F29" s="21" t="n">
         <v>433</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="22">
         <f>IF($F29="","",$B$40+$B$41*$B29+$B$42*$C29+$B$43*$D29+$B$44*$E29)</f>
         <v/>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="22">
         <f>IF($G29="","",$F29-$G29)</f>
         <v/>
       </c>
@@ -3939,31 +3946,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="15" t="n">
+      <c r="B30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="15" t="n">
+      <c r="F30" s="21" t="n">
         <v>483</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="22">
         <f>IF($F30="","",$B$40+$B$41*$B30+$B$42*$C30+$B$43*$D30+$B$44*$E30)</f>
         <v/>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="22">
         <f>IF($G30="","",$F30-$G30)</f>
         <v/>
       </c>
@@ -4017,31 +4024,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="15" t="n">
+      <c r="B31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="E31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="15" t="n">
+      <c r="E31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="21" t="n">
         <v>261</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="22">
         <f>IF($F31="","",$B$40+$B$41*$B31+$B$42*$C31+$B$43*$D31+$B$44*$E31)</f>
         <v/>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="22">
         <f>IF($G31="","",$F31-$G31)</f>
         <v/>
       </c>
@@ -4095,31 +4102,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="15" t="n">
+      <c r="B32" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="21" t="n">
         <v>53</v>
       </c>
-      <c r="E32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="15" t="n">
+      <c r="E32" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="21" t="n">
         <v>424</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="22">
         <f>IF($F32="","",$B$40+$B$41*$B32+$B$42*$C32+$B$43*$D32+$B$44*$E32)</f>
         <v/>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="22">
         <f>IF($G32="","",$F32-$G32)</f>
         <v/>
       </c>
@@ -4173,31 +4180,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="15" t="n">
+      <c r="B33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="E33" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="15" t="n">
+      <c r="E33" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="21" t="n">
         <v>359</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="22">
         <f>IF($F33="","",$B$40+$B$41*$B33+$B$42*$C33+$B$43*$D33+$B$44*$E33)</f>
         <v/>
       </c>
-      <c r="H33" s="20">
+      <c r="H33" s="22">
         <f>IF($G33="","",$F33-$G33)</f>
         <v/>
       </c>
@@ -4251,31 +4258,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="15" t="n">
+      <c r="B34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="15" t="n">
+      <c r="E34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="21" t="n">
         <v>505</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="22">
         <f>IF($F34="","",$B$40+$B$41*$B34+$B$42*$C34+$B$43*$D34+$B$44*$E34)</f>
         <v/>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="22">
         <f>IF($G34="","",$F34-$G34)</f>
         <v/>
       </c>
@@ -4400,184 +4407,184 @@
       </c>
     </row>
     <row r="40" ht="84" customHeight="1">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,5),"")</f>
         <v/>
       </c>
-      <c r="C40" s="30">
+      <c r="C40" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,5),"")</f>
         <v/>
       </c>
-      <c r="D40" s="30">
+      <c r="D40" s="31">
         <f>IFERROR($B40/$C40,"")</f>
         <v/>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="32">
         <f>IFERROR(TDIST(ABS($D40),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="I40" s="32">
+      <c r="I40" s="33">
         <f>IF($B40="","","Predicted handle time for a contact with every driver at zero — before 17:00, under the limit, a brand-new agent, no transfers. Read it as the starting point the four effects are added to, not as a prediction.")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,4),"")</f>
         <v/>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,4),"")</f>
         <v/>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="31">
         <f>IFERROR($B41/$C41,"")</f>
         <v/>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <f>IFERROR(TDIST(ABS($D41),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="31">
         <f>IFERROR(1/(1-INDEX(LINEST($B$11:$B$34,$J$11:$L$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="34">
         <f>IFERROR($B41*(MAX($B$11:$B$34)-MIN($B$11:$B$34)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="27">
+      <c r="H41" s="29">
         <f>IF($E41="","",IF($E41&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G41)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="33">
         <f>IF($B41="","","Seconds the after-17:00 flag adds once the other three are held still. Compare it with the p-value beside it before you repeat it out loud.")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="A42" s="30" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,3),"")</f>
         <v/>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,3),"")</f>
         <v/>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="31">
         <f>IFERROR($B42/$C42,"")</f>
         <v/>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="32">
         <f>IFERROR(TDIST(ABS($D42),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="31">
         <f>IFERROR(1/(1-INDEX(LINEST($C$11:$C$34,$M$11:$O$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="34">
         <f>IFERROR($B42*(MAX($C$11:$C$34)-MIN($C$11:$C$34)),"")</f>
         <v/>
       </c>
-      <c r="H42" s="27">
+      <c r="H42" s="29">
         <f>IF($E42="","",IF($E42&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G42)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="33">
         <f>IF($B42="","","Seconds the $50 authority limit adds once the other three are held still. This is the queue, not the money.")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B43" s="30">
+      <c r="B43" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,2),"")</f>
         <v/>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,2),"")</f>
         <v/>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="31">
         <f>IFERROR($B43/$C43,"")</f>
         <v/>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="32">
         <f>IFERROR(TDIST(ABS($D43),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="31">
         <f>IFERROR(1/(1-INDEX(LINEST($D$11:$D$34,$P$11:$R$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="33">
+      <c r="G43" s="34">
         <f>IFERROR($B43*(MAX($D$11:$D$34)-MIN($D$11:$D$34)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="27">
+      <c r="H43" s="29">
         <f>IF($E43="","",IF($E43&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G43)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I43" s="32">
+      <c r="I43" s="33">
         <f>IF($B43="","","Seconds per extra month of tenure — negative means longer-serving agents are quicker. Small per month, so read the range column, not this one.")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B44" s="30">
+      <c r="B44" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,1),"")</f>
         <v/>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="31">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,1),"")</f>
         <v/>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="31">
         <f>IFERROR($B44/$C44,"")</f>
         <v/>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <f>IFERROR(TDIST(ABS($D44),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F44" s="30">
+      <c r="F44" s="31">
         <f>IFERROR(1/(1-INDEX(LINEST($E$11:$E$34,$S$11:$U$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="34">
         <f>IFERROR($B44*(MAX($E$11:$E$34)-MIN($E$11:$E$34)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="27">
+      <c r="H44" s="29">
         <f>IF($E44="","",IF($E44&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G44)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="33">
         <f>IF($B44="","","Seconds each extra transfer adds once the other three are held still. Compare it with the 50.7 seconds the single-driver tab gave you.")</f>
         <v/>
       </c>
@@ -4634,7 +4641,7 @@
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B49" s="22">
+      <c r="B49" s="24">
         <f>COUNT($F$11:$F$34)</f>
         <v/>
       </c>
@@ -4650,7 +4657,7 @@
           <t>Predictors (k)</t>
         </is>
       </c>
-      <c r="B50" s="22">
+      <c r="B50" s="24">
         <f>4</f>
         <v/>
       </c>
@@ -4666,7 +4673,7 @@
           <t>R²</t>
         </is>
       </c>
-      <c r="B51" s="24">
+      <c r="B51" s="26">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,1),"")</f>
         <v/>
       </c>
@@ -4682,7 +4689,7 @@
           <t>Adjusted R²</t>
         </is>
       </c>
-      <c r="B52" s="24">
+      <c r="B52" s="26">
         <f>IFERROR(1-(1-$B$51)*($B$49-1)/($B$49-$B$50-1),"")</f>
         <v/>
       </c>
@@ -4698,7 +4705,7 @@
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B53" s="23">
+      <c r="B53" s="25">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,2),"")</f>
         <v/>
       </c>
@@ -4714,7 +4721,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="B54" s="23">
+      <c r="B54" s="25">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,1),"")</f>
         <v/>
       </c>
@@ -4730,7 +4737,7 @@
           <t>Degrees of freedom (residual)</t>
         </is>
       </c>
-      <c r="B55" s="22">
+      <c r="B55" s="24">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,2),"")</f>
         <v/>
       </c>
@@ -4746,7 +4753,7 @@
           <t>p-value for F</t>
         </is>
       </c>
-      <c r="B56" s="26">
+      <c r="B56" s="28">
         <f>IFERROR(FDIST($B$54,$B$50,$B$55),"")</f>
         <v/>
       </c>
@@ -4762,7 +4769,7 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B57" s="21">
+      <c r="B57" s="23">
         <f>IF($B$56="","",IF($B$56&gt;=0.05,"NO MODEL — these four together explain nothing",IF($B$52&lt;0.3,"USABLE BUT WEAK — read the effect sizes, not the R²","USABLE — now go and look at the residual chart")))</f>
         <v/>
       </c>
@@ -4990,171 +4997,171 @@
       <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n">
+      <c r="B10" s="35" t="n">
         <v>-3.05</v>
       </c>
-      <c r="C10" s="34" t="n">
+      <c r="C10" s="35" t="n">
         <v>0.24</v>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="37">
         <f>IFERROR(EXP($B10),"")</f>
         <v/>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="37">
         <f>IFERROR(EXP($B10-1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="37">
         <f>IFERROR(EXP($B10+1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="H10" s="37">
+      <c r="H10" s="38">
         <f>"Baseline odds of a reopen with every driver at zero: "&amp;TEXT($E10,"0.000")&amp;" to 1, which is "&amp;TEXT($E10/(1+$E10),"0.0%")&amp;" probability."</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="39" t="n">
         <v>1.16</v>
       </c>
-      <c r="C11" s="34" t="n">
+      <c r="C11" s="39" t="n">
         <v>0.21</v>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="41">
         <f>IFERROR(EXP($B11),"")</f>
         <v/>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="41">
         <f>IFERROR(EXP($B11-1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="41">
         <f>IFERROR(EXP($B11+1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="33">
         <f>"Raising the adjustment after 17:00 multiplies the odds of a reopen by "&amp;TEXT($E11,"0.00")&amp;". This is the posting-batch effect, and it is the largest single driver in the model."</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B12" s="34" t="n">
+      <c r="B12" s="39" t="n">
         <v>0.83</v>
       </c>
-      <c r="C12" s="34" t="n">
+      <c r="C12" s="39" t="n">
         <v>0.22</v>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="40" t="inlineStr">
         <is>
           <t>0.0002</t>
         </is>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="41">
         <f>IFERROR(EXP($B12),"")</f>
         <v/>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="41">
         <f>IFERROR(EXP($B12-1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="G12" s="38">
+      <c r="G12" s="41">
         <f>IFERROR(EXP($B12+1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="33">
         <f>"Clearing the $50 authority limit multiplies the odds of a reopen by "&amp;TEXT($E12,"0.00")&amp;", because the case waits in a queue for approval."</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="84" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B13" s="34" t="n">
+      <c r="B13" s="39" t="n">
         <v>-0.038</v>
       </c>
-      <c r="C13" s="34" t="n">
+      <c r="C13" s="39" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" s="40" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="41">
         <f>IFERROR(EXP($B13),"")</f>
         <v/>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="41">
         <f>IFERROR(EXP($B13-1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="41">
         <f>IFERROR(EXP($B13+1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="33">
         <f>"Each extra month of tenure multiplies the odds by "&amp;TEXT($E13,"0.000")&amp;" — so a 24-month agent runs at "&amp;TEXT($E13^24,"0.00")&amp;" times the odds of a first-week agent."</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n">
+      <c r="B14" s="39" t="n">
         <v>0.61</v>
       </c>
-      <c r="C14" s="34" t="n">
+      <c r="C14" s="39" t="n">
         <v>0.12</v>
       </c>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="D14" s="40" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="41">
         <f>IFERROR(EXP($B14),"")</f>
         <v/>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="41">
         <f>IFERROR(EXP($B14-1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="41">
         <f>IFERROR(EXP($B14+1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="33">
         <f>"Each extra transfer multiplies the odds of a reopen by "&amp;TEXT($E14,"0.00")&amp;". Multiply by how common transfers are before you rank it against the others."</f>
         <v/>
       </c>
@@ -5250,797 +5257,797 @@
       <c r="F19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="39">
+      <c r="G19" s="42">
         <f>IF($B19="","",$B$10+$B$11*$B19+$B$12*$C19+$B$13*$D19+$B$14*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="43">
         <f>IFERROR(1/(1+EXP(-$G19)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="44">
         <f>IF($H19="","",IF($H19&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15" t="n">
+      <c r="B20" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="E20" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="25">
+      <c r="E20" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="27">
         <f>IF($B20="","",$B$10+$B$11*$B20+$B$12*$C20+$B$13*$D20+$B$14*$E20)</f>
         <v/>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="26">
         <f>IFERROR(1/(1+EXP(-$G20)),"")</f>
         <v/>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="24">
         <f>IF($H20="","",IF($H20&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15" t="n">
+      <c r="B21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="21" t="n">
         <v>39</v>
       </c>
-      <c r="E21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="25">
+      <c r="E21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="27">
         <f>IF($B21="","",$B$10+$B$11*$B21+$B$12*$C21+$B$13*$D21+$B$14*$E21)</f>
         <v/>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="26">
         <f>IFERROR(1/(1+EXP(-$G21)),"")</f>
         <v/>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="24">
         <f>IF($H21="","",IF($H21&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15" t="n">
+      <c r="B22" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="21" t="n">
         <v>39</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="25">
+      <c r="F22" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="27">
         <f>IF($B22="","",$B$10+$B$11*$B22+$B$12*$C22+$B$13*$D22+$B$14*$E22)</f>
         <v/>
       </c>
-      <c r="H22" s="24">
+      <c r="H22" s="26">
         <f>IFERROR(1/(1+EXP(-$G22)),"")</f>
         <v/>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="24">
         <f>IF($H22="","",IF($H22&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15" t="n">
+      <c r="B23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="21" t="n">
         <v>33</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="25">
+      <c r="F23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="27">
         <f>IF($B23="","",$B$10+$B$11*$B23+$B$12*$C23+$B$13*$D23+$B$14*$E23)</f>
         <v/>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="26">
         <f>IFERROR(1/(1+EXP(-$G23)),"")</f>
         <v/>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="24">
         <f>IF($H23="","",IF($H23&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="15" t="n">
+      <c r="B24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E24" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="25">
+      <c r="F24" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="27">
         <f>IF($B24="","",$B$10+$B$11*$B24+$B$12*$C24+$B$13*$D24+$B$14*$E24)</f>
         <v/>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="26">
         <f>IFERROR(1/(1+EXP(-$G24)),"")</f>
         <v/>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="24">
         <f>IF($H24="","",IF($H24&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="15" t="n">
+      <c r="B25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="25">
+      <c r="F25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="27">
         <f>IF($B25="","",$B$10+$B$11*$B25+$B$12*$C25+$B$13*$D25+$B$14*$E25)</f>
         <v/>
       </c>
-      <c r="H25" s="24">
+      <c r="H25" s="26">
         <f>IFERROR(1/(1+EXP(-$G25)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="24">
         <f>IF($H25="","",IF($H25&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="15" t="n">
+      <c r="B26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="25">
+      <c r="E26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="27">
         <f>IF($B26="","",$B$10+$B$11*$B26+$B$12*$C26+$B$13*$D26+$B$14*$E26)</f>
         <v/>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="26">
         <f>IFERROR(1/(1+EXP(-$G26)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="22">
+      <c r="I26" s="24">
         <f>IF($H26="","",IF($H26&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="15" t="n">
+      <c r="B27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="25">
+      <c r="E27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="27">
         <f>IF($B27="","",$B$10+$B$11*$B27+$B$12*$C27+$B$13*$D27+$B$14*$E27)</f>
         <v/>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="26">
         <f>IFERROR(1/(1+EXP(-$G27)),"")</f>
         <v/>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="24">
         <f>IF($H27="","",IF($H27&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="15" t="n">
+      <c r="B28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="E28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="25">
+      <c r="E28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="27">
         <f>IF($B28="","",$B$10+$B$11*$B28+$B$12*$C28+$B$13*$D28+$B$14*$E28)</f>
         <v/>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="26">
         <f>IFERROR(1/(1+EXP(-$G28)),"")</f>
         <v/>
       </c>
-      <c r="I28" s="22">
+      <c r="I28" s="24">
         <f>IF($H28="","",IF($H28&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="15" t="n">
+      <c r="B29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="21" t="n">
         <v>28</v>
       </c>
-      <c r="E29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="25">
+      <c r="E29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="27">
         <f>IF($B29="","",$B$10+$B$11*$B29+$B$12*$C29+$B$13*$D29+$B$14*$E29)</f>
         <v/>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="26">
         <f>IFERROR(1/(1+EXP(-$G29)),"")</f>
         <v/>
       </c>
-      <c r="I29" s="22">
+      <c r="I29" s="24">
         <f>IF($H29="","",IF($H29&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="15" t="n">
+      <c r="B30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="25">
+      <c r="F30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="27">
         <f>IF($B30="","",$B$10+$B$11*$B30+$B$12*$C30+$B$13*$D30+$B$14*$E30)</f>
         <v/>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="26">
         <f>IFERROR(1/(1+EXP(-$G30)),"")</f>
         <v/>
       </c>
-      <c r="I30" s="22">
+      <c r="I30" s="24">
         <f>IF($H30="","",IF($H30&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="15" t="n">
+      <c r="B31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="25">
+      <c r="E31" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="27">
         <f>IF($B31="","",$B$10+$B$11*$B31+$B$12*$C31+$B$13*$D31+$B$14*$E31)</f>
         <v/>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="26">
         <f>IFERROR(1/(1+EXP(-$G31)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="24">
         <f>IF($H31="","",IF($H31&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="15" t="n">
+      <c r="B32" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="21" t="n">
         <v>39</v>
       </c>
-      <c r="E32" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="25">
+      <c r="E32" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="27">
         <f>IF($B32="","",$B$10+$B$11*$B32+$B$12*$C32+$B$13*$D32+$B$14*$E32)</f>
         <v/>
       </c>
-      <c r="H32" s="24">
+      <c r="H32" s="26">
         <f>IFERROR(1/(1+EXP(-$G32)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="24">
         <f>IF($H32="","",IF($H32&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="15" t="n">
+      <c r="B33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="E33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="25">
+      <c r="E33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="27">
         <f>IF($B33="","",$B$10+$B$11*$B33+$B$12*$C33+$B$13*$D33+$B$14*$E33)</f>
         <v/>
       </c>
-      <c r="H33" s="24">
+      <c r="H33" s="26">
         <f>IFERROR(1/(1+EXP(-$G33)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="22">
+      <c r="I33" s="24">
         <f>IF($H33="","",IF($H33&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="15" t="n">
+      <c r="B34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="E34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="25">
+      <c r="E34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="27">
         <f>IF($B34="","",$B$10+$B$11*$B34+$B$12*$C34+$B$13*$D34+$B$14*$E34)</f>
         <v/>
       </c>
-      <c r="H34" s="24">
+      <c r="H34" s="26">
         <f>IFERROR(1/(1+EXP(-$G34)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="22">
+      <c r="I34" s="24">
         <f>IF($H34="","",IF($H34&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="15" t="n">
+      <c r="B35" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="E35" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="25">
+      <c r="E35" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="27">
         <f>IF($B35="","",$B$10+$B$11*$B35+$B$12*$C35+$B$13*$D35+$B$14*$E35)</f>
         <v/>
       </c>
-      <c r="H35" s="24">
+      <c r="H35" s="26">
         <f>IFERROR(1/(1+EXP(-$G35)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="22">
+      <c r="I35" s="24">
         <f>IF($H35="","",IF($H35&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="15" t="n">
+      <c r="B36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="25">
+      <c r="E36" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="27">
         <f>IF($B36="","",$B$10+$B$11*$B36+$B$12*$C36+$B$13*$D36+$B$14*$E36)</f>
         <v/>
       </c>
-      <c r="H36" s="24">
+      <c r="H36" s="26">
         <f>IFERROR(1/(1+EXP(-$G36)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="22">
+      <c r="I36" s="24">
         <f>IF($H36="","",IF($H36&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="15" t="n">
+      <c r="B37" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="14" t="n">
+      <c r="E37" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="25">
+      <c r="F37" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="27">
         <f>IF($B37="","",$B$10+$B$11*$B37+$B$12*$C37+$B$13*$D37+$B$14*$E37)</f>
         <v/>
       </c>
-      <c r="H37" s="24">
+      <c r="H37" s="26">
         <f>IFERROR(1/(1+EXP(-$G37)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="22">
+      <c r="I37" s="24">
         <f>IF($H37="","",IF($H37&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="15" t="n">
+      <c r="B38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="E38" s="14" t="n">
+      <c r="E38" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="25">
+      <c r="F38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="27">
         <f>IF($B38="","",$B$10+$B$11*$B38+$B$12*$C38+$B$13*$D38+$B$14*$E38)</f>
         <v/>
       </c>
-      <c r="H38" s="24">
+      <c r="H38" s="26">
         <f>IFERROR(1/(1+EXP(-$G38)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="22">
+      <c r="I38" s="24">
         <f>IF($H38="","",IF($H38&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="15" t="n">
+      <c r="B39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="25">
+      <c r="E39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="27">
         <f>IF($B39="","",$B$10+$B$11*$B39+$B$12*$C39+$B$13*$D39+$B$14*$E39)</f>
         <v/>
       </c>
-      <c r="H39" s="24">
+      <c r="H39" s="26">
         <f>IFERROR(1/(1+EXP(-$G39)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="22">
+      <c r="I39" s="24">
         <f>IF($H39="","",IF($H39&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="15" t="n">
+      <c r="B40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="21" t="n">
         <v>53</v>
       </c>
-      <c r="E40" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="25">
+      <c r="E40" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="27">
         <f>IF($B40="","",$B$10+$B$11*$B40+$B$12*$C40+$B$13*$D40+$B$14*$E40)</f>
         <v/>
       </c>
-      <c r="H40" s="24">
+      <c r="H40" s="26">
         <f>IFERROR(1/(1+EXP(-$G40)),"")</f>
         <v/>
       </c>
-      <c r="I40" s="22">
+      <c r="I40" s="24">
         <f>IF($H40="","",IF($H40&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="15" t="n">
+      <c r="B41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="21" t="n">
         <v>21</v>
       </c>
-      <c r="E41" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="25">
+      <c r="E41" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="27">
         <f>IF($B41="","",$B$10+$B$11*$B41+$B$12*$C41+$B$13*$D41+$B$14*$E41)</f>
         <v/>
       </c>
-      <c r="H41" s="24">
+      <c r="H41" s="26">
         <f>IFERROR(1/(1+EXP(-$G41)),"")</f>
         <v/>
       </c>
-      <c r="I41" s="22">
+      <c r="I41" s="24">
         <f>IF($H41="","",IF($H41&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="15" t="n">
+      <c r="B42" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="E42" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="25">
+      <c r="E42" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="27">
         <f>IF($B42="","",$B$10+$B$11*$B42+$B$12*$C42+$B$13*$D42+$B$14*$E42)</f>
         <v/>
       </c>
-      <c r="H42" s="24">
+      <c r="H42" s="26">
         <f>IFERROR(1/(1+EXP(-$G42)),"")</f>
         <v/>
       </c>
-      <c r="I42" s="22">
+      <c r="I42" s="24">
         <f>IF($H42="","",IF($H42&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -6074,7 +6081,7 @@
           <t>Flag a contact at this probability or above</t>
         </is>
       </c>
-      <c r="B46" s="42" t="n">
+      <c r="B46" s="45" t="n">
         <v>0.2</v>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -6089,7 +6096,7 @@
           <t>AUC the tool reported</t>
         </is>
       </c>
-      <c r="B47" s="43" t="n">
+      <c r="B47" s="46" t="n">
         <v>0.74</v>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -6147,15 +6154,15 @@
           <t>Flagged — predicted reopen</t>
         </is>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="22">
         <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=1))</f>
         <v/>
       </c>
-      <c r="C51" s="20">
+      <c r="C51" s="22">
         <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=0))</f>
         <v/>
       </c>
-      <c r="D51" s="20">
+      <c r="D51" s="22">
         <f>SUM($B51:$C51)</f>
         <v/>
       </c>
@@ -6166,15 +6173,15 @@
           <t>Not flagged</t>
         </is>
       </c>
-      <c r="B52" s="20">
+      <c r="B52" s="22">
         <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=1))</f>
         <v/>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="22">
         <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=0))</f>
         <v/>
       </c>
-      <c r="D52" s="20">
+      <c r="D52" s="22">
         <f>SUM($B52:$C52)</f>
         <v/>
       </c>
@@ -6185,15 +6192,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="22">
         <f>SUM($B$51:$B$52)</f>
         <v/>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="22">
         <f>SUM($C$51:$C$52)</f>
         <v/>
       </c>
-      <c r="D53" s="20">
+      <c r="D53" s="22">
         <f>SUM($D$51:$D$52)</f>
         <v/>
       </c>
@@ -6250,7 +6257,7 @@
           <t>Sensitivity — reopens you caught</t>
         </is>
       </c>
-      <c r="B58" s="24">
+      <c r="B58" s="26">
         <f>IFERROR($B$51/($B$51+$B$52),"")</f>
         <v/>
       </c>
@@ -6266,7 +6273,7 @@
           <t>Specificity — quiet contacts left alone</t>
         </is>
       </c>
-      <c r="B59" s="24">
+      <c r="B59" s="26">
         <f>IFERROR($C$52/($C$52+$C$51),"")</f>
         <v/>
       </c>
@@ -6282,7 +6289,7 @@
           <t>Precision — flags that were right</t>
         </is>
       </c>
-      <c r="B60" s="24">
+      <c r="B60" s="26">
         <f>IFERROR($B$51/($B$51+$C$51),"")</f>
         <v/>
       </c>
@@ -6298,7 +6305,7 @@
           <t>Accuracy — rows called correctly</t>
         </is>
       </c>
-      <c r="B61" s="24">
+      <c r="B61" s="26">
         <f>IFERROR(($B$51+$C$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
         <v/>
       </c>
@@ -6314,7 +6321,7 @@
           <t>Base rate — share that actually reopened</t>
         </is>
       </c>
-      <c r="B62" s="24">
+      <c r="B62" s="26">
         <f>IFERROR(($B$51+$B$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
         <v/>
       </c>
@@ -6330,7 +6337,7 @@
           <t>Verdict at this threshold</t>
         </is>
       </c>
-      <c r="B63" s="21">
+      <c r="B63" s="23">
         <f>IF($B$51+$B$52=0,"NO REOPENS IN THE SAMPLE",IF($B$51/($B$51+$B$52)&lt;0.5,"MISSES MORE THAN HALF — lower the threshold",IF($B$51/($B$51+$C$51)&lt;0.2,"TOO MANY FALSE ALARMS — raise the threshold","USABLE FOR TARGETING — check it against the cost of a flag")))</f>
         <v/>
       </c>

--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -145,8 +145,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -157,6 +155,7 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -183,12 +182,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -1046,14 +1039,14 @@
     <row r="6">
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Green row</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+          <t>Green cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>A worked example so you can see the expected format. Delete it when you start.</t>
+          <t>A worked example, so you can see the expected format and the charts say something the moment you open the file. Replace it with your own data when you start.</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1208,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Fit a straight line through two columns, then find out how much of the outcome that one driver actually explains. Yellow cells are yours; everything blue is a formula you can point at.</t>
+          <t>Fit a straight line through two columns, then find out how much of the outcome that one driver actually explains. The green rows are a worked example — replace them with your own pairs. Yellow cells above are yours to set; everything blue is a formula you can point at.</t>
         </is>
       </c>
     </row>
@@ -1367,26 +1360,26 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="21" t="n">
+      <c r="B12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="15" t="n">
         <v>506</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="20">
         <f>IF($C12="","",$B$41+$B$40*$B12)</f>
         <v/>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="20">
         <f>IF($D12="","",$C12-$D12)</f>
         <v/>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="21">
         <f>IF($E12="","",IF(ABS($E12)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1400,551 +1393,551 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="21" t="n">
+      <c r="B13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="15" t="n">
         <v>344</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="20">
         <f>IF($C13="","",$B$41+$B$40*$B13)</f>
         <v/>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="20">
         <f>IF($D13="","",$C13-$D13)</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="21">
         <f>IF($E13="","",IF(ABS($E13)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C14" s="15" t="n">
         <v>479</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="20">
         <f>IF($C14="","",$B$41+$B$40*$B14)</f>
         <v/>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="20">
         <f>IF($D14="","",$C14-$D14)</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="21">
         <f>IF($E14="","",IF(ABS($E14)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
+      <c r="B15" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="21" t="n">
+      <c r="C15" s="15" t="n">
         <v>422</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="20">
         <f>IF($C15="","",$B$41+$B$40*$B15)</f>
         <v/>
       </c>
-      <c r="E15" s="22">
+      <c r="E15" s="20">
         <f>IF($D15="","",$C15-$D15)</f>
         <v/>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="21">
         <f>IF($E15="","",IF(ABS($E15)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
+      <c r="B16" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="15" t="n">
         <v>452</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="20">
         <f>IF($C16="","",$B$41+$B$40*$B16)</f>
         <v/>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="20">
         <f>IF($D16="","",$C16-$D16)</f>
         <v/>
       </c>
-      <c r="F16" s="23">
+      <c r="F16" s="21">
         <f>IF($E16="","",IF(ABS($E16)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
+      <c r="B17" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="15" t="n">
         <v>374</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="20">
         <f>IF($C17="","",$B$41+$B$40*$B17)</f>
         <v/>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="20">
         <f>IF($D17="","",$C17-$D17)</f>
         <v/>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="21">
         <f>IF($E17="","",IF(ABS($E17)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="21" t="n">
+      <c r="B18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="15" t="n">
         <v>451</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="20">
         <f>IF($C18="","",$B$41+$B$40*$B18)</f>
         <v/>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="20">
         <f>IF($D18="","",$C18-$D18)</f>
         <v/>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="21">
         <f>IF($E18="","",IF(ABS($E18)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="21" t="n">
+      <c r="B19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="15" t="n">
         <v>360</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="20">
         <f>IF($C19="","",$B$41+$B$40*$B19)</f>
         <v/>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="20">
         <f>IF($D19="","",$C19-$D19)</f>
         <v/>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="21">
         <f>IF($E19="","",IF(ABS($E19)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="21" t="n">
+      <c r="B20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="15" t="n">
         <v>260</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="20">
         <f>IF($C20="","",$B$41+$B$40*$B20)</f>
         <v/>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="20">
         <f>IF($D20="","",$C20-$D20)</f>
         <v/>
       </c>
-      <c r="F20" s="23">
+      <c r="F20" s="21">
         <f>IF($E20="","",IF(ABS($E20)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="21" t="n">
+      <c r="B21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="15" t="n">
         <v>415</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="20">
         <f>IF($C21="","",$B$41+$B$40*$B21)</f>
         <v/>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="20">
         <f>IF($D21="","",$C21-$D21)</f>
         <v/>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="21">
         <f>IF($E21="","",IF(ABS($E21)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
+      <c r="B22" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="15" t="n">
         <v>555</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="20">
         <f>IF($C22="","",$B$41+$B$40*$B22)</f>
         <v/>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="20">
         <f>IF($D22="","",$C22-$D22)</f>
         <v/>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="21">
         <f>IF($E22="","",IF(ABS($E22)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="21" t="n">
+      <c r="B23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="15" t="n">
         <v>393</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="20">
         <f>IF($C23="","",$B$41+$B$40*$B23)</f>
         <v/>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="20">
         <f>IF($D23="","",$C23-$D23)</f>
         <v/>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="21">
         <f>IF($E23="","",IF(ABS($E23)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="21" t="n">
+      <c r="B24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="15" t="n">
         <v>454</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="20">
         <f>IF($C24="","",$B$41+$B$40*$B24)</f>
         <v/>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="20">
         <f>IF($D24="","",$C24-$D24)</f>
         <v/>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="21">
         <f>IF($E24="","",IF(ABS($E24)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="21" t="n">
+      <c r="B25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="15" t="n">
         <v>257</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="20">
         <f>IF($C25="","",$B$41+$B$40*$B25)</f>
         <v/>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="20">
         <f>IF($D25="","",$C25-$D25)</f>
         <v/>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="21">
         <f>IF($E25="","",IF(ABS($E25)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="21" t="n">
+      <c r="B26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="15" t="n">
         <v>544</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="20">
         <f>IF($C26="","",$B$41+$B$40*$B26)</f>
         <v/>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="20">
         <f>IF($D26="","",$C26-$D26)</f>
         <v/>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="21">
         <f>IF($E26="","",IF(ABS($E26)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="21" t="n">
+      <c r="B27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="15" t="n">
         <v>482</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="20">
         <f>IF($C27="","",$B$41+$B$40*$B27)</f>
         <v/>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="20">
         <f>IF($D27="","",$C27-$D27)</f>
         <v/>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="21">
         <f>IF($E27="","",IF(ABS($E27)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="21" t="n">
+      <c r="B28" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="15" t="n">
         <v>403</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="20">
         <f>IF($C28="","",$B$41+$B$40*$B28)</f>
         <v/>
       </c>
-      <c r="E28" s="22">
+      <c r="E28" s="20">
         <f>IF($D28="","",$C28-$D28)</f>
         <v/>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="21">
         <f>IF($E28="","",IF(ABS($E28)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
+      <c r="B29" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="15" t="n">
         <v>433</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="20">
         <f>IF($C29="","",$B$41+$B$40*$B29)</f>
         <v/>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="20">
         <f>IF($D29="","",$C29-$D29)</f>
         <v/>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="21">
         <f>IF($E29="","",IF(ABS($E29)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="21" t="n">
+      <c r="C30" s="15" t="n">
         <v>483</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="20">
         <f>IF($C30="","",$B$41+$B$40*$B30)</f>
         <v/>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="20">
         <f>IF($D30="","",$C30-$D30)</f>
         <v/>
       </c>
-      <c r="F30" s="23">
+      <c r="F30" s="21">
         <f>IF($E30="","",IF(ABS($E30)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="21" t="n">
+      <c r="B31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="15" t="n">
         <v>261</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="20">
         <f>IF($C31="","",$B$41+$B$40*$B31)</f>
         <v/>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="20">
         <f>IF($D31="","",$C31-$D31)</f>
         <v/>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="21">
         <f>IF($E31="","",IF(ABS($E31)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="21" t="n">
+      <c r="B32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="15" t="n">
         <v>424</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="20">
         <f>IF($C32="","",$B$41+$B$40*$B32)</f>
         <v/>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="20">
         <f>IF($D32="","",$C32-$D32)</f>
         <v/>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="21">
         <f>IF($E32="","",IF(ABS($E32)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="21" t="n">
+      <c r="B33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="15" t="n">
         <v>359</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="20">
         <f>IF($C33="","",$B$41+$B$40*$B33)</f>
         <v/>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="20">
         <f>IF($D33="","",$C33-$D33)</f>
         <v/>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="21">
         <f>IF($E33="","",IF(ABS($E33)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="21" t="n">
+      <c r="B34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="15" t="n">
         <v>505</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="20">
         <f>IF($C34="","",$B$41+$B$40*$B34)</f>
         <v/>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="20">
         <f>IF($D34="","",$C34-$D34)</f>
         <v/>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="21">
         <f>IF($E34="","",IF(ABS($E34)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1995,7 +1988,7 @@
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B39" s="24">
+      <c r="B39" s="22">
         <f>COUNT($C$11:$C$34)</f>
         <v/>
       </c>
@@ -2011,7 +2004,7 @@
           <t>Slope — seconds per extra transfer</t>
         </is>
       </c>
-      <c r="B40" s="25">
+      <c r="B40" s="23">
         <f>SLOPE($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2027,7 +2020,7 @@
           <t>Intercept — seconds at zero transfers</t>
         </is>
       </c>
-      <c r="B41" s="25">
+      <c r="B41" s="23">
         <f>INTERCEPT($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2043,7 +2036,7 @@
           <t>R² — share of the spread the line explains</t>
         </is>
       </c>
-      <c r="B42" s="26">
+      <c r="B42" s="24">
         <f>RSQ($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2059,7 +2052,7 @@
           <t>Correlation r</t>
         </is>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="25">
         <f>CORREL($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2075,7 +2068,7 @@
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B44" s="25">
+      <c r="B44" s="23">
         <f>STEYX($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2091,7 +2084,7 @@
           <t>Standard error of the slope</t>
         </is>
       </c>
-      <c r="B45" s="25">
+      <c r="B45" s="23">
         <f>INDEX(LINEST($C$11:$C$34,$B$11:$B$34,TRUE,TRUE),2,1)</f>
         <v/>
       </c>
@@ -2107,7 +2100,7 @@
           <t>t-stat for the slope</t>
         </is>
       </c>
-      <c r="B46" s="25">
+      <c r="B46" s="23">
         <f>IFERROR($B$40/$B$45,"")</f>
         <v/>
       </c>
@@ -2123,7 +2116,7 @@
           <t>Degrees of freedom</t>
         </is>
       </c>
-      <c r="B47" s="24">
+      <c r="B47" s="22">
         <f>IFERROR(COUNT($C$11:$C$34)-2,"")</f>
         <v/>
       </c>
@@ -2139,7 +2132,7 @@
           <t>p-value for the slope</t>
         </is>
       </c>
-      <c r="B48" s="28">
+      <c r="B48" s="26">
         <f>IFERROR(TDIST(ABS($B$46),$B$47,2),"")</f>
         <v/>
       </c>
@@ -2163,13 +2156,13 @@
       <c r="F50" s="7" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="29">
+      <c r="A51" s="27">
         <f>"Handle time in seconds  =  "&amp;TEXT($B$41,"0.0")&amp;"  +  "&amp;TEXT($B$40,"0.0")&amp;" × transfers.      One more transfer is worth about "&amp;TEXT($B$40,"0")&amp;" seconds, and this one driver explains "&amp;TEXT($B$42,"0%")&amp;" of the spread in handle time "&amp;"(p = "&amp;TEXT($B$48,"0.000")&amp;", n = "&amp;TEXT($B$39,"0")&amp;")."</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="29">
+      <c r="A52" s="27">
         <f>IF($B$48="","",IF($B$48&gt;=0.05,"NOT PROVEN — at this sample size the slope is not distinguishable from a flat line. Collect more rows before you build anything on it.",IF($B$42&lt;0.3,"REAL BUT PARTIAL — the slope is significant (p = "&amp;TEXT($B$48,"0.000")&amp;") and the line still explains only "&amp;TEXT($B$42,"0%")&amp;" of the spread. Transfers are a genuine driver AND most of what moves handle time is not in this model.","REAL AND STRONG — significant, and the line explains "&amp;TEXT($B$42,"0%")&amp;" of the spread. Rare in support data; check the sample before you celebrate.")))</f>
         <v/>
       </c>
@@ -2357,7 +2350,7 @@
           <t>Smallest effect worth acting on (seconds)</t>
         </is>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="28" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -2535,31 +2528,31 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="21" t="n">
+      <c r="B12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="E12" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="21" t="n">
+      <c r="E12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="15" t="n">
         <v>506</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="20">
         <f>IF($F12="","",$B$40+$B$41*$B12+$B$42*$C12+$B$43*$D12+$B$44*$E12)</f>
         <v/>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="20">
         <f>IF($G12="","",$F12-$G12)</f>
         <v/>
       </c>
@@ -2620,31 +2613,31 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="21" t="n">
+      <c r="B13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E13" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="21" t="n">
+      <c r="E13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="15" t="n">
         <v>344</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="20">
         <f>IF($F13="","",$B$40+$B$41*$B13+$B$42*$C13+$B$43*$D13+$B$44*$E13)</f>
         <v/>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="20">
         <f>IF($G13="","",$F13-$G13)</f>
         <v/>
       </c>
@@ -2698,31 +2691,31 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="21" t="n">
+      <c r="B14" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="15" t="n">
         <v>479</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="20">
         <f>IF($F14="","",$B$40+$B$41*$B14+$B$42*$C14+$B$43*$D14+$B$44*$E14)</f>
         <v/>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="20">
         <f>IF($G14="","",$F14-$G14)</f>
         <v/>
       </c>
@@ -2776,31 +2769,31 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="21" t="n">
+      <c r="B15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="15" t="n">
         <v>422</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="20">
         <f>IF($F15="","",$B$40+$B$41*$B15+$B$42*$C15+$B$43*$D15+$B$44*$E15)</f>
         <v/>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="20">
         <f>IF($G15="","",$F15-$G15)</f>
         <v/>
       </c>
@@ -2854,31 +2847,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="21" t="n">
+      <c r="B16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="20" t="n">
+      <c r="E16" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="21" t="n">
+      <c r="F16" s="15" t="n">
         <v>452</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="20">
         <f>IF($F16="","",$B$40+$B$41*$B16+$B$42*$C16+$B$43*$D16+$B$44*$E16)</f>
         <v/>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="20">
         <f>IF($G16="","",$F16-$G16)</f>
         <v/>
       </c>
@@ -2932,31 +2925,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="21" t="n">
+      <c r="B17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E17" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="21" t="n">
+      <c r="F17" s="15" t="n">
         <v>374</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="20">
         <f>IF($F17="","",$B$40+$B$41*$B17+$B$42*$C17+$B$43*$D17+$B$44*$E17)</f>
         <v/>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="20">
         <f>IF($G17="","",$F17-$G17)</f>
         <v/>
       </c>
@@ -3010,31 +3003,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="21" t="n">
+      <c r="B18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="21" t="n">
+      <c r="E18" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="15" t="n">
         <v>451</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="20">
         <f>IF($F18="","",$B$40+$B$41*$B18+$B$42*$C18+$B$43*$D18+$B$44*$E18)</f>
         <v/>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="20">
         <f>IF($G18="","",$F18-$G18)</f>
         <v/>
       </c>
@@ -3088,31 +3081,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="21" t="n">
+      <c r="B19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="21" t="n">
+      <c r="E19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="15" t="n">
         <v>360</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="20">
         <f>IF($F19="","",$B$40+$B$41*$B19+$B$42*$C19+$B$43*$D19+$B$44*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="20">
         <f>IF($G19="","",$F19-$G19)</f>
         <v/>
       </c>
@@ -3166,31 +3159,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="21" t="n">
+      <c r="B20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="21" t="n">
+      <c r="E20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15" t="n">
         <v>260</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="20">
         <f>IF($F20="","",$B$40+$B$41*$B20+$B$42*$C20+$B$43*$D20+$B$44*$E20)</f>
         <v/>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="20">
         <f>IF($G20="","",$F20-$G20)</f>
         <v/>
       </c>
@@ -3244,31 +3237,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="21" t="n">
+      <c r="B21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="E21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="21" t="n">
+      <c r="E21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15" t="n">
         <v>415</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="20">
         <f>IF($F21="","",$B$40+$B$41*$B21+$B$42*$C21+$B$43*$D21+$B$44*$E21)</f>
         <v/>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="20">
         <f>IF($G21="","",$F21-$G21)</f>
         <v/>
       </c>
@@ -3322,31 +3315,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="21" t="n">
+      <c r="B22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="21" t="n">
+      <c r="F22" s="15" t="n">
         <v>555</v>
       </c>
-      <c r="G22" s="22">
+      <c r="G22" s="20">
         <f>IF($F22="","",$B$40+$B$41*$B22+$B$42*$C22+$B$43*$D22+$B$44*$E22)</f>
         <v/>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="20">
         <f>IF($G22="","",$F22-$G22)</f>
         <v/>
       </c>
@@ -3400,31 +3393,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="21" t="n">
+      <c r="B23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="21" t="n">
+      <c r="E23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="15" t="n">
         <v>393</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="20">
         <f>IF($F23="","",$B$40+$B$41*$B23+$B$42*$C23+$B$43*$D23+$B$44*$E23)</f>
         <v/>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="20">
         <f>IF($G23="","",$F23-$G23)</f>
         <v/>
       </c>
@@ -3478,31 +3471,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="21" t="n">
+      <c r="B24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="21" t="n">
+      <c r="E24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="15" t="n">
         <v>454</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="20">
         <f>IF($F24="","",$B$40+$B$41*$B24+$B$42*$C24+$B$43*$D24+$B$44*$E24)</f>
         <v/>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="20">
         <f>IF($G24="","",$F24-$G24)</f>
         <v/>
       </c>
@@ -3556,31 +3549,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="21" t="n">
+      <c r="B25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="E25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="21" t="n">
+      <c r="E25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="15" t="n">
         <v>257</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="20">
         <f>IF($F25="","",$B$40+$B$41*$B25+$B$42*$C25+$B$43*$D25+$B$44*$E25)</f>
         <v/>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="20">
         <f>IF($G25="","",$F25-$G25)</f>
         <v/>
       </c>
@@ -3634,31 +3627,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="21" t="n">
+      <c r="B26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="E26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="21" t="n">
+      <c r="E26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="15" t="n">
         <v>544</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="20">
         <f>IF($F26="","",$B$40+$B$41*$B26+$B$42*$C26+$B$43*$D26+$B$44*$E26)</f>
         <v/>
       </c>
-      <c r="H26" s="22">
+      <c r="H26" s="20">
         <f>IF($G26="","",$F26-$G26)</f>
         <v/>
       </c>
@@ -3712,31 +3705,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="21" t="n">
+      <c r="B27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E27" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="21" t="n">
+      <c r="E27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="15" t="n">
         <v>482</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="20">
         <f>IF($F27="","",$B$40+$B$41*$B27+$B$42*$C27+$B$43*$D27+$B$44*$E27)</f>
         <v/>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="20">
         <f>IF($G27="","",$F27-$G27)</f>
         <v/>
       </c>
@@ -3790,31 +3783,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="21" t="n">
+      <c r="B28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="21" t="n">
+      <c r="E28" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="15" t="n">
         <v>403</v>
       </c>
-      <c r="G28" s="22">
+      <c r="G28" s="20">
         <f>IF($F28="","",$B$40+$B$41*$B28+$B$42*$C28+$B$43*$D28+$B$44*$E28)</f>
         <v/>
       </c>
-      <c r="H28" s="22">
+      <c r="H28" s="20">
         <f>IF($G28="","",$F28-$G28)</f>
         <v/>
       </c>
@@ -3868,31 +3861,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="21" t="n">
+      <c r="B29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="20" t="n">
+      <c r="E29" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="21" t="n">
+      <c r="F29" s="15" t="n">
         <v>433</v>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="20">
         <f>IF($F29="","",$B$40+$B$41*$B29+$B$42*$C29+$B$43*$D29+$B$44*$E29)</f>
         <v/>
       </c>
-      <c r="H29" s="22">
+      <c r="H29" s="20">
         <f>IF($G29="","",$F29-$G29)</f>
         <v/>
       </c>
@@ -3946,31 +3939,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="21" t="n">
+      <c r="B30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E30" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="21" t="n">
+      <c r="F30" s="15" t="n">
         <v>483</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="20">
         <f>IF($F30="","",$B$40+$B$41*$B30+$B$42*$C30+$B$43*$D30+$B$44*$E30)</f>
         <v/>
       </c>
-      <c r="H30" s="22">
+      <c r="H30" s="20">
         <f>IF($G30="","",$F30-$G30)</f>
         <v/>
       </c>
@@ -4024,31 +4017,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="21" t="n">
+      <c r="B31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="21" t="n">
+      <c r="E31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="15" t="n">
         <v>261</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="20">
         <f>IF($F31="","",$B$40+$B$41*$B31+$B$42*$C31+$B$43*$D31+$B$44*$E31)</f>
         <v/>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="20">
         <f>IF($G31="","",$F31-$G31)</f>
         <v/>
       </c>
@@ -4102,31 +4095,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="21" t="n">
+      <c r="B32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="15" t="n">
         <v>53</v>
       </c>
-      <c r="E32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="21" t="n">
+      <c r="E32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="15" t="n">
         <v>424</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="20">
         <f>IF($F32="","",$B$40+$B$41*$B32+$B$42*$C32+$B$43*$D32+$B$44*$E32)</f>
         <v/>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="20">
         <f>IF($G32="","",$F32-$G32)</f>
         <v/>
       </c>
@@ -4180,31 +4173,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="21" t="n">
+      <c r="B33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="E33" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="21" t="n">
+      <c r="E33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="15" t="n">
         <v>359</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="20">
         <f>IF($F33="","",$B$40+$B$41*$B33+$B$42*$C33+$B$43*$D33+$B$44*$E33)</f>
         <v/>
       </c>
-      <c r="H33" s="22">
+      <c r="H33" s="20">
         <f>IF($G33="","",$F33-$G33)</f>
         <v/>
       </c>
@@ -4258,31 +4251,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="21" t="n">
+      <c r="B34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="21" t="n">
+      <c r="E34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="15" t="n">
         <v>505</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="20">
         <f>IF($F34="","",$B$40+$B$41*$B34+$B$42*$C34+$B$43*$D34+$B$44*$E34)</f>
         <v/>
       </c>
-      <c r="H34" s="22">
+      <c r="H34" s="20">
         <f>IF($G34="","",$F34-$G34)</f>
         <v/>
       </c>
@@ -4407,184 +4400,184 @@
       </c>
     </row>
     <row r="40" ht="84" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,5),"")</f>
         <v/>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,5),"")</f>
         <v/>
       </c>
-      <c r="D40" s="31">
+      <c r="D40" s="30">
         <f>IFERROR($B40/$C40,"")</f>
         <v/>
       </c>
-      <c r="E40" s="32">
+      <c r="E40" s="31">
         <f>IFERROR(TDIST(ABS($D40),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="I40" s="33">
+      <c r="I40" s="32">
         <f>IF($B40="","","Predicted handle time for a contact with every driver at zero — before 17:00, under the limit, a brand-new agent, no transfers. Read it as the starting point the four effects are added to, not as a prediction.")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B41" s="31">
+      <c r="B41" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,4),"")</f>
         <v/>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,4),"")</f>
         <v/>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="30">
         <f>IFERROR($B41/$C41,"")</f>
         <v/>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="31">
         <f>IFERROR(TDIST(ABS($D41),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($B$11:$B$34,$J$11:$L$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="33">
         <f>IFERROR($B41*(MAX($B$11:$B$34)-MIN($B$11:$B$34)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="29">
+      <c r="H41" s="27">
         <f>IF($E41="","",IF($E41&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G41)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="32">
         <f>IF($B41="","","Seconds the after-17:00 flag adds once the other three are held still. Compare it with the p-value beside it before you repeat it out loud.")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="30" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,3),"")</f>
         <v/>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,3),"")</f>
         <v/>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="30">
         <f>IFERROR($B42/$C42,"")</f>
         <v/>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="31">
         <f>IFERROR(TDIST(ABS($D42),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($C$11:$C$34,$M$11:$O$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="33">
         <f>IFERROR($B42*(MAX($C$11:$C$34)-MIN($C$11:$C$34)),"")</f>
         <v/>
       </c>
-      <c r="H42" s="29">
+      <c r="H42" s="27">
         <f>IF($E42="","",IF($E42&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G42)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="32">
         <f>IF($B42="","","Seconds the $50 authority limit adds once the other three are held still. This is the queue, not the money.")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="30" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B43" s="31">
+      <c r="B43" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,2),"")</f>
         <v/>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,2),"")</f>
         <v/>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="30">
         <f>IFERROR($B43/$C43,"")</f>
         <v/>
       </c>
-      <c r="E43" s="32">
+      <c r="E43" s="31">
         <f>IFERROR(TDIST(ABS($D43),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F43" s="31">
+      <c r="F43" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($D$11:$D$34,$P$11:$R$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="33">
         <f>IFERROR($B43*(MAX($D$11:$D$34)-MIN($D$11:$D$34)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="29">
+      <c r="H43" s="27">
         <f>IF($E43="","",IF($E43&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G43)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I43" s="33">
+      <c r="I43" s="32">
         <f>IF($B43="","","Seconds per extra month of tenure — negative means longer-serving agents are quicker. Small per month, so read the range column, not this one.")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="30" t="inlineStr">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B44" s="31">
+      <c r="B44" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,1),"")</f>
         <v/>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,1),"")</f>
         <v/>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="30">
         <f>IFERROR($B44/$C44,"")</f>
         <v/>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="31">
         <f>IFERROR(TDIST(ABS($D44),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($E$11:$E$34,$S$11:$U$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="33">
         <f>IFERROR($B44*(MAX($E$11:$E$34)-MIN($E$11:$E$34)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="29">
+      <c r="H44" s="27">
         <f>IF($E44="","",IF($E44&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G44)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I44" s="33">
+      <c r="I44" s="32">
         <f>IF($B44="","","Seconds each extra transfer adds once the other three are held still. Compare it with the 50.7 seconds the single-driver tab gave you.")</f>
         <v/>
       </c>
@@ -4641,7 +4634,7 @@
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B49" s="24">
+      <c r="B49" s="22">
         <f>COUNT($F$11:$F$34)</f>
         <v/>
       </c>
@@ -4657,7 +4650,7 @@
           <t>Predictors (k)</t>
         </is>
       </c>
-      <c r="B50" s="24">
+      <c r="B50" s="22">
         <f>4</f>
         <v/>
       </c>
@@ -4673,7 +4666,7 @@
           <t>R²</t>
         </is>
       </c>
-      <c r="B51" s="26">
+      <c r="B51" s="24">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,1),"")</f>
         <v/>
       </c>
@@ -4689,7 +4682,7 @@
           <t>Adjusted R²</t>
         </is>
       </c>
-      <c r="B52" s="26">
+      <c r="B52" s="24">
         <f>IFERROR(1-(1-$B$51)*($B$49-1)/($B$49-$B$50-1),"")</f>
         <v/>
       </c>
@@ -4705,7 +4698,7 @@
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B53" s="25">
+      <c r="B53" s="23">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,2),"")</f>
         <v/>
       </c>
@@ -4721,7 +4714,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="B54" s="25">
+      <c r="B54" s="23">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,1),"")</f>
         <v/>
       </c>
@@ -4737,7 +4730,7 @@
           <t>Degrees of freedom (residual)</t>
         </is>
       </c>
-      <c r="B55" s="24">
+      <c r="B55" s="22">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,2),"")</f>
         <v/>
       </c>
@@ -4753,7 +4746,7 @@
           <t>p-value for F</t>
         </is>
       </c>
-      <c r="B56" s="28">
+      <c r="B56" s="26">
         <f>IFERROR(FDIST($B$54,$B$50,$B$55),"")</f>
         <v/>
       </c>
@@ -4769,7 +4762,7 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B57" s="23">
+      <c r="B57" s="21">
         <f>IF($B$56="","",IF($B$56&gt;=0.05,"NO MODEL — these four together explain nothing",IF($B$52&lt;0.3,"USABLE BUT WEAK — read the effect sizes, not the R²","USABLE — now go and look at the residual chart")))</f>
         <v/>
       </c>
@@ -4997,171 +4990,171 @@
       <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="34" t="n">
         <v>-3.05</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="34" t="n">
         <v>0.24</v>
       </c>
-      <c r="D10" s="36" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="36">
         <f>IFERROR(EXP($B10),"")</f>
         <v/>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="36">
         <f>IFERROR(EXP($B10-1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="G10" s="37">
+      <c r="G10" s="36">
         <f>IFERROR(EXP($B10+1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="37">
         <f>"Baseline odds of a reopen with every driver at zero: "&amp;TEXT($E10,"0.000")&amp;" to 1, which is "&amp;TEXT($E10/(1+$E10),"0.0%")&amp;" probability."</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B11" s="39" t="n">
+      <c r="B11" s="34" t="n">
         <v>1.16</v>
       </c>
-      <c r="C11" s="39" t="n">
+      <c r="C11" s="34" t="n">
         <v>0.21</v>
       </c>
-      <c r="D11" s="40" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="38">
         <f>IFERROR(EXP($B11),"")</f>
         <v/>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="38">
         <f>IFERROR(EXP($B11-1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="38">
         <f>IFERROR(EXP($B11+1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="H11" s="33">
+      <c r="H11" s="32">
         <f>"Raising the adjustment after 17:00 multiplies the odds of a reopen by "&amp;TEXT($E11,"0.00")&amp;". This is the posting-batch effect, and it is the largest single driver in the model."</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B12" s="39" t="n">
+      <c r="B12" s="34" t="n">
         <v>0.83</v>
       </c>
-      <c r="C12" s="39" t="n">
+      <c r="C12" s="34" t="n">
         <v>0.22</v>
       </c>
-      <c r="D12" s="40" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>0.0002</t>
         </is>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="38">
         <f>IFERROR(EXP($B12),"")</f>
         <v/>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="38">
         <f>IFERROR(EXP($B12-1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="38">
         <f>IFERROR(EXP($B12+1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="32">
         <f>"Clearing the $50 authority limit multiplies the odds of a reopen by "&amp;TEXT($E12,"0.00")&amp;", because the case waits in a queue for approval."</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="84" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B13" s="39" t="n">
+      <c r="B13" s="34" t="n">
         <v>-0.038</v>
       </c>
-      <c r="C13" s="39" t="n">
+      <c r="C13" s="34" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="D13" s="40" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="38">
         <f>IFERROR(EXP($B13),"")</f>
         <v/>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="38">
         <f>IFERROR(EXP($B13-1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="38">
         <f>IFERROR(EXP($B13+1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="32">
         <f>"Each extra month of tenure multiplies the odds by "&amp;TEXT($E13,"0.000")&amp;" — so a 24-month agent runs at "&amp;TEXT($E13^24,"0.00")&amp;" times the odds of a first-week agent."</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B14" s="39" t="n">
+      <c r="B14" s="34" t="n">
         <v>0.61</v>
       </c>
-      <c r="C14" s="39" t="n">
+      <c r="C14" s="34" t="n">
         <v>0.12</v>
       </c>
-      <c r="D14" s="40" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="38">
         <f>IFERROR(EXP($B14),"")</f>
         <v/>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="38">
         <f>IFERROR(EXP($B14-1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="38">
         <f>IFERROR(EXP($B14+1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="32">
         <f>"Each extra transfer multiplies the odds of a reopen by "&amp;TEXT($E14,"0.00")&amp;". Multiply by how common transfers are before you rank it against the others."</f>
         <v/>
       </c>
@@ -5257,797 +5250,797 @@
       <c r="F19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="42">
+      <c r="G19" s="39">
         <f>IF($B19="","",$B$10+$B$11*$B19+$B$12*$C19+$B$13*$D19+$B$14*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="43">
+      <c r="H19" s="40">
         <f>IFERROR(1/(1+EXP(-$G19)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="44">
+      <c r="I19" s="41">
         <f>IF($H19="","",IF($H19&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="21" t="n">
+      <c r="B20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="E20" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="27">
+      <c r="E20" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="25">
         <f>IF($B20="","",$B$10+$B$11*$B20+$B$12*$C20+$B$13*$D20+$B$14*$E20)</f>
         <v/>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="24">
         <f>IFERROR(1/(1+EXP(-$G20)),"")</f>
         <v/>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="22">
         <f>IF($H20="","",IF($H20&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="21" t="n">
+      <c r="B21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E21" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="27">
+      <c r="E21" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="25">
         <f>IF($B21="","",$B$10+$B$11*$B21+$B$12*$C21+$B$13*$D21+$B$14*$E21)</f>
         <v/>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="24">
         <f>IFERROR(1/(1+EXP(-$G21)),"")</f>
         <v/>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="22">
         <f>IF($H21="","",IF($H21&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="21" t="n">
+      <c r="B22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E22" s="20" t="n">
+      <c r="E22" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="27">
+      <c r="F22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="25">
         <f>IF($B22="","",$B$10+$B$11*$B22+$B$12*$C22+$B$13*$D22+$B$14*$E22)</f>
         <v/>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="24">
         <f>IFERROR(1/(1+EXP(-$G22)),"")</f>
         <v/>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="22">
         <f>IF($H22="","",IF($H22&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="21" t="n">
+      <c r="B23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15" t="n">
         <v>33</v>
       </c>
-      <c r="E23" s="20" t="n">
+      <c r="E23" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="27">
+      <c r="F23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="25">
         <f>IF($B23="","",$B$10+$B$11*$B23+$B$12*$C23+$B$13*$D23+$B$14*$E23)</f>
         <v/>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="24">
         <f>IFERROR(1/(1+EXP(-$G23)),"")</f>
         <v/>
       </c>
-      <c r="I23" s="24">
+      <c r="I23" s="22">
         <f>IF($H23="","",IF($H23&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="21" t="n">
+      <c r="B24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E24" s="20" t="n">
+      <c r="E24" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="27">
+      <c r="F24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="25">
         <f>IF($B24="","",$B$10+$B$11*$B24+$B$12*$C24+$B$13*$D24+$B$14*$E24)</f>
         <v/>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="24">
         <f>IFERROR(1/(1+EXP(-$G24)),"")</f>
         <v/>
       </c>
-      <c r="I24" s="24">
+      <c r="I24" s="22">
         <f>IF($H24="","",IF($H24&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="21" t="n">
+      <c r="B25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="15" t="n">
         <v>46</v>
       </c>
-      <c r="E25" s="20" t="n">
+      <c r="E25" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="27">
+      <c r="F25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="25">
         <f>IF($B25="","",$B$10+$B$11*$B25+$B$12*$C25+$B$13*$D25+$B$14*$E25)</f>
         <v/>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="24">
         <f>IFERROR(1/(1+EXP(-$G25)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="24">
+      <c r="I25" s="22">
         <f>IF($H25="","",IF($H25&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="21" t="n">
+      <c r="B26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="27">
+      <c r="E26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="25">
         <f>IF($B26="","",$B$10+$B$11*$B26+$B$12*$C26+$B$13*$D26+$B$14*$E26)</f>
         <v/>
       </c>
-      <c r="H26" s="26">
+      <c r="H26" s="24">
         <f>IFERROR(1/(1+EXP(-$G26)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="24">
+      <c r="I26" s="22">
         <f>IF($H26="","",IF($H26&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="21" t="n">
+      <c r="B27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="27">
+      <c r="E27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="25">
         <f>IF($B27="","",$B$10+$B$11*$B27+$B$12*$C27+$B$13*$D27+$B$14*$E27)</f>
         <v/>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="24">
         <f>IFERROR(1/(1+EXP(-$G27)),"")</f>
         <v/>
       </c>
-      <c r="I27" s="24">
+      <c r="I27" s="22">
         <f>IF($H27="","",IF($H27&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="21" t="n">
+      <c r="B28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="E28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="27">
+      <c r="E28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="25">
         <f>IF($B28="","",$B$10+$B$11*$B28+$B$12*$C28+$B$13*$D28+$B$14*$E28)</f>
         <v/>
       </c>
-      <c r="H28" s="26">
+      <c r="H28" s="24">
         <f>IFERROR(1/(1+EXP(-$G28)),"")</f>
         <v/>
       </c>
-      <c r="I28" s="24">
+      <c r="I28" s="22">
         <f>IF($H28="","",IF($H28&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="21" t="n">
+      <c r="B29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="15" t="n">
         <v>28</v>
       </c>
-      <c r="E29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="27">
+      <c r="E29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="25">
         <f>IF($B29="","",$B$10+$B$11*$B29+$B$12*$C29+$B$13*$D29+$B$14*$E29)</f>
         <v/>
       </c>
-      <c r="H29" s="26">
+      <c r="H29" s="24">
         <f>IFERROR(1/(1+EXP(-$G29)),"")</f>
         <v/>
       </c>
-      <c r="I29" s="24">
+      <c r="I29" s="22">
         <f>IF($H29="","",IF($H29&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="21" t="n">
+      <c r="B30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="20" t="n">
+      <c r="E30" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="27">
+      <c r="F30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="25">
         <f>IF($B30="","",$B$10+$B$11*$B30+$B$12*$C30+$B$13*$D30+$B$14*$E30)</f>
         <v/>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="24">
         <f>IFERROR(1/(1+EXP(-$G30)),"")</f>
         <v/>
       </c>
-      <c r="I30" s="24">
+      <c r="I30" s="22">
         <f>IF($H30="","",IF($H30&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="21" t="n">
+      <c r="B31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="27">
+      <c r="E31" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="25">
         <f>IF($B31="","",$B$10+$B$11*$B31+$B$12*$C31+$B$13*$D31+$B$14*$E31)</f>
         <v/>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="24">
         <f>IFERROR(1/(1+EXP(-$G31)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="24">
+      <c r="I31" s="22">
         <f>IF($H31="","",IF($H31&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="21" t="n">
+      <c r="B32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="15" t="n">
         <v>39</v>
       </c>
-      <c r="E32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="27">
+      <c r="E32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="25">
         <f>IF($B32="","",$B$10+$B$11*$B32+$B$12*$C32+$B$13*$D32+$B$14*$E32)</f>
         <v/>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="24">
         <f>IFERROR(1/(1+EXP(-$G32)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="24">
+      <c r="I32" s="22">
         <f>IF($H32="","",IF($H32&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="21" t="n">
+      <c r="B33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="E33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="27">
+      <c r="E33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="25">
         <f>IF($B33="","",$B$10+$B$11*$B33+$B$12*$C33+$B$13*$D33+$B$14*$E33)</f>
         <v/>
       </c>
-      <c r="H33" s="26">
+      <c r="H33" s="24">
         <f>IFERROR(1/(1+EXP(-$G33)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="24">
+      <c r="I33" s="22">
         <f>IF($H33="","",IF($H33&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="21" t="n">
+      <c r="B34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="E34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="27">
+      <c r="E34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="25">
         <f>IF($B34="","",$B$10+$B$11*$B34+$B$12*$C34+$B$13*$D34+$B$14*$E34)</f>
         <v/>
       </c>
-      <c r="H34" s="26">
+      <c r="H34" s="24">
         <f>IFERROR(1/(1+EXP(-$G34)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="24">
+      <c r="I34" s="22">
         <f>IF($H34="","",IF($H34&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="21" t="n">
+      <c r="B35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E35" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="27">
+      <c r="E35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="25">
         <f>IF($B35="","",$B$10+$B$11*$B35+$B$12*$C35+$B$13*$D35+$B$14*$E35)</f>
         <v/>
       </c>
-      <c r="H35" s="26">
+      <c r="H35" s="24">
         <f>IFERROR(1/(1+EXP(-$G35)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="24">
+      <c r="I35" s="22">
         <f>IF($H35="","",IF($H35&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="21" t="n">
+      <c r="B36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="27">
+      <c r="E36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="25">
         <f>IF($B36="","",$B$10+$B$11*$B36+$B$12*$C36+$B$13*$D36+$B$14*$E36)</f>
         <v/>
       </c>
-      <c r="H36" s="26">
+      <c r="H36" s="24">
         <f>IFERROR(1/(1+EXP(-$G36)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="24">
+      <c r="I36" s="22">
         <f>IF($H36="","",IF($H36&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="21" t="n">
+      <c r="B37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="20" t="n">
+      <c r="E37" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="27">
+      <c r="F37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="25">
         <f>IF($B37="","",$B$10+$B$11*$B37+$B$12*$C37+$B$13*$D37+$B$14*$E37)</f>
         <v/>
       </c>
-      <c r="H37" s="26">
+      <c r="H37" s="24">
         <f>IFERROR(1/(1+EXP(-$G37)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="24">
+      <c r="I37" s="22">
         <f>IF($H37="","",IF($H37&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="21" t="n">
+      <c r="B38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E38" s="20" t="n">
+      <c r="E38" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="27">
+      <c r="F38" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="25">
         <f>IF($B38="","",$B$10+$B$11*$B38+$B$12*$C38+$B$13*$D38+$B$14*$E38)</f>
         <v/>
       </c>
-      <c r="H38" s="26">
+      <c r="H38" s="24">
         <f>IFERROR(1/(1+EXP(-$G38)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="24">
+      <c r="I38" s="22">
         <f>IF($H38="","",IF($H38&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="21" t="n">
+      <c r="B39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="27">
+      <c r="E39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="25">
         <f>IF($B39="","",$B$10+$B$11*$B39+$B$12*$C39+$B$13*$D39+$B$14*$E39)</f>
         <v/>
       </c>
-      <c r="H39" s="26">
+      <c r="H39" s="24">
         <f>IFERROR(1/(1+EXP(-$G39)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="24">
+      <c r="I39" s="22">
         <f>IF($H39="","",IF($H39&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="21" t="n">
+      <c r="B40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="15" t="n">
         <v>53</v>
       </c>
-      <c r="E40" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="27">
+      <c r="E40" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="25">
         <f>IF($B40="","",$B$10+$B$11*$B40+$B$12*$C40+$B$13*$D40+$B$14*$E40)</f>
         <v/>
       </c>
-      <c r="H40" s="26">
+      <c r="H40" s="24">
         <f>IFERROR(1/(1+EXP(-$G40)),"")</f>
         <v/>
       </c>
-      <c r="I40" s="24">
+      <c r="I40" s="22">
         <f>IF($H40="","",IF($H40&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="21" t="n">
+      <c r="B41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="E41" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="27">
+      <c r="E41" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25">
         <f>IF($B41="","",$B$10+$B$11*$B41+$B$12*$C41+$B$13*$D41+$B$14*$E41)</f>
         <v/>
       </c>
-      <c r="H41" s="26">
+      <c r="H41" s="24">
         <f>IFERROR(1/(1+EXP(-$G41)),"")</f>
         <v/>
       </c>
-      <c r="I41" s="24">
+      <c r="I41" s="22">
         <f>IF($H41="","",IF($H41&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="21" t="n">
+      <c r="B42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="27">
+      <c r="E42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="25">
         <f>IF($B42="","",$B$10+$B$11*$B42+$B$12*$C42+$B$13*$D42+$B$14*$E42)</f>
         <v/>
       </c>
-      <c r="H42" s="26">
+      <c r="H42" s="24">
         <f>IFERROR(1/(1+EXP(-$G42)),"")</f>
         <v/>
       </c>
-      <c r="I42" s="24">
+      <c r="I42" s="22">
         <f>IF($H42="","",IF($H42&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -6081,7 +6074,7 @@
           <t>Flag a contact at this probability or above</t>
         </is>
       </c>
-      <c r="B46" s="45" t="n">
+      <c r="B46" s="42" t="n">
         <v>0.2</v>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -6096,7 +6089,7 @@
           <t>AUC the tool reported</t>
         </is>
       </c>
-      <c r="B47" s="46" t="n">
+      <c r="B47" s="43" t="n">
         <v>0.74</v>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -6154,15 +6147,15 @@
           <t>Flagged — predicted reopen</t>
         </is>
       </c>
-      <c r="B51" s="22">
+      <c r="B51" s="20">
         <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=1))</f>
         <v/>
       </c>
-      <c r="C51" s="22">
+      <c r="C51" s="20">
         <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=0))</f>
         <v/>
       </c>
-      <c r="D51" s="22">
+      <c r="D51" s="20">
         <f>SUM($B51:$C51)</f>
         <v/>
       </c>
@@ -6173,15 +6166,15 @@
           <t>Not flagged</t>
         </is>
       </c>
-      <c r="B52" s="22">
+      <c r="B52" s="20">
         <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=1))</f>
         <v/>
       </c>
-      <c r="C52" s="22">
+      <c r="C52" s="20">
         <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=0))</f>
         <v/>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="20">
         <f>SUM($B52:$C52)</f>
         <v/>
       </c>
@@ -6192,15 +6185,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B53" s="22">
+      <c r="B53" s="20">
         <f>SUM($B$51:$B$52)</f>
         <v/>
       </c>
-      <c r="C53" s="22">
+      <c r="C53" s="20">
         <f>SUM($C$51:$C$52)</f>
         <v/>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="20">
         <f>SUM($D$51:$D$52)</f>
         <v/>
       </c>
@@ -6257,7 +6250,7 @@
           <t>Sensitivity — reopens you caught</t>
         </is>
       </c>
-      <c r="B58" s="26">
+      <c r="B58" s="24">
         <f>IFERROR($B$51/($B$51+$B$52),"")</f>
         <v/>
       </c>
@@ -6273,7 +6266,7 @@
           <t>Specificity — quiet contacts left alone</t>
         </is>
       </c>
-      <c r="B59" s="26">
+      <c r="B59" s="24">
         <f>IFERROR($C$52/($C$52+$C$51),"")</f>
         <v/>
       </c>
@@ -6289,7 +6282,7 @@
           <t>Precision — flags that were right</t>
         </is>
       </c>
-      <c r="B60" s="26">
+      <c r="B60" s="24">
         <f>IFERROR($B$51/($B$51+$C$51),"")</f>
         <v/>
       </c>
@@ -6305,7 +6298,7 @@
           <t>Accuracy — rows called correctly</t>
         </is>
       </c>
-      <c r="B61" s="26">
+      <c r="B61" s="24">
         <f>IFERROR(($B$51+$C$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
         <v/>
       </c>
@@ -6321,7 +6314,7 @@
           <t>Base rate — share that actually reopened</t>
         </is>
       </c>
-      <c r="B62" s="26">
+      <c r="B62" s="24">
         <f>IFERROR(($B$51+$B$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
         <v/>
       </c>
@@ -6337,7 +6330,7 @@
           <t>Verdict at this threshold</t>
         </is>
       </c>
-      <c r="B63" s="23">
+      <c r="B63" s="21">
         <f>IF($B$51+$B$52=0,"NO REOPENS IN THE SAMPLE",IF($B$51/($B$51+$B$52)&lt;0.5,"MISSES MORE THAN HALF — lower the threshold",IF($B$51/($B$51+$C$51)&lt;0.2,"TOO MANY FALSE ALARMS — raise the threshold","USABLE FOR TARGETING — check it against the cost of a flag")))</f>
         <v/>
       </c>

--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -114,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -141,12 +141,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,18 +175,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="5" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -1371,15 +1360,15 @@
       <c r="C12" s="15" t="n">
         <v>506</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="16">
         <f>IF($C12="","",$B$41+$B$40*$B12)</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="16">
         <f>IF($D12="","",$C12-$D12)</f>
         <v/>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="17">
         <f>IF($E12="","",IF(ABS($E12)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1404,15 +1393,15 @@
       <c r="C13" s="15" t="n">
         <v>344</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="16">
         <f>IF($C13="","",$B$41+$B$40*$B13)</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="16">
         <f>IF($D13="","",$C13-$D13)</f>
         <v/>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="17">
         <f>IF($E13="","",IF(ABS($E13)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1429,15 +1418,15 @@
       <c r="C14" s="15" t="n">
         <v>479</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="16">
         <f>IF($C14="","",$B$41+$B$40*$B14)</f>
         <v/>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="16">
         <f>IF($D14="","",$C14-$D14)</f>
         <v/>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="17">
         <f>IF($E14="","",IF(ABS($E14)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1454,15 +1443,15 @@
       <c r="C15" s="15" t="n">
         <v>422</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="16">
         <f>IF($C15="","",$B$41+$B$40*$B15)</f>
         <v/>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="16">
         <f>IF($D15="","",$C15-$D15)</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="17">
         <f>IF($E15="","",IF(ABS($E15)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1479,15 +1468,15 @@
       <c r="C16" s="15" t="n">
         <v>452</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="16">
         <f>IF($C16="","",$B$41+$B$40*$B16)</f>
         <v/>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="16">
         <f>IF($D16="","",$C16-$D16)</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="17">
         <f>IF($E16="","",IF(ABS($E16)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1504,15 +1493,15 @@
       <c r="C17" s="15" t="n">
         <v>374</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="16">
         <f>IF($C17="","",$B$41+$B$40*$B17)</f>
         <v/>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="16">
         <f>IF($D17="","",$C17-$D17)</f>
         <v/>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="17">
         <f>IF($E17="","",IF(ABS($E17)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1529,15 +1518,15 @@
       <c r="C18" s="15" t="n">
         <v>451</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="16">
         <f>IF($C18="","",$B$41+$B$40*$B18)</f>
         <v/>
       </c>
-      <c r="E18" s="20">
+      <c r="E18" s="16">
         <f>IF($D18="","",$C18-$D18)</f>
         <v/>
       </c>
-      <c r="F18" s="21">
+      <c r="F18" s="17">
         <f>IF($E18="","",IF(ABS($E18)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1554,15 +1543,15 @@
       <c r="C19" s="15" t="n">
         <v>360</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="16">
         <f>IF($C19="","",$B$41+$B$40*$B19)</f>
         <v/>
       </c>
-      <c r="E19" s="20">
+      <c r="E19" s="16">
         <f>IF($D19="","",$C19-$D19)</f>
         <v/>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="17">
         <f>IF($E19="","",IF(ABS($E19)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1579,15 +1568,15 @@
       <c r="C20" s="15" t="n">
         <v>260</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="16">
         <f>IF($C20="","",$B$41+$B$40*$B20)</f>
         <v/>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="16">
         <f>IF($D20="","",$C20-$D20)</f>
         <v/>
       </c>
-      <c r="F20" s="21">
+      <c r="F20" s="17">
         <f>IF($E20="","",IF(ABS($E20)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1604,15 +1593,15 @@
       <c r="C21" s="15" t="n">
         <v>415</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="16">
         <f>IF($C21="","",$B$41+$B$40*$B21)</f>
         <v/>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="16">
         <f>IF($D21="","",$C21-$D21)</f>
         <v/>
       </c>
-      <c r="F21" s="21">
+      <c r="F21" s="17">
         <f>IF($E21="","",IF(ABS($E21)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1629,15 +1618,15 @@
       <c r="C22" s="15" t="n">
         <v>555</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="16">
         <f>IF($C22="","",$B$41+$B$40*$B22)</f>
         <v/>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="16">
         <f>IF($D22="","",$C22-$D22)</f>
         <v/>
       </c>
-      <c r="F22" s="21">
+      <c r="F22" s="17">
         <f>IF($E22="","",IF(ABS($E22)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1654,15 +1643,15 @@
       <c r="C23" s="15" t="n">
         <v>393</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="16">
         <f>IF($C23="","",$B$41+$B$40*$B23)</f>
         <v/>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="16">
         <f>IF($D23="","",$C23-$D23)</f>
         <v/>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="17">
         <f>IF($E23="","",IF(ABS($E23)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1679,15 +1668,15 @@
       <c r="C24" s="15" t="n">
         <v>454</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="16">
         <f>IF($C24="","",$B$41+$B$40*$B24)</f>
         <v/>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="16">
         <f>IF($D24="","",$C24-$D24)</f>
         <v/>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="17">
         <f>IF($E24="","",IF(ABS($E24)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1704,15 +1693,15 @@
       <c r="C25" s="15" t="n">
         <v>257</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="16">
         <f>IF($C25="","",$B$41+$B$40*$B25)</f>
         <v/>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="16">
         <f>IF($D25="","",$C25-$D25)</f>
         <v/>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="17">
         <f>IF($E25="","",IF(ABS($E25)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1729,15 +1718,15 @@
       <c r="C26" s="15" t="n">
         <v>544</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="16">
         <f>IF($C26="","",$B$41+$B$40*$B26)</f>
         <v/>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="16">
         <f>IF($D26="","",$C26-$D26)</f>
         <v/>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="17">
         <f>IF($E26="","",IF(ABS($E26)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1754,15 +1743,15 @@
       <c r="C27" s="15" t="n">
         <v>482</v>
       </c>
-      <c r="D27" s="20">
+      <c r="D27" s="16">
         <f>IF($C27="","",$B$41+$B$40*$B27)</f>
         <v/>
       </c>
-      <c r="E27" s="20">
+      <c r="E27" s="16">
         <f>IF($D27="","",$C27-$D27)</f>
         <v/>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="17">
         <f>IF($E27="","",IF(ABS($E27)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1779,15 +1768,15 @@
       <c r="C28" s="15" t="n">
         <v>403</v>
       </c>
-      <c r="D28" s="20">
+      <c r="D28" s="16">
         <f>IF($C28="","",$B$41+$B$40*$B28)</f>
         <v/>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="16">
         <f>IF($D28="","",$C28-$D28)</f>
         <v/>
       </c>
-      <c r="F28" s="21">
+      <c r="F28" s="17">
         <f>IF($E28="","",IF(ABS($E28)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1804,15 +1793,15 @@
       <c r="C29" s="15" t="n">
         <v>433</v>
       </c>
-      <c r="D29" s="20">
+      <c r="D29" s="16">
         <f>IF($C29="","",$B$41+$B$40*$B29)</f>
         <v/>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="16">
         <f>IF($D29="","",$C29-$D29)</f>
         <v/>
       </c>
-      <c r="F29" s="21">
+      <c r="F29" s="17">
         <f>IF($E29="","",IF(ABS($E29)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1829,15 +1818,15 @@
       <c r="C30" s="15" t="n">
         <v>483</v>
       </c>
-      <c r="D30" s="20">
+      <c r="D30" s="16">
         <f>IF($C30="","",$B$41+$B$40*$B30)</f>
         <v/>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="16">
         <f>IF($D30="","",$C30-$D30)</f>
         <v/>
       </c>
-      <c r="F30" s="21">
+      <c r="F30" s="17">
         <f>IF($E30="","",IF(ABS($E30)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1854,15 +1843,15 @@
       <c r="C31" s="15" t="n">
         <v>261</v>
       </c>
-      <c r="D31" s="20">
+      <c r="D31" s="16">
         <f>IF($C31="","",$B$41+$B$40*$B31)</f>
         <v/>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="16">
         <f>IF($D31="","",$C31-$D31)</f>
         <v/>
       </c>
-      <c r="F31" s="21">
+      <c r="F31" s="17">
         <f>IF($E31="","",IF(ABS($E31)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1879,15 +1868,15 @@
       <c r="C32" s="15" t="n">
         <v>424</v>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="16">
         <f>IF($C32="","",$B$41+$B$40*$B32)</f>
         <v/>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="16">
         <f>IF($D32="","",$C32-$D32)</f>
         <v/>
       </c>
-      <c r="F32" s="21">
+      <c r="F32" s="17">
         <f>IF($E32="","",IF(ABS($E32)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1904,15 +1893,15 @@
       <c r="C33" s="15" t="n">
         <v>359</v>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="16">
         <f>IF($C33="","",$B$41+$B$40*$B33)</f>
         <v/>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="16">
         <f>IF($D33="","",$C33-$D33)</f>
         <v/>
       </c>
-      <c r="F33" s="21">
+      <c r="F33" s="17">
         <f>IF($E33="","",IF(ABS($E33)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1929,15 +1918,15 @@
       <c r="C34" s="15" t="n">
         <v>505</v>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="16">
         <f>IF($C34="","",$B$41+$B$40*$B34)</f>
         <v/>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="16">
         <f>IF($D34="","",$C34-$D34)</f>
         <v/>
       </c>
-      <c r="F34" s="21">
+      <c r="F34" s="17">
         <f>IF($E34="","",IF(ABS($E34)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
@@ -1988,7 +1977,7 @@
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B39" s="22">
+      <c r="B39" s="20">
         <f>COUNT($C$11:$C$34)</f>
         <v/>
       </c>
@@ -2004,7 +1993,7 @@
           <t>Slope — seconds per extra transfer</t>
         </is>
       </c>
-      <c r="B40" s="23">
+      <c r="B40" s="21">
         <f>SLOPE($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2020,7 +2009,7 @@
           <t>Intercept — seconds at zero transfers</t>
         </is>
       </c>
-      <c r="B41" s="23">
+      <c r="B41" s="21">
         <f>INTERCEPT($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2036,7 +2025,7 @@
           <t>R² — share of the spread the line explains</t>
         </is>
       </c>
-      <c r="B42" s="24">
+      <c r="B42" s="22">
         <f>RSQ($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2052,7 +2041,7 @@
           <t>Correlation r</t>
         </is>
       </c>
-      <c r="B43" s="25">
+      <c r="B43" s="23">
         <f>CORREL($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2068,7 +2057,7 @@
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B44" s="23">
+      <c r="B44" s="21">
         <f>STEYX($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2084,7 +2073,7 @@
           <t>Standard error of the slope</t>
         </is>
       </c>
-      <c r="B45" s="23">
+      <c r="B45" s="21">
         <f>INDEX(LINEST($C$11:$C$34,$B$11:$B$34,TRUE,TRUE),2,1)</f>
         <v/>
       </c>
@@ -2100,7 +2089,7 @@
           <t>t-stat for the slope</t>
         </is>
       </c>
-      <c r="B46" s="23">
+      <c r="B46" s="21">
         <f>IFERROR($B$40/$B$45,"")</f>
         <v/>
       </c>
@@ -2116,7 +2105,7 @@
           <t>Degrees of freedom</t>
         </is>
       </c>
-      <c r="B47" s="22">
+      <c r="B47" s="20">
         <f>IFERROR(COUNT($C$11:$C$34)-2,"")</f>
         <v/>
       </c>
@@ -2132,7 +2121,7 @@
           <t>p-value for the slope</t>
         </is>
       </c>
-      <c r="B48" s="26">
+      <c r="B48" s="24">
         <f>IFERROR(TDIST(ABS($B$46),$B$47,2),"")</f>
         <v/>
       </c>
@@ -2156,13 +2145,13 @@
       <c r="F50" s="7" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="27">
+      <c r="A51" s="25">
         <f>"Handle time in seconds  =  "&amp;TEXT($B$41,"0.0")&amp;"  +  "&amp;TEXT($B$40,"0.0")&amp;" × transfers.      One more transfer is worth about "&amp;TEXT($B$40,"0")&amp;" seconds, and this one driver explains "&amp;TEXT($B$42,"0%")&amp;" of the spread in handle time "&amp;"(p = "&amp;TEXT($B$48,"0.000")&amp;", n = "&amp;TEXT($B$39,"0")&amp;")."</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="27">
+      <c r="A52" s="25">
         <f>IF($B$48="","",IF($B$48&gt;=0.05,"NOT PROVEN — at this sample size the slope is not distinguishable from a flat line. Collect more rows before you build anything on it.",IF($B$42&lt;0.3,"REAL BUT PARTIAL — the slope is significant (p = "&amp;TEXT($B$48,"0.000")&amp;") and the line still explains only "&amp;TEXT($B$42,"0%")&amp;" of the spread. Transfers are a genuine driver AND most of what moves handle time is not in this model.","REAL AND STRONG — significant, and the line explains "&amp;TEXT($B$42,"0%")&amp;" of the spread. Rare in support data; check the sample before you celebrate.")))</f>
         <v/>
       </c>
@@ -2350,7 +2339,7 @@
           <t>Smallest effect worth acting on (seconds)</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="26" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -2548,11 +2537,11 @@
       <c r="F12" s="15" t="n">
         <v>506</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="16">
         <f>IF($F12="","",$B$40+$B$41*$B12+$B$42*$C12+$B$43*$D12+$B$44*$E12)</f>
         <v/>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="16">
         <f>IF($G12="","",$F12-$G12)</f>
         <v/>
       </c>
@@ -2633,11 +2622,11 @@
       <c r="F13" s="15" t="n">
         <v>344</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="16">
         <f>IF($F13="","",$B$40+$B$41*$B13+$B$42*$C13+$B$43*$D13+$B$44*$E13)</f>
         <v/>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="16">
         <f>IF($G13="","",$F13-$G13)</f>
         <v/>
       </c>
@@ -2711,11 +2700,11 @@
       <c r="F14" s="15" t="n">
         <v>479</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="16">
         <f>IF($F14="","",$B$40+$B$41*$B14+$B$42*$C14+$B$43*$D14+$B$44*$E14)</f>
         <v/>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="16">
         <f>IF($G14="","",$F14-$G14)</f>
         <v/>
       </c>
@@ -2789,11 +2778,11 @@
       <c r="F15" s="15" t="n">
         <v>422</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="16">
         <f>IF($F15="","",$B$40+$B$41*$B15+$B$42*$C15+$B$43*$D15+$B$44*$E15)</f>
         <v/>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="16">
         <f>IF($G15="","",$F15-$G15)</f>
         <v/>
       </c>
@@ -2867,11 +2856,11 @@
       <c r="F16" s="15" t="n">
         <v>452</v>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="16">
         <f>IF($F16="","",$B$40+$B$41*$B16+$B$42*$C16+$B$43*$D16+$B$44*$E16)</f>
         <v/>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="16">
         <f>IF($G16="","",$F16-$G16)</f>
         <v/>
       </c>
@@ -2945,11 +2934,11 @@
       <c r="F17" s="15" t="n">
         <v>374</v>
       </c>
-      <c r="G17" s="20">
+      <c r="G17" s="16">
         <f>IF($F17="","",$B$40+$B$41*$B17+$B$42*$C17+$B$43*$D17+$B$44*$E17)</f>
         <v/>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="16">
         <f>IF($G17="","",$F17-$G17)</f>
         <v/>
       </c>
@@ -3023,11 +3012,11 @@
       <c r="F18" s="15" t="n">
         <v>451</v>
       </c>
-      <c r="G18" s="20">
+      <c r="G18" s="16">
         <f>IF($F18="","",$B$40+$B$41*$B18+$B$42*$C18+$B$43*$D18+$B$44*$E18)</f>
         <v/>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="16">
         <f>IF($G18="","",$F18-$G18)</f>
         <v/>
       </c>
@@ -3101,11 +3090,11 @@
       <c r="F19" s="15" t="n">
         <v>360</v>
       </c>
-      <c r="G19" s="20">
+      <c r="G19" s="16">
         <f>IF($F19="","",$B$40+$B$41*$B19+$B$42*$C19+$B$43*$D19+$B$44*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="16">
         <f>IF($G19="","",$F19-$G19)</f>
         <v/>
       </c>
@@ -3179,11 +3168,11 @@
       <c r="F20" s="15" t="n">
         <v>260</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="16">
         <f>IF($F20="","",$B$40+$B$41*$B20+$B$42*$C20+$B$43*$D20+$B$44*$E20)</f>
         <v/>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="16">
         <f>IF($G20="","",$F20-$G20)</f>
         <v/>
       </c>
@@ -3257,11 +3246,11 @@
       <c r="F21" s="15" t="n">
         <v>415</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="16">
         <f>IF($F21="","",$B$40+$B$41*$B21+$B$42*$C21+$B$43*$D21+$B$44*$E21)</f>
         <v/>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="16">
         <f>IF($G21="","",$F21-$G21)</f>
         <v/>
       </c>
@@ -3335,11 +3324,11 @@
       <c r="F22" s="15" t="n">
         <v>555</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="16">
         <f>IF($F22="","",$B$40+$B$41*$B22+$B$42*$C22+$B$43*$D22+$B$44*$E22)</f>
         <v/>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="16">
         <f>IF($G22="","",$F22-$G22)</f>
         <v/>
       </c>
@@ -3413,11 +3402,11 @@
       <c r="F23" s="15" t="n">
         <v>393</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="16">
         <f>IF($F23="","",$B$40+$B$41*$B23+$B$42*$C23+$B$43*$D23+$B$44*$E23)</f>
         <v/>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="16">
         <f>IF($G23="","",$F23-$G23)</f>
         <v/>
       </c>
@@ -3491,11 +3480,11 @@
       <c r="F24" s="15" t="n">
         <v>454</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="16">
         <f>IF($F24="","",$B$40+$B$41*$B24+$B$42*$C24+$B$43*$D24+$B$44*$E24)</f>
         <v/>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="16">
         <f>IF($G24="","",$F24-$G24)</f>
         <v/>
       </c>
@@ -3569,11 +3558,11 @@
       <c r="F25" s="15" t="n">
         <v>257</v>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="16">
         <f>IF($F25="","",$B$40+$B$41*$B25+$B$42*$C25+$B$43*$D25+$B$44*$E25)</f>
         <v/>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="16">
         <f>IF($G25="","",$F25-$G25)</f>
         <v/>
       </c>
@@ -3647,11 +3636,11 @@
       <c r="F26" s="15" t="n">
         <v>544</v>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="16">
         <f>IF($F26="","",$B$40+$B$41*$B26+$B$42*$C26+$B$43*$D26+$B$44*$E26)</f>
         <v/>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="16">
         <f>IF($G26="","",$F26-$G26)</f>
         <v/>
       </c>
@@ -3725,11 +3714,11 @@
       <c r="F27" s="15" t="n">
         <v>482</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="16">
         <f>IF($F27="","",$B$40+$B$41*$B27+$B$42*$C27+$B$43*$D27+$B$44*$E27)</f>
         <v/>
       </c>
-      <c r="H27" s="20">
+      <c r="H27" s="16">
         <f>IF($G27="","",$F27-$G27)</f>
         <v/>
       </c>
@@ -3803,11 +3792,11 @@
       <c r="F28" s="15" t="n">
         <v>403</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="16">
         <f>IF($F28="","",$B$40+$B$41*$B28+$B$42*$C28+$B$43*$D28+$B$44*$E28)</f>
         <v/>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="16">
         <f>IF($G28="","",$F28-$G28)</f>
         <v/>
       </c>
@@ -3881,11 +3870,11 @@
       <c r="F29" s="15" t="n">
         <v>433</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="16">
         <f>IF($F29="","",$B$40+$B$41*$B29+$B$42*$C29+$B$43*$D29+$B$44*$E29)</f>
         <v/>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="16">
         <f>IF($G29="","",$F29-$G29)</f>
         <v/>
       </c>
@@ -3959,11 +3948,11 @@
       <c r="F30" s="15" t="n">
         <v>483</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="16">
         <f>IF($F30="","",$B$40+$B$41*$B30+$B$42*$C30+$B$43*$D30+$B$44*$E30)</f>
         <v/>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="16">
         <f>IF($G30="","",$F30-$G30)</f>
         <v/>
       </c>
@@ -4037,11 +4026,11 @@
       <c r="F31" s="15" t="n">
         <v>261</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="16">
         <f>IF($F31="","",$B$40+$B$41*$B31+$B$42*$C31+$B$43*$D31+$B$44*$E31)</f>
         <v/>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="16">
         <f>IF($G31="","",$F31-$G31)</f>
         <v/>
       </c>
@@ -4115,11 +4104,11 @@
       <c r="F32" s="15" t="n">
         <v>424</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="16">
         <f>IF($F32="","",$B$40+$B$41*$B32+$B$42*$C32+$B$43*$D32+$B$44*$E32)</f>
         <v/>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="16">
         <f>IF($G32="","",$F32-$G32)</f>
         <v/>
       </c>
@@ -4193,11 +4182,11 @@
       <c r="F33" s="15" t="n">
         <v>359</v>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="16">
         <f>IF($F33="","",$B$40+$B$41*$B33+$B$42*$C33+$B$43*$D33+$B$44*$E33)</f>
         <v/>
       </c>
-      <c r="H33" s="20">
+      <c r="H33" s="16">
         <f>IF($G33="","",$F33-$G33)</f>
         <v/>
       </c>
@@ -4271,11 +4260,11 @@
       <c r="F34" s="15" t="n">
         <v>505</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="16">
         <f>IF($F34="","",$B$40+$B$41*$B34+$B$42*$C34+$B$43*$D34+$B$44*$E34)</f>
         <v/>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="16">
         <f>IF($G34="","",$F34-$G34)</f>
         <v/>
       </c>
@@ -4400,184 +4389,184 @@
       </c>
     </row>
     <row r="40" ht="84" customHeight="1">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="28">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,5),"")</f>
         <v/>
       </c>
-      <c r="C40" s="30">
+      <c r="C40" s="28">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,5),"")</f>
         <v/>
       </c>
-      <c r="D40" s="30">
+      <c r="D40" s="28">
         <f>IFERROR($B40/$C40,"")</f>
         <v/>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="29">
         <f>IFERROR(TDIST(ABS($D40),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="I40" s="32">
+      <c r="I40" s="30">
         <f>IF($B40="","","Predicted handle time for a contact with every driver at zero — before 17:00, under the limit, a brand-new agent, no transfers. Read it as the starting point the four effects are added to, not as a prediction.")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="28">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,4),"")</f>
         <v/>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="28">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,4),"")</f>
         <v/>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="28">
         <f>IFERROR($B41/$C41,"")</f>
         <v/>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="29">
         <f>IFERROR(TDIST(ABS($D41),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="28">
         <f>IFERROR(1/(1-INDEX(LINEST($B$11:$B$34,$J$11:$L$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="31">
         <f>IFERROR($B41*(MAX($B$11:$B$34)-MIN($B$11:$B$34)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="27">
+      <c r="H41" s="25">
         <f>IF($E41="","",IF($E41&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G41)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="30">
         <f>IF($B41="","","Seconds the after-17:00 flag adds once the other three are held still. Compare it with the p-value beside it before you repeat it out loud.")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="28">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,3),"")</f>
         <v/>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="28">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,3),"")</f>
         <v/>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="28">
         <f>IFERROR($B42/$C42,"")</f>
         <v/>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="29">
         <f>IFERROR(TDIST(ABS($D42),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="28">
         <f>IFERROR(1/(1-INDEX(LINEST($C$11:$C$34,$M$11:$O$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="31">
         <f>IFERROR($B42*(MAX($C$11:$C$34)-MIN($C$11:$C$34)),"")</f>
         <v/>
       </c>
-      <c r="H42" s="27">
+      <c r="H42" s="25">
         <f>IF($E42="","",IF($E42&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G42)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="30">
         <f>IF($B42="","","Seconds the $50 authority limit adds once the other three are held still. This is the queue, not the money.")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B43" s="30">
+      <c r="B43" s="28">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,2),"")</f>
         <v/>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="28">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,2),"")</f>
         <v/>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="28">
         <f>IFERROR($B43/$C43,"")</f>
         <v/>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="29">
         <f>IFERROR(TDIST(ABS($D43),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="28">
         <f>IFERROR(1/(1-INDEX(LINEST($D$11:$D$34,$P$11:$R$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="33">
+      <c r="G43" s="31">
         <f>IFERROR($B43*(MAX($D$11:$D$34)-MIN($D$11:$D$34)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="27">
+      <c r="H43" s="25">
         <f>IF($E43="","",IF($E43&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G43)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I43" s="32">
+      <c r="I43" s="30">
         <f>IF($B43="","","Seconds per extra month of tenure — negative means longer-serving agents are quicker. Small per month, so read the range column, not this one.")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B44" s="30">
+      <c r="B44" s="28">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,1),"")</f>
         <v/>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="28">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,1),"")</f>
         <v/>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="28">
         <f>IFERROR($B44/$C44,"")</f>
         <v/>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="29">
         <f>IFERROR(TDIST(ABS($D44),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F44" s="30">
+      <c r="F44" s="28">
         <f>IFERROR(1/(1-INDEX(LINEST($E$11:$E$34,$S$11:$U$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="31">
         <f>IFERROR($B44*(MAX($E$11:$E$34)-MIN($E$11:$E$34)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="27">
+      <c r="H44" s="25">
         <f>IF($E44="","",IF($E44&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G44)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="30">
         <f>IF($B44="","","Seconds each extra transfer adds once the other three are held still. Compare it with the 50.7 seconds the single-driver tab gave you.")</f>
         <v/>
       </c>
@@ -4634,7 +4623,7 @@
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B49" s="22">
+      <c r="B49" s="20">
         <f>COUNT($F$11:$F$34)</f>
         <v/>
       </c>
@@ -4650,7 +4639,7 @@
           <t>Predictors (k)</t>
         </is>
       </c>
-      <c r="B50" s="22">
+      <c r="B50" s="20">
         <f>4</f>
         <v/>
       </c>
@@ -4666,7 +4655,7 @@
           <t>R²</t>
         </is>
       </c>
-      <c r="B51" s="24">
+      <c r="B51" s="22">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,1),"")</f>
         <v/>
       </c>
@@ -4682,7 +4671,7 @@
           <t>Adjusted R²</t>
         </is>
       </c>
-      <c r="B52" s="24">
+      <c r="B52" s="22">
         <f>IFERROR(1-(1-$B$51)*($B$49-1)/($B$49-$B$50-1),"")</f>
         <v/>
       </c>
@@ -4698,7 +4687,7 @@
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B53" s="23">
+      <c r="B53" s="21">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,2),"")</f>
         <v/>
       </c>
@@ -4714,7 +4703,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="B54" s="23">
+      <c r="B54" s="21">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,1),"")</f>
         <v/>
       </c>
@@ -4730,7 +4719,7 @@
           <t>Degrees of freedom (residual)</t>
         </is>
       </c>
-      <c r="B55" s="22">
+      <c r="B55" s="20">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,2),"")</f>
         <v/>
       </c>
@@ -4746,7 +4735,7 @@
           <t>p-value for F</t>
         </is>
       </c>
-      <c r="B56" s="26">
+      <c r="B56" s="24">
         <f>IFERROR(FDIST($B$54,$B$50,$B$55),"")</f>
         <v/>
       </c>
@@ -4762,7 +4751,7 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B57" s="21">
+      <c r="B57" s="17">
         <f>IF($B$56="","",IF($B$56&gt;=0.05,"NO MODEL — these four together explain nothing",IF($B$52&lt;0.3,"USABLE BUT WEAK — read the effect sizes, not the R²","USABLE — now go and look at the residual chart")))</f>
         <v/>
       </c>
@@ -4990,171 +4979,171 @@
       <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n">
+      <c r="B10" s="32" t="n">
         <v>-3.05</v>
       </c>
-      <c r="C10" s="34" t="n">
+      <c r="C10" s="32" t="n">
         <v>0.24</v>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="34">
         <f>IFERROR(EXP($B10),"")</f>
         <v/>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="34">
         <f>IFERROR(EXP($B10-1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="34">
         <f>IFERROR(EXP($B10+1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="H10" s="37">
+      <c r="H10" s="30">
         <f>"Baseline odds of a reopen with every driver at zero: "&amp;TEXT($E10,"0.000")&amp;" to 1, which is "&amp;TEXT($E10/(1+$E10),"0.0%")&amp;" probability."</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="32" t="n">
         <v>1.16</v>
       </c>
-      <c r="C11" s="34" t="n">
+      <c r="C11" s="32" t="n">
         <v>0.21</v>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="34">
         <f>IFERROR(EXP($B11),"")</f>
         <v/>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="34">
         <f>IFERROR(EXP($B11-1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="34">
         <f>IFERROR(EXP($B11+1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="30">
         <f>"Raising the adjustment after 17:00 multiplies the odds of a reopen by "&amp;TEXT($E11,"0.00")&amp;". This is the posting-batch effect, and it is the largest single driver in the model."</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B12" s="34" t="n">
+      <c r="B12" s="32" t="n">
         <v>0.83</v>
       </c>
-      <c r="C12" s="34" t="n">
+      <c r="C12" s="32" t="n">
         <v>0.22</v>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>0.0002</t>
         </is>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="34">
         <f>IFERROR(EXP($B12),"")</f>
         <v/>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="34">
         <f>IFERROR(EXP($B12-1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="G12" s="38">
+      <c r="G12" s="34">
         <f>IFERROR(EXP($B12+1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="30">
         <f>"Clearing the $50 authority limit multiplies the odds of a reopen by "&amp;TEXT($E12,"0.00")&amp;", because the case waits in a queue for approval."</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="84" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B13" s="34" t="n">
+      <c r="B13" s="32" t="n">
         <v>-0.038</v>
       </c>
-      <c r="C13" s="34" t="n">
+      <c r="C13" s="32" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="34">
         <f>IFERROR(EXP($B13),"")</f>
         <v/>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="34">
         <f>IFERROR(EXP($B13-1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="34">
         <f>IFERROR(EXP($B13+1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="30">
         <f>"Each extra month of tenure multiplies the odds by "&amp;TEXT($E13,"0.000")&amp;" — so a 24-month agent runs at "&amp;TEXT($E13^24,"0.00")&amp;" times the odds of a first-week agent."</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n">
+      <c r="B14" s="32" t="n">
         <v>0.61</v>
       </c>
-      <c r="C14" s="34" t="n">
+      <c r="C14" s="32" t="n">
         <v>0.12</v>
       </c>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="34">
         <f>IFERROR(EXP($B14),"")</f>
         <v/>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="34">
         <f>IFERROR(EXP($B14-1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="34">
         <f>IFERROR(EXP($B14+1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="30">
         <f>"Each extra transfer multiplies the odds of a reopen by "&amp;TEXT($E14,"0.00")&amp;". Multiply by how common transfers are before you rank it against the others."</f>
         <v/>
       </c>
@@ -5250,15 +5239,15 @@
       <c r="F19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="39">
+      <c r="G19" s="23">
         <f>IF($B19="","",$B$10+$B$11*$B19+$B$12*$C19+$B$13*$D19+$B$14*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="22">
         <f>IFERROR(1/(1+EXP(-$G19)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="20">
         <f>IF($H19="","",IF($H19&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5284,15 +5273,15 @@
       <c r="F20" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="23">
         <f>IF($B20="","",$B$10+$B$11*$B20+$B$12*$C20+$B$13*$D20+$B$14*$E20)</f>
         <v/>
       </c>
-      <c r="H20" s="24">
+      <c r="H20" s="22">
         <f>IFERROR(1/(1+EXP(-$G20)),"")</f>
         <v/>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="20">
         <f>IF($H20="","",IF($H20&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5318,15 +5307,15 @@
       <c r="F21" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="23">
         <f>IF($B21="","",$B$10+$B$11*$B21+$B$12*$C21+$B$13*$D21+$B$14*$E21)</f>
         <v/>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="22">
         <f>IFERROR(1/(1+EXP(-$G21)),"")</f>
         <v/>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="20">
         <f>IF($H21="","",IF($H21&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5352,15 +5341,15 @@
       <c r="F22" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="23">
         <f>IF($B22="","",$B$10+$B$11*$B22+$B$12*$C22+$B$13*$D22+$B$14*$E22)</f>
         <v/>
       </c>
-      <c r="H22" s="24">
+      <c r="H22" s="22">
         <f>IFERROR(1/(1+EXP(-$G22)),"")</f>
         <v/>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="20">
         <f>IF($H22="","",IF($H22&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5386,15 +5375,15 @@
       <c r="F23" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="23">
         <f>IF($B23="","",$B$10+$B$11*$B23+$B$12*$C23+$B$13*$D23+$B$14*$E23)</f>
         <v/>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="22">
         <f>IFERROR(1/(1+EXP(-$G23)),"")</f>
         <v/>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="20">
         <f>IF($H23="","",IF($H23&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5420,15 +5409,15 @@
       <c r="F24" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="23">
         <f>IF($B24="","",$B$10+$B$11*$B24+$B$12*$C24+$B$13*$D24+$B$14*$E24)</f>
         <v/>
       </c>
-      <c r="H24" s="24">
+      <c r="H24" s="22">
         <f>IFERROR(1/(1+EXP(-$G24)),"")</f>
         <v/>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="20">
         <f>IF($H24="","",IF($H24&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5454,15 +5443,15 @@
       <c r="F25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="23">
         <f>IF($B25="","",$B$10+$B$11*$B25+$B$12*$C25+$B$13*$D25+$B$14*$E25)</f>
         <v/>
       </c>
-      <c r="H25" s="24">
+      <c r="H25" s="22">
         <f>IFERROR(1/(1+EXP(-$G25)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="20">
         <f>IF($H25="","",IF($H25&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5488,15 +5477,15 @@
       <c r="F26" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="23">
         <f>IF($B26="","",$B$10+$B$11*$B26+$B$12*$C26+$B$13*$D26+$B$14*$E26)</f>
         <v/>
       </c>
-      <c r="H26" s="24">
+      <c r="H26" s="22">
         <f>IFERROR(1/(1+EXP(-$G26)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="22">
+      <c r="I26" s="20">
         <f>IF($H26="","",IF($H26&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5522,15 +5511,15 @@
       <c r="F27" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="25">
+      <c r="G27" s="23">
         <f>IF($B27="","",$B$10+$B$11*$B27+$B$12*$C27+$B$13*$D27+$B$14*$E27)</f>
         <v/>
       </c>
-      <c r="H27" s="24">
+      <c r="H27" s="22">
         <f>IFERROR(1/(1+EXP(-$G27)),"")</f>
         <v/>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="20">
         <f>IF($H27="","",IF($H27&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5556,15 +5545,15 @@
       <c r="F28" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="23">
         <f>IF($B28="","",$B$10+$B$11*$B28+$B$12*$C28+$B$13*$D28+$B$14*$E28)</f>
         <v/>
       </c>
-      <c r="H28" s="24">
+      <c r="H28" s="22">
         <f>IFERROR(1/(1+EXP(-$G28)),"")</f>
         <v/>
       </c>
-      <c r="I28" s="22">
+      <c r="I28" s="20">
         <f>IF($H28="","",IF($H28&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5590,15 +5579,15 @@
       <c r="F29" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="25">
+      <c r="G29" s="23">
         <f>IF($B29="","",$B$10+$B$11*$B29+$B$12*$C29+$B$13*$D29+$B$14*$E29)</f>
         <v/>
       </c>
-      <c r="H29" s="24">
+      <c r="H29" s="22">
         <f>IFERROR(1/(1+EXP(-$G29)),"")</f>
         <v/>
       </c>
-      <c r="I29" s="22">
+      <c r="I29" s="20">
         <f>IF($H29="","",IF($H29&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5624,15 +5613,15 @@
       <c r="F30" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="23">
         <f>IF($B30="","",$B$10+$B$11*$B30+$B$12*$C30+$B$13*$D30+$B$14*$E30)</f>
         <v/>
       </c>
-      <c r="H30" s="24">
+      <c r="H30" s="22">
         <f>IFERROR(1/(1+EXP(-$G30)),"")</f>
         <v/>
       </c>
-      <c r="I30" s="22">
+      <c r="I30" s="20">
         <f>IF($H30="","",IF($H30&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5658,15 +5647,15 @@
       <c r="F31" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="25">
+      <c r="G31" s="23">
         <f>IF($B31="","",$B$10+$B$11*$B31+$B$12*$C31+$B$13*$D31+$B$14*$E31)</f>
         <v/>
       </c>
-      <c r="H31" s="24">
+      <c r="H31" s="22">
         <f>IFERROR(1/(1+EXP(-$G31)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="20">
         <f>IF($H31="","",IF($H31&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5692,15 +5681,15 @@
       <c r="F32" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="23">
         <f>IF($B32="","",$B$10+$B$11*$B32+$B$12*$C32+$B$13*$D32+$B$14*$E32)</f>
         <v/>
       </c>
-      <c r="H32" s="24">
+      <c r="H32" s="22">
         <f>IFERROR(1/(1+EXP(-$G32)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="22">
+      <c r="I32" s="20">
         <f>IF($H32="","",IF($H32&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5726,15 +5715,15 @@
       <c r="F33" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="23">
         <f>IF($B33="","",$B$10+$B$11*$B33+$B$12*$C33+$B$13*$D33+$B$14*$E33)</f>
         <v/>
       </c>
-      <c r="H33" s="24">
+      <c r="H33" s="22">
         <f>IFERROR(1/(1+EXP(-$G33)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="22">
+      <c r="I33" s="20">
         <f>IF($H33="","",IF($H33&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5760,15 +5749,15 @@
       <c r="F34" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="23">
         <f>IF($B34="","",$B$10+$B$11*$B34+$B$12*$C34+$B$13*$D34+$B$14*$E34)</f>
         <v/>
       </c>
-      <c r="H34" s="24">
+      <c r="H34" s="22">
         <f>IFERROR(1/(1+EXP(-$G34)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="22">
+      <c r="I34" s="20">
         <f>IF($H34="","",IF($H34&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5794,15 +5783,15 @@
       <c r="F35" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="23">
         <f>IF($B35="","",$B$10+$B$11*$B35+$B$12*$C35+$B$13*$D35+$B$14*$E35)</f>
         <v/>
       </c>
-      <c r="H35" s="24">
+      <c r="H35" s="22">
         <f>IFERROR(1/(1+EXP(-$G35)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="22">
+      <c r="I35" s="20">
         <f>IF($H35="","",IF($H35&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5828,15 +5817,15 @@
       <c r="F36" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="23">
         <f>IF($B36="","",$B$10+$B$11*$B36+$B$12*$C36+$B$13*$D36+$B$14*$E36)</f>
         <v/>
       </c>
-      <c r="H36" s="24">
+      <c r="H36" s="22">
         <f>IFERROR(1/(1+EXP(-$G36)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="22">
+      <c r="I36" s="20">
         <f>IF($H36="","",IF($H36&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5862,15 +5851,15 @@
       <c r="F37" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="25">
+      <c r="G37" s="23">
         <f>IF($B37="","",$B$10+$B$11*$B37+$B$12*$C37+$B$13*$D37+$B$14*$E37)</f>
         <v/>
       </c>
-      <c r="H37" s="24">
+      <c r="H37" s="22">
         <f>IFERROR(1/(1+EXP(-$G37)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="22">
+      <c r="I37" s="20">
         <f>IF($H37="","",IF($H37&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5896,15 +5885,15 @@
       <c r="F38" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="25">
+      <c r="G38" s="23">
         <f>IF($B38="","",$B$10+$B$11*$B38+$B$12*$C38+$B$13*$D38+$B$14*$E38)</f>
         <v/>
       </c>
-      <c r="H38" s="24">
+      <c r="H38" s="22">
         <f>IFERROR(1/(1+EXP(-$G38)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="22">
+      <c r="I38" s="20">
         <f>IF($H38="","",IF($H38&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5930,15 +5919,15 @@
       <c r="F39" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="23">
         <f>IF($B39="","",$B$10+$B$11*$B39+$B$12*$C39+$B$13*$D39+$B$14*$E39)</f>
         <v/>
       </c>
-      <c r="H39" s="24">
+      <c r="H39" s="22">
         <f>IFERROR(1/(1+EXP(-$G39)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="22">
+      <c r="I39" s="20">
         <f>IF($H39="","",IF($H39&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5964,15 +5953,15 @@
       <c r="F40" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="25">
+      <c r="G40" s="23">
         <f>IF($B40="","",$B$10+$B$11*$B40+$B$12*$C40+$B$13*$D40+$B$14*$E40)</f>
         <v/>
       </c>
-      <c r="H40" s="24">
+      <c r="H40" s="22">
         <f>IFERROR(1/(1+EXP(-$G40)),"")</f>
         <v/>
       </c>
-      <c r="I40" s="22">
+      <c r="I40" s="20">
         <f>IF($H40="","",IF($H40&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5998,15 +5987,15 @@
       <c r="F41" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="25">
+      <c r="G41" s="23">
         <f>IF($B41="","",$B$10+$B$11*$B41+$B$12*$C41+$B$13*$D41+$B$14*$E41)</f>
         <v/>
       </c>
-      <c r="H41" s="24">
+      <c r="H41" s="22">
         <f>IFERROR(1/(1+EXP(-$G41)),"")</f>
         <v/>
       </c>
-      <c r="I41" s="22">
+      <c r="I41" s="20">
         <f>IF($H41="","",IF($H41&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -6032,15 +6021,15 @@
       <c r="F42" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="25">
+      <c r="G42" s="23">
         <f>IF($B42="","",$B$10+$B$11*$B42+$B$12*$C42+$B$13*$D42+$B$14*$E42)</f>
         <v/>
       </c>
-      <c r="H42" s="24">
+      <c r="H42" s="22">
         <f>IFERROR(1/(1+EXP(-$G42)),"")</f>
         <v/>
       </c>
-      <c r="I42" s="22">
+      <c r="I42" s="20">
         <f>IF($H42="","",IF($H42&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -6074,7 +6063,7 @@
           <t>Flag a contact at this probability or above</t>
         </is>
       </c>
-      <c r="B46" s="42" t="n">
+      <c r="B46" s="35" t="n">
         <v>0.2</v>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -6089,7 +6078,7 @@
           <t>AUC the tool reported</t>
         </is>
       </c>
-      <c r="B47" s="43" t="n">
+      <c r="B47" s="36" t="n">
         <v>0.74</v>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -6147,15 +6136,15 @@
           <t>Flagged — predicted reopen</t>
         </is>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="16">
         <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=1))</f>
         <v/>
       </c>
-      <c r="C51" s="20">
+      <c r="C51" s="16">
         <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=0))</f>
         <v/>
       </c>
-      <c r="D51" s="20">
+      <c r="D51" s="16">
         <f>SUM($B51:$C51)</f>
         <v/>
       </c>
@@ -6166,15 +6155,15 @@
           <t>Not flagged</t>
         </is>
       </c>
-      <c r="B52" s="20">
+      <c r="B52" s="16">
         <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=1))</f>
         <v/>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="16">
         <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=0))</f>
         <v/>
       </c>
-      <c r="D52" s="20">
+      <c r="D52" s="16">
         <f>SUM($B52:$C52)</f>
         <v/>
       </c>
@@ -6185,15 +6174,15 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="16">
         <f>SUM($B$51:$B$52)</f>
         <v/>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="16">
         <f>SUM($C$51:$C$52)</f>
         <v/>
       </c>
-      <c r="D53" s="20">
+      <c r="D53" s="16">
         <f>SUM($D$51:$D$52)</f>
         <v/>
       </c>
@@ -6250,7 +6239,7 @@
           <t>Sensitivity — reopens you caught</t>
         </is>
       </c>
-      <c r="B58" s="24">
+      <c r="B58" s="22">
         <f>IFERROR($B$51/($B$51+$B$52),"")</f>
         <v/>
       </c>
@@ -6266,7 +6255,7 @@
           <t>Specificity — quiet contacts left alone</t>
         </is>
       </c>
-      <c r="B59" s="24">
+      <c r="B59" s="22">
         <f>IFERROR($C$52/($C$52+$C$51),"")</f>
         <v/>
       </c>
@@ -6282,7 +6271,7 @@
           <t>Precision — flags that were right</t>
         </is>
       </c>
-      <c r="B60" s="24">
+      <c r="B60" s="22">
         <f>IFERROR($B$51/($B$51+$C$51),"")</f>
         <v/>
       </c>
@@ -6298,7 +6287,7 @@
           <t>Accuracy — rows called correctly</t>
         </is>
       </c>
-      <c r="B61" s="24">
+      <c r="B61" s="22">
         <f>IFERROR(($B$51+$C$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
         <v/>
       </c>
@@ -6314,7 +6303,7 @@
           <t>Base rate — share that actually reopened</t>
         </is>
       </c>
-      <c r="B62" s="24">
+      <c r="B62" s="22">
         <f>IFERROR(($B$51+$B$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
         <v/>
       </c>
@@ -6330,7 +6319,7 @@
           <t>Verdict at this threshold</t>
         </is>
       </c>
-      <c r="B63" s="21">
+      <c r="B63" s="17">
         <f>IF($B$51+$B$52=0,"NO REOPENS IN THE SAMPLE",IF($B$51/($B$51+$B$52)&lt;0.5,"MISSES MORE THAN HALF — lower the threshold",IF($B$51/($B$51+$C$51)&lt;0.2,"TOO MANY FALSE ALARMS — raise the threshold","USABLE FOR TARGETING — check it against the cost of a flag")))</f>
         <v/>
       </c>

--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -1157,6 +1157,9 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B9"/>
+  </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Transfers per contact</t>
+          <t>Transfers before resolution</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
@@ -1269,10 +1269,10 @@
       </c>
     </row>
     <row r="8"/>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>THE DATA — one row per contact, x beside y  ·  Key: Fitted y = what the model predicts for that row, before you compare it with what actually happened · Residual = what the model missed on that row: the value that actually happened minus the fitted one</t>
+          <t>THE DATA — one row per contact. First the two columns you measured: x, the driver you are testing, then y, the outcome. Then three the sheet works out for you. Contact ref is the case number and the time of day it was raised  ·  Key: Fitted y = what the model predicts for that row, before you compare it with what actually happened · Residual = what the model missed on that row: the value that actually happened minus the fitted one</t>
         </is>
       </c>
       <c r="B9" s="7" t="n"/>
@@ -1284,32 +1284,32 @@
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Contact ref</t>
+          <t>Contact ref · time raised</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Transfers before resolution (x)</t>
+          <t>x — transfers before resolution</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Handle time in seconds (y)</t>
+          <t>y — handle time, seconds (measured)</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Fitted y — what the line predicts</t>
+          <t>Fitted y — seconds the line predicts for that x</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Residual (y − fitted)</t>
+          <t>Residual — seconds the line missed by (y − fitted)</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Off the line by more than 1.5 standard errors?</t>
+          <t>Unusual? residual larger than 1.5 standard errors</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -2352,10 +2352,10 @@
       </c>
     </row>
     <row r="8"/>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>THE DATA — the same 24 contacts, with all four drivers beside y  ·  Key: Fitted y = what the model predicts for that row, before you compare it with what actually happened · Residual = what the model missed on that row: the value that actually happened minus the fitted one</t>
+          <t>THE DATA — the same 24 contacts, with all four drivers beside y. Contact ref is the case number and the time of day it was raised, which is where the 17:00 column comes from  ·  Key: Fitted y = what the model predicts for that row, before you compare it with what actually happened · Residual = what the model missed on that row: the value that actually happened minus the fitted one</t>
         </is>
       </c>
       <c r="B9" s="7" t="n"/>
@@ -5159,10 +5159,10 @@
       </c>
     </row>
     <row r="16"/>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>STEP 2 — the same 24 contacts, scored with those coefficients  ·  Key: Logit = the log-odds the model works in, before it is turned back into a probability · Predicted probability = the model's chance that this particular row ends in the outcome</t>
+          <t>STEP 2 — the same 24 contacts, scored with those coefficients. Contact ref is the case number and the time of day it was raised, which is where the 17:00 column comes from. The last two columns are the model's working: the logit it computes, then the same thing as a probability  ·  Key: Logit = the log-odds the model works in, before it is turned back into a probability · Predicted probability = the model's chance that this particular row ends in the outcome</t>
         </is>
       </c>
       <c r="B17" s="7" t="n"/>

--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -4329,10 +4329,10 @@
     </row>
     <row r="36"/>
     <row r="37"/>
-    <row r="38" ht="72" customHeight="1">
+    <row r="38" ht="108" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>STEP 1 — the coefficients, and which of them you can act on  ·  Key: Coefficient = how far the outcome moves for a one-unit change in that driver, with the other drivers held still · Std error = how much that number would wobble if you drew another sample the same size · t-stat = the coefficient divided by its own standard error; roughly 2 or more is the usual signal · p-value = the chance of seeing a difference this big if nothing had really changed · VIF = variance inflation factor, how much two drivers move together; under 5 is fine, over 10 means drop one</t>
+          <t>STEP 1 — the coefficients, and which of them you can act on  ·  Key: Coefficient = how far the outcome moves for a one-unit change in that driver, with the other drivers held still · Std error = how much that number would wobble if you drew another sample the same size · t-stat = the coefficient divided by its own standard error; roughly 2 or more is the usual signal · p-value = the chance of seeing a difference this big if nothing had really changed · VIF = variance inflation factor, how much two drivers move together; under 5 is fine, over 10 means drop one · Effect across the observed range = the coefficient multiplied by the full span of that driver in the data you actually have. A coefficient answers 'per one unit'; this answers 'over the range that exists', which is the size a process owner can act on. A large per-unit effect on a driver that barely varies moves nothing in practice, and only this column shows that</t>
         </is>
       </c>
       <c r="B38" s="7" t="n"/>

--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -1269,10 +1269,12 @@
       </c>
     </row>
     <row r="8"/>
-    <row r="9" ht="48" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>THE DATA — one row per contact. First the two columns you measured: x, the driver you are testing, then y, the outcome. Then three the sheet works out for you. Contact ref is the case number and the time of day it was raised  ·  Key: Fitted y = what the model predicts for that row, before you compare it with what actually happened · Residual = what the model missed on that row: the value that actually happened minus the fitted one</t>
+          <t>THE DATA — one row per contact. First the two columns you measured: x, the driver you are testing, then y, the outcome. Then three the sheet works out for you. Contact ref is the case number and the time of day it was raised  ·  Key:
+• Fitted y = what the model predicts for that row, before you compare it with what actually happened
+• Residual = what the model missed on that row: the value that actually happened minus the fitted one</t>
         </is>
       </c>
       <c r="B9" s="7" t="n"/>
@@ -2355,7 +2357,9 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>THE DATA — the same 24 contacts, with all four drivers beside y. Contact ref is the case number and the time of day it was raised, which is where the 17:00 column comes from  ·  Key: Fitted y = what the model predicts for that row, before you compare it with what actually happened · Residual = what the model missed on that row: the value that actually happened minus the fitted one</t>
+          <t>THE DATA — the same 24 contacts, with all four drivers beside y. Contact ref is the case number and the time of day it was raised, which is where the 17:00 column comes from  ·  Key:
+• Fitted y = what the model predicts for that row, before you compare it with what actually happened
+• Residual = what the model missed on that row: the value that actually happened minus the fitted one</t>
         </is>
       </c>
       <c r="B9" s="7" t="n"/>
@@ -4329,10 +4333,16 @@
     </row>
     <row r="36"/>
     <row r="37"/>
-    <row r="38" ht="108" customHeight="1">
+    <row r="38" ht="144" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>STEP 1 — the coefficients, and which of them you can act on  ·  Key: Coefficient = how far the outcome moves for a one-unit change in that driver, with the other drivers held still · Std error = how much that number would wobble if you drew another sample the same size · t-stat = the coefficient divided by its own standard error; roughly 2 or more is the usual signal · p-value = the chance of seeing a difference this big if nothing had really changed · VIF = variance inflation factor, how much two drivers move together; under 5 is fine, over 10 means drop one · Effect across the observed range = the coefficient multiplied by the full span of that driver in the data you actually have. A coefficient answers 'per one unit'; this answers 'over the range that exists', which is the size a process owner can act on. A large per-unit effect on a driver that barely varies moves nothing in practice, and only this column shows that</t>
+          <t>STEP 1 — the coefficients, and which of them you can act on  ·  Key:
+• Coefficient = how far the outcome moves for a one-unit change in that driver, with the other drivers held still
+• Std error = how much that number would wobble if you drew another sample the same size
+• t-stat = the coefficient divided by its own standard error; roughly 2 or more is the usual signal
+• p-value = the chance of seeing a difference this big if nothing had really changed
+• VIF = variance inflation factor, how much two drivers move together; under 5 is fine, over 10 means drop one
+• Effect across the observed range = the coefficient multiplied by the full span of that driver in the data you actually have. A coefficient answers 'per one unit'; this answers 'over the range that exists', which is the size a process owner can act on. A large per-unit effect on a driver that barely varies moves nothing in practice, and only this column shows that</t>
         </is>
       </c>
       <c r="B38" s="7" t="n"/>
@@ -4923,10 +4933,15 @@
       </c>
     </row>
     <row r="7"/>
-    <row r="8" ht="60" customHeight="1">
+    <row r="8" ht="84" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>STEP 1 — paste the coefficient table your tool produced  ·  Key: Coefficient = how far the outcome moves for a one-unit change in that driver, with the other drivers held still · Std error = how much that number would wobble if you drew another sample the same size · p-value = the chance of seeing a difference this big if nothing had really changed · Odds ratio = how many times the odds of the outcome multiply when that driver goes up by one · CI = confidence interval, the range the true value plausibly sits in</t>
+          <t>STEP 1 — paste the coefficient table your tool produced  ·  Key:
+• Coefficient = how far the outcome moves for a one-unit change in that driver, with the other drivers held still
+• Std error = how much that number would wobble if you drew another sample the same size
+• p-value = the chance of seeing a difference this big if nothing had really changed
+• Odds ratio = how many times the odds of the outcome multiply when that driver goes up by one
+• CI = confidence interval, the range the true value plausibly sits in</t>
         </is>
       </c>
       <c r="B8" s="7" t="n"/>
@@ -5162,7 +5177,9 @@
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>STEP 2 — the same 24 contacts, scored with those coefficients. Contact ref is the case number and the time of day it was raised, which is where the 17:00 column comes from. The last two columns are the model's working: the logit it computes, then the same thing as a probability  ·  Key: Logit = the log-odds the model works in, before it is turned back into a probability · Predicted probability = the model's chance that this particular row ends in the outcome</t>
+          <t>STEP 2 — the same 24 contacts, scored with those coefficients. Contact ref is the case number and the time of day it was raised, which is where the 17:00 column comes from. The last two columns are the model's working: the logit it computes, then the same thing as a probability  ·  Key:
+• Logit = the log-odds the model works in, before it is turned back into a probability
+• Predicted probability = the model's chance that this particular row ends in the outcome</t>
         </is>
       </c>
       <c r="B17" s="7" t="n"/>

--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,11 @@
     </font>
     <font>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -114,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -145,6 +150,9 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -650,7 +658,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>9</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -677,7 +685,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>24</col>
+      <col>26</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -1172,7 +1180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1183,6 +1191,15 @@
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1711,7 +1728,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="66" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
@@ -1734,6 +1751,12 @@
       <c r="F26" s="17">
         <f>IF($E26="","",IF(ABS($E26)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  The line is what the model claims; the vertical distance from each point to it is what it got wrong. One driver explains 26.4% of the spread here, so three quarters of it is everything not on this chart. Read the residual plot on the next tab before you quote the slope anywhere.
+SO:  Do not price a benefit off this slope. One driver explains 26.4% of the spread, so move to the multiple-regression tab and find the rest before anyone quotes seconds per transfer to Finance.</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1982,7 +2005,7 @@
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B39" s="20">
+      <c r="B39" s="21">
         <f>COUNT($C$11:$C$34)</f>
         <v/>
       </c>
@@ -1998,7 +2021,7 @@
           <t>Slope — seconds per extra transfer</t>
         </is>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="22">
         <f>SLOPE($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2014,7 +2037,7 @@
           <t>Intercept — seconds at zero transfers</t>
         </is>
       </c>
-      <c r="B41" s="21">
+      <c r="B41" s="22">
         <f>INTERCEPT($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2030,7 +2053,7 @@
           <t>R² — share of the spread the line explains</t>
         </is>
       </c>
-      <c r="B42" s="22">
+      <c r="B42" s="23">
         <f>RSQ($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2046,7 +2069,7 @@
           <t>Correlation r</t>
         </is>
       </c>
-      <c r="B43" s="23">
+      <c r="B43" s="24">
         <f>CORREL($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2062,7 +2085,7 @@
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B44" s="21">
+      <c r="B44" s="22">
         <f>STEYX($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
@@ -2078,7 +2101,7 @@
           <t>Standard error of the slope</t>
         </is>
       </c>
-      <c r="B45" s="21">
+      <c r="B45" s="22">
         <f>INDEX(LINEST($C$11:$C$34,$B$11:$B$34,TRUE,TRUE),2,1)</f>
         <v/>
       </c>
@@ -2094,7 +2117,7 @@
           <t>t-stat for the slope</t>
         </is>
       </c>
-      <c r="B46" s="21">
+      <c r="B46" s="22">
         <f>IFERROR($B$40/$B$45,"")</f>
         <v/>
       </c>
@@ -2110,7 +2133,7 @@
           <t>Degrees of freedom</t>
         </is>
       </c>
-      <c r="B47" s="20">
+      <c r="B47" s="21">
         <f>IFERROR(COUNT($C$11:$C$34)-2,"")</f>
         <v/>
       </c>
@@ -2126,7 +2149,7 @@
           <t>p-value for the slope</t>
         </is>
       </c>
-      <c r="B48" s="24">
+      <c r="B48" s="25">
         <f>IFERROR(TDIST(ABS($B$46),$B$47,2),"")</f>
         <v/>
       </c>
@@ -2150,13 +2173,13 @@
       <c r="F50" s="7" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="25">
+      <c r="A51" s="26">
         <f>"Handle time in seconds  =  "&amp;TEXT($B$41,"0.0")&amp;"  +  "&amp;TEXT($B$40,"0.0")&amp;" × transfers.      One more transfer is worth about "&amp;TEXT($B$40,"0")&amp;" seconds, and this one driver explains "&amp;TEXT($B$42,"0%")&amp;" of the spread in handle time "&amp;"(p = "&amp;TEXT($B$48,"0.000")&amp;", n = "&amp;TEXT($B$39,"0")&amp;")."</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="25">
+      <c r="A52" s="26">
         <f>IF($B$48="","",IF($B$48&gt;=0.05,"NOT PROVEN — at this sample size the slope is not distinguishable from a flat line. Collect more rows before you build anything on it.",IF($B$42&lt;0.3,"REAL BUT PARTIAL — the slope is significant (p = "&amp;TEXT($B$48,"0.000")&amp;") and the line still explains only "&amp;TEXT($B$42,"0%")&amp;" of the spread. Transfers are a genuine driver AND most of what moves handle time is not in this model.","REAL AND STRONG — significant, and the line explains "&amp;TEXT($B$42,"0%")&amp;" of the spread. Rare in support data; check the sample before you celebrate.")))</f>
         <v/>
       </c>
@@ -2196,7 +2219,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="27">
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="C39:F39"/>
@@ -2204,6 +2227,7 @@
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A56:F56"/>
+    <mergeCell ref="J26:R26"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A57:F57"/>
     <mergeCell ref="A2:F2"/>
@@ -2238,7 +2262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:W63"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -2264,6 +2288,15 @@
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="13" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2344,7 +2377,7 @@
           <t>Smallest effect worth acting on (seconds)</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="27" t="n">
         <v>20</v>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -3622,7 +3655,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="88" customHeight="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
@@ -3698,6 +3731,12 @@
       <c r="U26" s="19">
         <f>D26</f>
         <v/>
+      </c>
+      <c r="Y26" s="20" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Fitted values across, misses up and down, zero as the reference line. A shapeless band means the straight line is a fair description. A funnel means the error grows with the prediction, and a curve means you have fitted a line to something bent — in both cases the p-values above are not trustworthy. The 24 residuals here sit between roughly -100 and +100 seconds with no funnel and no curve.
+SO:  The model is safe to interpret, so go back to the coefficient table and act on the predictors whose intervals exclude zero — and only those. A clean residual plot licenses the p-values above it; it does not make a weak predictor worth acting on.</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -4402,184 +4441,184 @@
       </c>
     </row>
     <row r="40" ht="84" customHeight="1">
-      <c r="A40" s="27" t="inlineStr">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B40" s="28">
+      <c r="B40" s="29">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,5),"")</f>
         <v/>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="29">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,5),"")</f>
         <v/>
       </c>
-      <c r="D40" s="28">
+      <c r="D40" s="29">
         <f>IFERROR($B40/$C40,"")</f>
         <v/>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="30">
         <f>IFERROR(TDIST(ABS($D40),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="I40" s="30">
+      <c r="I40" s="31">
         <f>IF($B40="","","Predicted handle time for a contact with every driver at zero — before 17:00, under the limit, a brand-new agent, no transfers. Read it as the starting point the four effects are added to, not as a prediction.")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="27" t="inlineStr">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B41" s="28">
+      <c r="B41" s="29">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,4),"")</f>
         <v/>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="29">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,4),"")</f>
         <v/>
       </c>
-      <c r="D41" s="28">
+      <c r="D41" s="29">
         <f>IFERROR($B41/$C41,"")</f>
         <v/>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="30">
         <f>IFERROR(TDIST(ABS($D41),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F41" s="28">
+      <c r="F41" s="29">
         <f>IFERROR(1/(1-INDEX(LINEST($B$11:$B$34,$J$11:$L$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <f>IFERROR($B41*(MAX($B$11:$B$34)-MIN($B$11:$B$34)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="25">
+      <c r="H41" s="26">
         <f>IF($E41="","",IF($E41&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G41)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I41" s="30">
+      <c r="I41" s="31">
         <f>IF($B41="","","Seconds the after-17:00 flag adds once the other three are held still. Compare it with the p-value beside it before you repeat it out loud.")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="27" t="inlineStr">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B42" s="28">
+      <c r="B42" s="29">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,3),"")</f>
         <v/>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="29">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,3),"")</f>
         <v/>
       </c>
-      <c r="D42" s="28">
+      <c r="D42" s="29">
         <f>IFERROR($B42/$C42,"")</f>
         <v/>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="30">
         <f>IFERROR(TDIST(ABS($D42),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F42" s="28">
+      <c r="F42" s="29">
         <f>IFERROR(1/(1-INDEX(LINEST($C$11:$C$34,$M$11:$O$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="32">
         <f>IFERROR($B42*(MAX($C$11:$C$34)-MIN($C$11:$C$34)),"")</f>
         <v/>
       </c>
-      <c r="H42" s="25">
+      <c r="H42" s="26">
         <f>IF($E42="","",IF($E42&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G42)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I42" s="30">
+      <c r="I42" s="31">
         <f>IF($B42="","","Seconds the $50 authority limit adds once the other three are held still. This is the queue, not the money.")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="27" t="inlineStr">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B43" s="28">
+      <c r="B43" s="29">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,2),"")</f>
         <v/>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="29">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,2),"")</f>
         <v/>
       </c>
-      <c r="D43" s="28">
+      <c r="D43" s="29">
         <f>IFERROR($B43/$C43,"")</f>
         <v/>
       </c>
-      <c r="E43" s="29">
+      <c r="E43" s="30">
         <f>IFERROR(TDIST(ABS($D43),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F43" s="28">
+      <c r="F43" s="29">
         <f>IFERROR(1/(1-INDEX(LINEST($D$11:$D$34,$P$11:$R$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="31">
+      <c r="G43" s="32">
         <f>IFERROR($B43*(MAX($D$11:$D$34)-MIN($D$11:$D$34)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="25">
+      <c r="H43" s="26">
         <f>IF($E43="","",IF($E43&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G43)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I43" s="30">
+      <c r="I43" s="31">
         <f>IF($B43="","","Seconds per extra month of tenure — negative means longer-serving agents are quicker. Small per month, so read the range column, not this one.")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="27" t="inlineStr">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B44" s="28">
+      <c r="B44" s="29">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,1),"")</f>
         <v/>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="29">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,1),"")</f>
         <v/>
       </c>
-      <c r="D44" s="28">
+      <c r="D44" s="29">
         <f>IFERROR($B44/$C44,"")</f>
         <v/>
       </c>
-      <c r="E44" s="29">
+      <c r="E44" s="30">
         <f>IFERROR(TDIST(ABS($D44),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F44" s="28">
+      <c r="F44" s="29">
         <f>IFERROR(1/(1-INDEX(LINEST($E$11:$E$34,$S$11:$U$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <f>IFERROR($B44*(MAX($E$11:$E$34)-MIN($E$11:$E$34)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="25">
+      <c r="H44" s="26">
         <f>IF($E44="","",IF($E44&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G44)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I44" s="30">
+      <c r="I44" s="31">
         <f>IF($B44="","","Seconds each extra transfer adds once the other three are held still. Compare it with the 50.7 seconds the single-driver tab gave you.")</f>
         <v/>
       </c>
@@ -4636,7 +4675,7 @@
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B49" s="20">
+      <c r="B49" s="21">
         <f>COUNT($F$11:$F$34)</f>
         <v/>
       </c>
@@ -4652,7 +4691,7 @@
           <t>Predictors (k)</t>
         </is>
       </c>
-      <c r="B50" s="20">
+      <c r="B50" s="21">
         <f>4</f>
         <v/>
       </c>
@@ -4668,7 +4707,7 @@
           <t>R²</t>
         </is>
       </c>
-      <c r="B51" s="22">
+      <c r="B51" s="23">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,1),"")</f>
         <v/>
       </c>
@@ -4684,7 +4723,7 @@
           <t>Adjusted R²</t>
         </is>
       </c>
-      <c r="B52" s="22">
+      <c r="B52" s="23">
         <f>IFERROR(1-(1-$B$51)*($B$49-1)/($B$49-$B$50-1),"")</f>
         <v/>
       </c>
@@ -4700,7 +4739,7 @@
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B53" s="21">
+      <c r="B53" s="22">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,2),"")</f>
         <v/>
       </c>
@@ -4716,7 +4755,7 @@
           <t>F</t>
         </is>
       </c>
-      <c r="B54" s="21">
+      <c r="B54" s="22">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,1),"")</f>
         <v/>
       </c>
@@ -4732,7 +4771,7 @@
           <t>Degrees of freedom (residual)</t>
         </is>
       </c>
-      <c r="B55" s="20">
+      <c r="B55" s="21">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,2),"")</f>
         <v/>
       </c>
@@ -4748,7 +4787,7 @@
           <t>p-value for F</t>
         </is>
       </c>
-      <c r="B56" s="24">
+      <c r="B56" s="25">
         <f>IFERROR(FDIST($B$54,$B$50,$B$55),"")</f>
         <v/>
       </c>
@@ -4819,9 +4858,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="26">
     <mergeCell ref="C52:I52"/>
     <mergeCell ref="C7:I7"/>
+    <mergeCell ref="Y26:AG26"/>
     <mergeCell ref="C57:I57"/>
     <mergeCell ref="C53:I53"/>
     <mergeCell ref="A2:I2"/>
@@ -4997,171 +5037,171 @@
       <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B10" s="32" t="n">
+      <c r="B10" s="33" t="n">
         <v>-3.05</v>
       </c>
-      <c r="C10" s="32" t="n">
+      <c r="C10" s="33" t="n">
         <v>0.24</v>
       </c>
-      <c r="D10" s="33" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E10" s="34">
+      <c r="E10" s="35">
         <f>IFERROR(EXP($B10),"")</f>
         <v/>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="35">
         <f>IFERROR(EXP($B10-1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="35">
         <f>IFERROR(EXP($B10+1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="31">
         <f>"Baseline odds of a reopen with every driver at zero: "&amp;TEXT($E10,"0.000")&amp;" to 1, which is "&amp;TEXT($E10/(1+$E10),"0.0%")&amp;" probability."</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B11" s="32" t="n">
+      <c r="B11" s="33" t="n">
         <v>1.16</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="33" t="n">
         <v>0.21</v>
       </c>
-      <c r="D11" s="33" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E11" s="34">
+      <c r="E11" s="35">
         <f>IFERROR(EXP($B11),"")</f>
         <v/>
       </c>
-      <c r="F11" s="34">
+      <c r="F11" s="35">
         <f>IFERROR(EXP($B11-1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="35">
         <f>IFERROR(EXP($B11+1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="31">
         <f>"Raising the adjustment after 17:00 multiplies the odds of a reopen by "&amp;TEXT($E11,"0.00")&amp;". This is the posting-batch effect, and it is the largest single driver in the model."</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B12" s="32" t="n">
+      <c r="B12" s="33" t="n">
         <v>0.83</v>
       </c>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="33" t="n">
         <v>0.22</v>
       </c>
-      <c r="D12" s="33" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
         <is>
           <t>0.0002</t>
         </is>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="35">
         <f>IFERROR(EXP($B12),"")</f>
         <v/>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="35">
         <f>IFERROR(EXP($B12-1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="35">
         <f>IFERROR(EXP($B12+1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="H12" s="30">
+      <c r="H12" s="31">
         <f>"Clearing the $50 authority limit multiplies the odds of a reopen by "&amp;TEXT($E12,"0.00")&amp;", because the case waits in a queue for approval."</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="84" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B13" s="32" t="n">
+      <c r="B13" s="33" t="n">
         <v>-0.038</v>
       </c>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="33" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="D13" s="33" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="35">
         <f>IFERROR(EXP($B13),"")</f>
         <v/>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="35">
         <f>IFERROR(EXP($B13-1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="35">
         <f>IFERROR(EXP($B13+1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <f>"Each extra month of tenure multiplies the odds by "&amp;TEXT($E13,"0.000")&amp;" — so a 24-month agent runs at "&amp;TEXT($E13^24,"0.00")&amp;" times the odds of a first-week agent."</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B14" s="32" t="n">
+      <c r="B14" s="33" t="n">
         <v>0.61</v>
       </c>
-      <c r="C14" s="32" t="n">
+      <c r="C14" s="33" t="n">
         <v>0.12</v>
       </c>
-      <c r="D14" s="33" t="inlineStr">
+      <c r="D14" s="34" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E14" s="34">
+      <c r="E14" s="35">
         <f>IFERROR(EXP($B14),"")</f>
         <v/>
       </c>
-      <c r="F14" s="34">
+      <c r="F14" s="35">
         <f>IFERROR(EXP($B14-1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="35">
         <f>IFERROR(EXP($B14+1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <f>"Each extra transfer multiplies the odds of a reopen by "&amp;TEXT($E14,"0.00")&amp;". Multiply by how common transfers are before you rank it against the others."</f>
         <v/>
       </c>
@@ -5259,15 +5299,15 @@
       <c r="F19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="24">
         <f>IF($B19="","",$B$10+$B$11*$B19+$B$12*$C19+$B$13*$D19+$B$14*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="23">
         <f>IFERROR(1/(1+EXP(-$G19)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="20">
+      <c r="I19" s="21">
         <f>IF($H19="","",IF($H19&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5293,15 +5333,15 @@
       <c r="F20" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="24">
         <f>IF($B20="","",$B$10+$B$11*$B20+$B$12*$C20+$B$13*$D20+$B$14*$E20)</f>
         <v/>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="23">
         <f>IFERROR(1/(1+EXP(-$G20)),"")</f>
         <v/>
       </c>
-      <c r="I20" s="20">
+      <c r="I20" s="21">
         <f>IF($H20="","",IF($H20&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5327,15 +5367,15 @@
       <c r="F21" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="24">
         <f>IF($B21="","",$B$10+$B$11*$B21+$B$12*$C21+$B$13*$D21+$B$14*$E21)</f>
         <v/>
       </c>
-      <c r="H21" s="22">
+      <c r="H21" s="23">
         <f>IFERROR(1/(1+EXP(-$G21)),"")</f>
         <v/>
       </c>
-      <c r="I21" s="20">
+      <c r="I21" s="21">
         <f>IF($H21="","",IF($H21&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5361,15 +5401,15 @@
       <c r="F22" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="24">
         <f>IF($B22="","",$B$10+$B$11*$B22+$B$12*$C22+$B$13*$D22+$B$14*$E22)</f>
         <v/>
       </c>
-      <c r="H22" s="22">
+      <c r="H22" s="23">
         <f>IFERROR(1/(1+EXP(-$G22)),"")</f>
         <v/>
       </c>
-      <c r="I22" s="20">
+      <c r="I22" s="21">
         <f>IF($H22="","",IF($H22&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5395,15 +5435,15 @@
       <c r="F23" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="24">
         <f>IF($B23="","",$B$10+$B$11*$B23+$B$12*$C23+$B$13*$D23+$B$14*$E23)</f>
         <v/>
       </c>
-      <c r="H23" s="22">
+      <c r="H23" s="23">
         <f>IFERROR(1/(1+EXP(-$G23)),"")</f>
         <v/>
       </c>
-      <c r="I23" s="20">
+      <c r="I23" s="21">
         <f>IF($H23="","",IF($H23&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5429,15 +5469,15 @@
       <c r="F24" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="24">
         <f>IF($B24="","",$B$10+$B$11*$B24+$B$12*$C24+$B$13*$D24+$B$14*$E24)</f>
         <v/>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="23">
         <f>IFERROR(1/(1+EXP(-$G24)),"")</f>
         <v/>
       </c>
-      <c r="I24" s="20">
+      <c r="I24" s="21">
         <f>IF($H24="","",IF($H24&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5463,15 +5503,15 @@
       <c r="F25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="24">
         <f>IF($B25="","",$B$10+$B$11*$B25+$B$12*$C25+$B$13*$D25+$B$14*$E25)</f>
         <v/>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="23">
         <f>IFERROR(1/(1+EXP(-$G25)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="20">
+      <c r="I25" s="21">
         <f>IF($H25="","",IF($H25&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5497,15 +5537,15 @@
       <c r="F26" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="24">
         <f>IF($B26="","",$B$10+$B$11*$B26+$B$12*$C26+$B$13*$D26+$B$14*$E26)</f>
         <v/>
       </c>
-      <c r="H26" s="22">
+      <c r="H26" s="23">
         <f>IFERROR(1/(1+EXP(-$G26)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="20">
+      <c r="I26" s="21">
         <f>IF($H26="","",IF($H26&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5531,15 +5571,15 @@
       <c r="F27" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="24">
         <f>IF($B27="","",$B$10+$B$11*$B27+$B$12*$C27+$B$13*$D27+$B$14*$E27)</f>
         <v/>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="23">
         <f>IFERROR(1/(1+EXP(-$G27)),"")</f>
         <v/>
       </c>
-      <c r="I27" s="20">
+      <c r="I27" s="21">
         <f>IF($H27="","",IF($H27&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5565,15 +5605,15 @@
       <c r="F28" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="23">
+      <c r="G28" s="24">
         <f>IF($B28="","",$B$10+$B$11*$B28+$B$12*$C28+$B$13*$D28+$B$14*$E28)</f>
         <v/>
       </c>
-      <c r="H28" s="22">
+      <c r="H28" s="23">
         <f>IFERROR(1/(1+EXP(-$G28)),"")</f>
         <v/>
       </c>
-      <c r="I28" s="20">
+      <c r="I28" s="21">
         <f>IF($H28="","",IF($H28&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5599,15 +5639,15 @@
       <c r="F29" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="24">
         <f>IF($B29="","",$B$10+$B$11*$B29+$B$12*$C29+$B$13*$D29+$B$14*$E29)</f>
         <v/>
       </c>
-      <c r="H29" s="22">
+      <c r="H29" s="23">
         <f>IFERROR(1/(1+EXP(-$G29)),"")</f>
         <v/>
       </c>
-      <c r="I29" s="20">
+      <c r="I29" s="21">
         <f>IF($H29="","",IF($H29&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5633,15 +5673,15 @@
       <c r="F30" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="24">
         <f>IF($B30="","",$B$10+$B$11*$B30+$B$12*$C30+$B$13*$D30+$B$14*$E30)</f>
         <v/>
       </c>
-      <c r="H30" s="22">
+      <c r="H30" s="23">
         <f>IFERROR(1/(1+EXP(-$G30)),"")</f>
         <v/>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="21">
         <f>IF($H30="","",IF($H30&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5667,15 +5707,15 @@
       <c r="F31" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="24">
         <f>IF($B31="","",$B$10+$B$11*$B31+$B$12*$C31+$B$13*$D31+$B$14*$E31)</f>
         <v/>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="23">
         <f>IFERROR(1/(1+EXP(-$G31)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="20">
+      <c r="I31" s="21">
         <f>IF($H31="","",IF($H31&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5701,15 +5741,15 @@
       <c r="F32" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="24">
         <f>IF($B32="","",$B$10+$B$11*$B32+$B$12*$C32+$B$13*$D32+$B$14*$E32)</f>
         <v/>
       </c>
-      <c r="H32" s="22">
+      <c r="H32" s="23">
         <f>IFERROR(1/(1+EXP(-$G32)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="21">
         <f>IF($H32="","",IF($H32&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5735,15 +5775,15 @@
       <c r="F33" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="24">
         <f>IF($B33="","",$B$10+$B$11*$B33+$B$12*$C33+$B$13*$D33+$B$14*$E33)</f>
         <v/>
       </c>
-      <c r="H33" s="22">
+      <c r="H33" s="23">
         <f>IFERROR(1/(1+EXP(-$G33)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="20">
+      <c r="I33" s="21">
         <f>IF($H33="","",IF($H33&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5769,15 +5809,15 @@
       <c r="F34" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="24">
         <f>IF($B34="","",$B$10+$B$11*$B34+$B$12*$C34+$B$13*$D34+$B$14*$E34)</f>
         <v/>
       </c>
-      <c r="H34" s="22">
+      <c r="H34" s="23">
         <f>IFERROR(1/(1+EXP(-$G34)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="20">
+      <c r="I34" s="21">
         <f>IF($H34="","",IF($H34&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5803,15 +5843,15 @@
       <c r="F35" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="24">
         <f>IF($B35="","",$B$10+$B$11*$B35+$B$12*$C35+$B$13*$D35+$B$14*$E35)</f>
         <v/>
       </c>
-      <c r="H35" s="22">
+      <c r="H35" s="23">
         <f>IFERROR(1/(1+EXP(-$G35)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="20">
+      <c r="I35" s="21">
         <f>IF($H35="","",IF($H35&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5837,15 +5877,15 @@
       <c r="F36" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="24">
         <f>IF($B36="","",$B$10+$B$11*$B36+$B$12*$C36+$B$13*$D36+$B$14*$E36)</f>
         <v/>
       </c>
-      <c r="H36" s="22">
+      <c r="H36" s="23">
         <f>IFERROR(1/(1+EXP(-$G36)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="20">
+      <c r="I36" s="21">
         <f>IF($H36="","",IF($H36&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5871,15 +5911,15 @@
       <c r="F37" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="24">
         <f>IF($B37="","",$B$10+$B$11*$B37+$B$12*$C37+$B$13*$D37+$B$14*$E37)</f>
         <v/>
       </c>
-      <c r="H37" s="22">
+      <c r="H37" s="23">
         <f>IFERROR(1/(1+EXP(-$G37)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="20">
+      <c r="I37" s="21">
         <f>IF($H37="","",IF($H37&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5905,15 +5945,15 @@
       <c r="F38" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="24">
         <f>IF($B38="","",$B$10+$B$11*$B38+$B$12*$C38+$B$13*$D38+$B$14*$E38)</f>
         <v/>
       </c>
-      <c r="H38" s="22">
+      <c r="H38" s="23">
         <f>IFERROR(1/(1+EXP(-$G38)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="20">
+      <c r="I38" s="21">
         <f>IF($H38="","",IF($H38&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5939,15 +5979,15 @@
       <c r="F39" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="24">
         <f>IF($B39="","",$B$10+$B$11*$B39+$B$12*$C39+$B$13*$D39+$B$14*$E39)</f>
         <v/>
       </c>
-      <c r="H39" s="22">
+      <c r="H39" s="23">
         <f>IFERROR(1/(1+EXP(-$G39)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="20">
+      <c r="I39" s="21">
         <f>IF($H39="","",IF($H39&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -5973,15 +6013,15 @@
       <c r="F40" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="24">
         <f>IF($B40="","",$B$10+$B$11*$B40+$B$12*$C40+$B$13*$D40+$B$14*$E40)</f>
         <v/>
       </c>
-      <c r="H40" s="22">
+      <c r="H40" s="23">
         <f>IFERROR(1/(1+EXP(-$G40)),"")</f>
         <v/>
       </c>
-      <c r="I40" s="20">
+      <c r="I40" s="21">
         <f>IF($H40="","",IF($H40&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -6007,15 +6047,15 @@
       <c r="F41" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="24">
         <f>IF($B41="","",$B$10+$B$11*$B41+$B$12*$C41+$B$13*$D41+$B$14*$E41)</f>
         <v/>
       </c>
-      <c r="H41" s="22">
+      <c r="H41" s="23">
         <f>IFERROR(1/(1+EXP(-$G41)),"")</f>
         <v/>
       </c>
-      <c r="I41" s="20">
+      <c r="I41" s="21">
         <f>IF($H41="","",IF($H41&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -6041,15 +6081,15 @@
       <c r="F42" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="24">
         <f>IF($B42="","",$B$10+$B$11*$B42+$B$12*$C42+$B$13*$D42+$B$14*$E42)</f>
         <v/>
       </c>
-      <c r="H42" s="22">
+      <c r="H42" s="23">
         <f>IFERROR(1/(1+EXP(-$G42)),"")</f>
         <v/>
       </c>
-      <c r="I42" s="20">
+      <c r="I42" s="21">
         <f>IF($H42="","",IF($H42&gt;=$B$46,1,0))</f>
         <v/>
       </c>
@@ -6083,7 +6123,7 @@
           <t>Flag a contact at this probability or above</t>
         </is>
       </c>
-      <c r="B46" s="35" t="n">
+      <c r="B46" s="36" t="n">
         <v>0.2</v>
       </c>
       <c r="C46" s="10" t="inlineStr">
@@ -6098,7 +6138,7 @@
           <t>AUC the tool reported</t>
         </is>
       </c>
-      <c r="B47" s="36" t="n">
+      <c r="B47" s="37" t="n">
         <v>0.74</v>
       </c>
       <c r="C47" s="10" t="inlineStr">
@@ -6259,7 +6299,7 @@
           <t>Sensitivity — reopens you caught</t>
         </is>
       </c>
-      <c r="B58" s="22">
+      <c r="B58" s="23">
         <f>IFERROR($B$51/($B$51+$B$52),"")</f>
         <v/>
       </c>
@@ -6275,7 +6315,7 @@
           <t>Specificity — quiet contacts left alone</t>
         </is>
       </c>
-      <c r="B59" s="22">
+      <c r="B59" s="23">
         <f>IFERROR($C$52/($C$52+$C$51),"")</f>
         <v/>
       </c>
@@ -6291,7 +6331,7 @@
           <t>Precision — flags that were right</t>
         </is>
       </c>
-      <c r="B60" s="22">
+      <c r="B60" s="23">
         <f>IFERROR($B$51/($B$51+$C$51),"")</f>
         <v/>
       </c>
@@ -6307,7 +6347,7 @@
           <t>Accuracy — rows called correctly</t>
         </is>
       </c>
-      <c r="B61" s="22">
+      <c r="B61" s="23">
         <f>IFERROR(($B$51+$C$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
         <v/>
       </c>
@@ -6323,7 +6363,7 @@
           <t>Base rate — share that actually reopened</t>
         </is>
       </c>
-      <c r="B62" s="22">
+      <c r="B62" s="23">
         <f>IFERROR(($B$51+$B$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
         <v/>
       </c>

--- a/templates/30-regression.xlsx
+++ b/templates/30-regression.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,10 @@
       <i val="1"/>
       <color rgb="FF4B5563"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -119,12 +123,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,9 +160,6 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -997,11 +1004,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="108" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1147,8 +1160,20 @@
     </row>
     <row r="22"/>
     <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Effect across the observed range = the coefficient multiplied by the full span of that driver in the data you actually have. A coefficient answers 'per one unit'; this answers 'over the range that exists', which is the size a process owner can act on. A large per-unit effect on a driver that barely varies moves nothing in practice, and only this column shows that</t>
+        </is>
+      </c>
+    </row>
     <row r="26"/>
     <row r="27"/>
     <row r="28"/>
@@ -1165,7 +1190,9 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="B9"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -1203,19 +1230,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Simple linear regression — one driver, one outcome</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Fit a straight line through two columns, then find out how much of the outcome that one driver actually explains. The green rows are a worked example — replace them with your own pairs. Yellow cells above are yours to set; everything blue is a formula you can point at.</t>
         </is>
@@ -1223,63 +1250,63 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>THE QUESTION — what you are modelling, and where the rows came from</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Outcome (y) — the thing you want to move</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Handle time in seconds</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Name the measurement, not the ambition. 'Handle time from CRM open to CRM close, in seconds' is a column you can pull; 'efficiency' is not.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Driver (x) — the one thing you are testing</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>One column, and one you could actually change. Start with the driver the process owner already believes in; you are testing their belief, not replacing it.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Where the rows come from</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>24 of 966 March contacts</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Say the population and the sampling method. A convenience sample of the contacts you happened to remember will produce a slope, and the slope will be of your memory.</t>
         </is>
@@ -1287,472 +1314,472 @@
     </row>
     <row r="8"/>
     <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>THE DATA — one row per contact. First the two columns you measured: x, the driver you are testing, then y, the outcome. Then three the sheet works out for you. Contact ref is the case number and the time of day it was raised  ·  Key:
 • Fitted y = what the model predicts for that row, before you compare it with what actually happened
 • Residual = what the model missed on that row: the value that actually happened minus the fitted one</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
     </row>
     <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Contact ref · time raised</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>x — transfers before resolution</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>y — handle time, seconds (measured)</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Fitted y — seconds the line predicts for that x</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Residual — seconds the line missed by (y − fitted)</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>Unusual? residual larger than 1.5 standard errors</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>fitted line endpoints — the chart reads these</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>BA-2201 · 17:05</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="15" t="n">
+      <c r="B11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="17" t="n">
         <v>280</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="18">
         <f>IF($C11="","",$B$41+$B$40*$B11)</f>
         <v/>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="18">
         <f>IF($D11="","",$C11-$D11)</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="19">
         <f>IF($E11="","",IF(ABS($E11)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="20">
         <f>IFERROR(MIN($B$11:$B$34),0)</f>
         <v/>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="21">
         <f>IFERROR($B$41+$B$40*$G$11,"")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="15" t="n">
+      <c r="B12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="17" t="n">
         <v>506</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="18">
         <f>IF($C12="","",$B$41+$B$40*$B12)</f>
         <v/>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="18">
         <f>IF($D12="","",$C12-$D12)</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="19">
         <f>IF($E12="","",IF(ABS($E12)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="20">
         <f>IFERROR(MAX($B$11:$B$34),0)</f>
         <v/>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="21">
         <f>IFERROR($B$41+$B$40*$G$12,"")</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="15" t="n">
+      <c r="B13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="17" t="n">
         <v>344</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="18">
         <f>IF($C13="","",$B$41+$B$40*$B13)</f>
         <v/>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="18">
         <f>IF($D13="","",$C13-$D13)</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="19">
         <f>IF($E13="","",IF(ABS($E13)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="17" t="n">
         <v>479</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="18">
         <f>IF($C14="","",$B$41+$B$40*$B14)</f>
         <v/>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="18">
         <f>IF($D14="","",$C14-$D14)</f>
         <v/>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="19">
         <f>IF($E14="","",IF(ABS($E14)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
+      <c r="B15" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="17" t="n">
         <v>422</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="18">
         <f>IF($C15="","",$B$41+$B$40*$B15)</f>
         <v/>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="18">
         <f>IF($D15="","",$C15-$D15)</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="19">
         <f>IF($E15="","",IF(ABS($E15)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B16" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="17" t="n">
         <v>452</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="18">
         <f>IF($C16="","",$B$41+$B$40*$B16)</f>
         <v/>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="18">
         <f>IF($D16="","",$C16-$D16)</f>
         <v/>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="19">
         <f>IF($E16="","",IF(ABS($E16)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B17" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C17" s="17" t="n">
         <v>374</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="18">
         <f>IF($C17="","",$B$41+$B$40*$B17)</f>
         <v/>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="18">
         <f>IF($D17="","",$C17-$D17)</f>
         <v/>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="19">
         <f>IF($E17="","",IF(ABS($E17)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="15" t="n">
+      <c r="B18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="17" t="n">
         <v>451</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="18">
         <f>IF($C18="","",$B$41+$B$40*$B18)</f>
         <v/>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="18">
         <f>IF($D18="","",$C18-$D18)</f>
         <v/>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="19">
         <f>IF($E18="","",IF(ABS($E18)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="15" t="n">
+      <c r="B19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="17" t="n">
         <v>360</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="18">
         <f>IF($C19="","",$B$41+$B$40*$B19)</f>
         <v/>
       </c>
-      <c r="E19" s="16">
+      <c r="E19" s="18">
         <f>IF($D19="","",$C19-$D19)</f>
         <v/>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="19">
         <f>IF($E19="","",IF(ABS($E19)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="15" t="n">
+      <c r="B20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="17" t="n">
         <v>260</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="18">
         <f>IF($C20="","",$B$41+$B$40*$B20)</f>
         <v/>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="18">
         <f>IF($D20="","",$C20-$D20)</f>
         <v/>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="19">
         <f>IF($E20="","",IF(ABS($E20)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="15" t="n">
+      <c r="B21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="17" t="n">
         <v>415</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="18">
         <f>IF($C21="","",$B$41+$B$40*$B21)</f>
         <v/>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="18">
         <f>IF($D21="","",$C21-$D21)</f>
         <v/>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="19">
         <f>IF($E21="","",IF(ABS($E21)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
+      <c r="B22" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="15" t="n">
+      <c r="C22" s="17" t="n">
         <v>555</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="18">
         <f>IF($C22="","",$B$41+$B$40*$B22)</f>
         <v/>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="18">
         <f>IF($D22="","",$C22-$D22)</f>
         <v/>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="19">
         <f>IF($E22="","",IF(ABS($E22)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="15" t="n">
+      <c r="B23" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="17" t="n">
         <v>393</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="18">
         <f>IF($C23="","",$B$41+$B$40*$B23)</f>
         <v/>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="18">
         <f>IF($D23="","",$C23-$D23)</f>
         <v/>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="19">
         <f>IF($E23="","",IF(ABS($E23)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="15" t="n">
+      <c r="B24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="17" t="n">
         <v>454</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="18">
         <f>IF($C24="","",$B$41+$B$40*$B24)</f>
         <v/>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="18">
         <f>IF($D24="","",$C24-$D24)</f>
         <v/>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="19">
         <f>IF($E24="","",IF(ABS($E24)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="15" t="n">
+      <c r="B25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="17" t="n">
         <v>257</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="18">
         <f>IF($C25="","",$B$41+$B$40*$B25)</f>
         <v/>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="18">
         <f>IF($D25="","",$C25-$D25)</f>
         <v/>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="19">
         <f>IF($E25="","",IF(ABS($E25)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="66" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="15" t="n">
+      <c r="B26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="17" t="n">
         <v>544</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="18">
         <f>IF($C26="","",$B$41+$B$40*$B26)</f>
         <v/>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="18">
         <f>IF($D26="","",$C26-$D26)</f>
         <v/>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="19">
         <f>IF($E26="","",IF(ABS($E26)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
-      <c r="J26" s="20" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>HOW TO READ IT.  The line is what the model claims; the vertical distance from each point to it is what it got wrong. One driver explains 26.4% of the spread here, so three quarters of it is everything not on this chart. Read the residual plot on the next tab before you quote the slope anywhere.
 SO:  Do not price a benefit off this slope. One driver explains 26.4% of the spread, so move to the multiple-regression tab and find the rest before anyone quotes seconds per transfer to Finance.</t>
@@ -1760,207 +1787,207 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="15" t="n">
+      <c r="B27" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="17" t="n">
         <v>482</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="18">
         <f>IF($C27="","",$B$41+$B$40*$B27)</f>
         <v/>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="18">
         <f>IF($D27="","",$C27-$D27)</f>
         <v/>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="19">
         <f>IF($E27="","",IF(ABS($E27)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="15" t="n">
+      <c r="B28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="17" t="n">
         <v>403</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="18">
         <f>IF($C28="","",$B$41+$B$40*$B28)</f>
         <v/>
       </c>
-      <c r="E28" s="16">
+      <c r="E28" s="18">
         <f>IF($D28="","",$C28-$D28)</f>
         <v/>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="19">
         <f>IF($E28="","",IF(ABS($E28)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C29" s="15" t="n">
+      <c r="C29" s="17" t="n">
         <v>433</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="18">
         <f>IF($C29="","",$B$41+$B$40*$B29)</f>
         <v/>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="18">
         <f>IF($D29="","",$C29-$D29)</f>
         <v/>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="19">
         <f>IF($E29="","",IF(ABS($E29)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
+      <c r="B30" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="15" t="n">
+      <c r="C30" s="17" t="n">
         <v>483</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="18">
         <f>IF($C30="","",$B$41+$B$40*$B30)</f>
         <v/>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="18">
         <f>IF($D30="","",$C30-$D30)</f>
         <v/>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="19">
         <f>IF($E30="","",IF(ABS($E30)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="15" t="n">
+      <c r="B31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="17" t="n">
         <v>261</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="18">
         <f>IF($C31="","",$B$41+$B$40*$B31)</f>
         <v/>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="18">
         <f>IF($D31="","",$C31-$D31)</f>
         <v/>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="19">
         <f>IF($E31="","",IF(ABS($E31)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="15" t="n">
+      <c r="B32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="17" t="n">
         <v>424</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="18">
         <f>IF($C32="","",$B$41+$B$40*$B32)</f>
         <v/>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="18">
         <f>IF($D32="","",$C32-$D32)</f>
         <v/>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="19">
         <f>IF($E32="","",IF(ABS($E32)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="15" t="n">
+      <c r="B33" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="17" t="n">
         <v>359</v>
       </c>
-      <c r="D33" s="16">
+      <c r="D33" s="18">
         <f>IF($C33="","",$B$41+$B$40*$B33)</f>
         <v/>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="18">
         <f>IF($D33="","",$C33-$D33)</f>
         <v/>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="19">
         <f>IF($E33="","",IF(ABS($E33)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="15" t="n">
+      <c r="B34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="17" t="n">
         <v>505</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="18">
         <f>IF($C34="","",$B$41+$B$40*$B34)</f>
         <v/>
       </c>
-      <c r="E34" s="16">
+      <c r="E34" s="18">
         <f>IF($D34="","",$C34-$D34)</f>
         <v/>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="19">
         <f>IF($E34="","",IF(ABS($E34)&gt;1.5*$B$44,"LOOK AT THIS ONE","on the line"))</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>The last three columns are the model marking its own homework. Fitted y is what the line says this contact should have taken; the residual is what it missed by. BA-2216 took 544 seconds on a single transfer, which the line cannot explain at all — hold on to it, because the multiple regression tab does explain it.</t>
         </is>
@@ -1968,192 +1995,192 @@
     </row>
     <row r="36"/>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>STEP 1 — the line, and whether it is real</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Statistic</t>
         </is>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>What it tells you</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr"/>
-      <c r="E38" s="12" t="inlineStr"/>
-      <c r="F38" s="12" t="inlineStr"/>
+      <c r="D38" s="14" t="inlineStr"/>
+      <c r="E38" s="14" t="inlineStr"/>
+      <c r="F38" s="14" t="inlineStr"/>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B39" s="21">
+      <c r="B39" s="22">
         <f>COUNT($C$11:$C$34)</f>
         <v/>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>COUNT(y). Thirty is where a regression starts to be worth quoting; below about fifteen you are describing this sample and nothing beyond it.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Slope — seconds per extra transfer</t>
         </is>
       </c>
-      <c r="B40" s="22">
+      <c r="B40" s="23">
         <f>SLOPE($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>SLOPE(y, x). How much y moves for one more transfer. This is the number that goes in a business case, not R².</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>Intercept — seconds at zero transfers</t>
         </is>
       </c>
-      <c r="B41" s="22">
+      <c r="B41" s="23">
         <f>INTERCEPT($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>INTERCEPT(y, x). Only meaningful if zero is inside the range you actually observed. Here it is: plenty of these contacts were never transferred.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>R² — share of the spread the line explains</t>
         </is>
       </c>
-      <c r="B42" s="23">
+      <c r="B42" s="24">
         <f>RSQ($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>RSQ(y, x). The share of the variation in y this one driver accounts for. Everything else is the drivers you did not put in the model.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>Correlation r</t>
         </is>
       </c>
-      <c r="B43" s="24">
+      <c r="B43" s="25">
         <f>CORREL($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>CORREL(y, x). The square root of R², carrying the sign. Useful for direction; do not quote it as if it were a share of anything.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B44" s="22">
+      <c r="B44" s="23">
         <f>STEYX($C$11:$C$34,$B$11:$B$34)</f>
         <v/>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C44" s="12" t="inlineStr">
         <is>
           <t>STEYX(y, x). The typical distance a point sits from the line, in seconds. This is the honest width of a prediction from this model.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
+      <c r="A45" s="10" t="inlineStr">
         <is>
           <t>Standard error of the slope</t>
         </is>
       </c>
-      <c r="B45" s="22">
+      <c r="B45" s="23">
         <f>INDEX(LINEST($C$11:$C$34,$B$11:$B$34,TRUE,TRUE),2,1)</f>
         <v/>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>INDEX(LINEST(y, x, TRUE, TRUE), 2, 1). LINEST returns a block; row 2 column 1 of it is how much the slope would wobble on another sample.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>t-stat for the slope</t>
         </is>
       </c>
-      <c r="B46" s="22">
+      <c r="B46" s="23">
         <f>IFERROR($B$40/$B$45,"")</f>
         <v/>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>Slope divided by its own standard error. Two or more and the slope is usually distinguishable from a flat line at this sample size.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>Degrees of freedom</t>
         </is>
       </c>
-      <c r="B47" s="21">
+      <c r="B47" s="22">
         <f>IFERROR(COUNT($C$11:$C$34)-2,"")</f>
         <v/>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>n − 2: one for the slope, one for the intercept. Everything about significance below depends on this being honest about your row count.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="A48" s="10" t="inlineStr">
         <is>
           <t>p-value for the slope</t>
         </is>
       </c>
-      <c r="B48" s="25">
+      <c r="B48" s="26">
         <f>IFERROR(TDIST(ABS($B$46),$B$47,2),"")</f>
         <v/>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C48" s="12" t="inlineStr">
         <is>
           <t>TDIST(|t|, df, 2). The chance of a slope this far from flat if transfers made no difference at all.</t>
         </is>
@@ -2161,58 +2188,58 @@
     </row>
     <row r="49"/>
     <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>THE MODEL, WRITTEN OUT — the sentence you are allowed to say</t>
         </is>
       </c>
-      <c r="B50" s="7" t="n"/>
-      <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
-      <c r="E50" s="7" t="n"/>
-      <c r="F50" s="7" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="26">
+      <c r="A51" s="27">
         <f>"Handle time in seconds  =  "&amp;TEXT($B$41,"0.0")&amp;"  +  "&amp;TEXT($B$40,"0.0")&amp;" × transfers.      One more transfer is worth about "&amp;TEXT($B$40,"0")&amp;" seconds, and this one driver explains "&amp;TEXT($B$42,"0%")&amp;" of the spread in handle time "&amp;"(p = "&amp;TEXT($B$48,"0.000")&amp;", n = "&amp;TEXT($B$39,"0")&amp;")."</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="26">
+      <c r="A52" s="27">
         <f>IF($B$48="","",IF($B$48&gt;=0.05,"NOT PROVEN — at this sample size the slope is not distinguishable from a flat line. Collect more rows before you build anything on it.",IF($B$42&lt;0.3,"REAL BUT PARTIAL — the slope is significant (p = "&amp;TEXT($B$48,"0.000")&amp;") and the line still explains only "&amp;TEXT($B$42,"0%")&amp;" of the spread. Transfers are a genuine driver AND most of what moves handle time is not in this model.","REAL AND STRONG — significant, and the line explains "&amp;TEXT($B$42,"0%")&amp;" of the spread. Rare in support data; check the sample before you celebrate.")))</f>
         <v/>
       </c>
     </row>
     <row r="53"/>
     <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>THE DECISION RULE — read this before you quote the R²</t>
         </is>
       </c>
-      <c r="B54" s="7" t="n"/>
-      <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
-      <c r="E54" s="7" t="n"/>
-      <c r="F54" s="7" t="n"/>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
     </row>
     <row r="55" ht="75" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>How high does R² have to be? Much lower than a manufacturing course will tell you. In support you are modelling human behaviour through a CRM, and 0.20 to 0.40 from a single driver is a normal, useful result. Judge the model on whether the SLOPE is big enough to act on and stable enough to bet on — not on R². A model that explains 25% of handle time and hands you a lever worth 50 seconds a contact is worth more than one explaining 80% of something you cannot change.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="75" customHeight="1">
-      <c r="A56" s="10" t="inlineStr">
+      <c r="A56" s="12" t="inlineStr">
         <is>
           <t>A significant coefficient is not the same as one worth acting on. Significance says the effect is probably not zero. It says nothing about size. With enough rows a 3-second effect becomes significant, and 3 seconds will not move your reopen rate. Always read the slope in the units of the problem, multiply it by the range you actually see, and compare that to the smallest change that would matter to the business.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="75" customHeight="1">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="A57" s="12" t="inlineStr">
         <is>
           <t>Correlation here is not causation, and one driver hides the rest. This sheet cannot tell you whether transfers CAUSE longer handle times or whether hard cases cause both. Nothing in a regression can. To claim cause you need either a mechanism you have watched at the gemba or a designed experiment (24-doe-design-matrix.xlsx). Until then this is a well-measured association, and you say so out loud.</t>
         </is>
@@ -2300,22 +2327,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Multiple regression — four candidate drivers at once</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
+      <c r="G1" s="6" t="n"/>
+      <c r="H1" s="6" t="n"/>
+      <c r="I1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>One driver at a time flatters whichever one you looked at first. This fits all four together, prices each one with the others held still, and shows you which of them the data cannot actually tell apart.</t>
         </is>
@@ -2323,64 +2350,64 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>THE MODEL — the outcome, and the smallest effect worth acting on</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Outcome (y) — what the model explains</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Handle time in seconds</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>One continuous column. If your outcome is yes/no — reopened, escalated, breached — this is the wrong tab: go to Logistic regression.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Where the rows come from</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>24 of 966 March contacts</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Population and sampling method. A model fitted on the contacts somebody escalated is a model of escalation, whatever you name the outcome.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Smallest effect worth acting on (seconds)</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>The smallest change in the outcome that would actually change a decision. Ask the process owner, before you see the coefficients. Twenty seconds a contact across 966 contacts a month is about five and a half hours of handling — enough to bother with; two seconds is not.</t>
         </is>
@@ -2388,1351 +2415,1351 @@
     </row>
     <row r="8"/>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>THE DATA — the same 24 contacts, with all four drivers beside y. Contact ref is the case number and the time of day it was raised, which is where the 17:00 column comes from  ·  Key:
 • Fitted y = what the model predicts for that row, before you compare it with what actually happened
 • Residual = what the model missed on that row: the value that actually happened minus the fitted one</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="9" t="n"/>
     </row>
     <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Contact ref</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>Handle time in seconds (y)</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Fitted y — what the model predicts</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>Residual (y − fitted)</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>VIF helper — the other three, for Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>VIF helper — the other three, for Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr">
+      <c r="P10" s="7" t="inlineStr">
         <is>
           <t>VIF helper — the other three, for Agent tenure in months</t>
         </is>
       </c>
-      <c r="S10" s="5" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>VIF helper — the other three, for Transfers before resolution</t>
         </is>
       </c>
-      <c r="V10" s="5" t="inlineStr">
+      <c r="V10" s="7" t="inlineStr">
         <is>
           <t>zero line — the chart reads these</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>BA-2201 · 17:05</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15" t="n">
+      <c r="B11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="E11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="15" t="n">
+      <c r="E11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="17" t="n">
         <v>280</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="18">
         <f>IF($F11="","",$B$40+$B$41*$B11+$B$42*$C11+$B$43*$D11+$B$44*$E11)</f>
         <v/>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="18">
         <f>IF($G11="","",$F11-$G11)</f>
         <v/>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="21">
         <f>C11</f>
         <v/>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="21">
         <f>D11</f>
         <v/>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="21">
         <f>E11</f>
         <v/>
       </c>
-      <c r="M11" s="19">
+      <c r="M11" s="21">
         <f>B11</f>
         <v/>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="21">
         <f>D11</f>
         <v/>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="21">
         <f>E11</f>
         <v/>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="21">
         <f>B11</f>
         <v/>
       </c>
-      <c r="Q11" s="19">
+      <c r="Q11" s="21">
         <f>C11</f>
         <v/>
       </c>
-      <c r="R11" s="19">
+      <c r="R11" s="21">
         <f>E11</f>
         <v/>
       </c>
-      <c r="S11" s="19">
+      <c r="S11" s="21">
         <f>B11</f>
         <v/>
       </c>
-      <c r="T11" s="19">
+      <c r="T11" s="21">
         <f>C11</f>
         <v/>
       </c>
-      <c r="U11" s="19">
+      <c r="U11" s="21">
         <f>D11</f>
         <v/>
       </c>
-      <c r="V11" s="19">
+      <c r="V11" s="21">
         <f>IFERROR(MIN($G$11:$G$34),0)</f>
         <v/>
       </c>
-      <c r="W11" s="19" t="n">
+      <c r="W11" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="15" t="n">
+      <c r="B12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="E12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="15" t="n">
+      <c r="E12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="17" t="n">
         <v>506</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="18">
         <f>IF($F12="","",$B$40+$B$41*$B12+$B$42*$C12+$B$43*$D12+$B$44*$E12)</f>
         <v/>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="18">
         <f>IF($G12="","",$F12-$G12)</f>
         <v/>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="21">
         <f>C12</f>
         <v/>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="21">
         <f>D12</f>
         <v/>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="21">
         <f>E12</f>
         <v/>
       </c>
-      <c r="M12" s="19">
+      <c r="M12" s="21">
         <f>B12</f>
         <v/>
       </c>
-      <c r="N12" s="19">
+      <c r="N12" s="21">
         <f>D12</f>
         <v/>
       </c>
-      <c r="O12" s="19">
+      <c r="O12" s="21">
         <f>E12</f>
         <v/>
       </c>
-      <c r="P12" s="19">
+      <c r="P12" s="21">
         <f>B12</f>
         <v/>
       </c>
-      <c r="Q12" s="19">
+      <c r="Q12" s="21">
         <f>C12</f>
         <v/>
       </c>
-      <c r="R12" s="19">
+      <c r="R12" s="21">
         <f>E12</f>
         <v/>
       </c>
-      <c r="S12" s="19">
+      <c r="S12" s="21">
         <f>B12</f>
         <v/>
       </c>
-      <c r="T12" s="19">
+      <c r="T12" s="21">
         <f>C12</f>
         <v/>
       </c>
-      <c r="U12" s="19">
+      <c r="U12" s="21">
         <f>D12</f>
         <v/>
       </c>
-      <c r="V12" s="19">
+      <c r="V12" s="21">
         <f>IFERROR(MAX($G$11:$G$34),0)</f>
         <v/>
       </c>
-      <c r="W12" s="19" t="n">
+      <c r="W12" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="15" t="n">
+      <c r="B13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="E13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="15" t="n">
+      <c r="E13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="17" t="n">
         <v>344</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="18">
         <f>IF($F13="","",$B$40+$B$41*$B13+$B$42*$C13+$B$43*$D13+$B$44*$E13)</f>
         <v/>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="18">
         <f>IF($G13="","",$F13-$G13)</f>
         <v/>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="21">
         <f>C13</f>
         <v/>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="21">
         <f>D13</f>
         <v/>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="21">
         <f>E13</f>
         <v/>
       </c>
-      <c r="M13" s="19">
+      <c r="M13" s="21">
         <f>B13</f>
         <v/>
       </c>
-      <c r="N13" s="19">
+      <c r="N13" s="21">
         <f>D13</f>
         <v/>
       </c>
-      <c r="O13" s="19">
+      <c r="O13" s="21">
         <f>E13</f>
         <v/>
       </c>
-      <c r="P13" s="19">
+      <c r="P13" s="21">
         <f>B13</f>
         <v/>
       </c>
-      <c r="Q13" s="19">
+      <c r="Q13" s="21">
         <f>C13</f>
         <v/>
       </c>
-      <c r="R13" s="19">
+      <c r="R13" s="21">
         <f>E13</f>
         <v/>
       </c>
-      <c r="S13" s="19">
+      <c r="S13" s="21">
         <f>B13</f>
         <v/>
       </c>
-      <c r="T13" s="19">
+      <c r="T13" s="21">
         <f>C13</f>
         <v/>
       </c>
-      <c r="U13" s="19">
+      <c r="U13" s="21">
         <f>D13</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="15" t="n">
+      <c r="B14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F14" s="17" t="n">
         <v>479</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="18">
         <f>IF($F14="","",$B$40+$B$41*$B14+$B$42*$C14+$B$43*$D14+$B$44*$E14)</f>
         <v/>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="18">
         <f>IF($G14="","",$F14-$G14)</f>
         <v/>
       </c>
-      <c r="J14" s="19">
+      <c r="J14" s="21">
         <f>C14</f>
         <v/>
       </c>
-      <c r="K14" s="19">
+      <c r="K14" s="21">
         <f>D14</f>
         <v/>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="21">
         <f>E14</f>
         <v/>
       </c>
-      <c r="M14" s="19">
+      <c r="M14" s="21">
         <f>B14</f>
         <v/>
       </c>
-      <c r="N14" s="19">
+      <c r="N14" s="21">
         <f>D14</f>
         <v/>
       </c>
-      <c r="O14" s="19">
+      <c r="O14" s="21">
         <f>E14</f>
         <v/>
       </c>
-      <c r="P14" s="19">
+      <c r="P14" s="21">
         <f>B14</f>
         <v/>
       </c>
-      <c r="Q14" s="19">
+      <c r="Q14" s="21">
         <f>C14</f>
         <v/>
       </c>
-      <c r="R14" s="19">
+      <c r="R14" s="21">
         <f>E14</f>
         <v/>
       </c>
-      <c r="S14" s="19">
+      <c r="S14" s="21">
         <f>B14</f>
         <v/>
       </c>
-      <c r="T14" s="19">
+      <c r="T14" s="21">
         <f>C14</f>
         <v/>
       </c>
-      <c r="U14" s="19">
+      <c r="U14" s="21">
         <f>D14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15" t="n">
+      <c r="B15" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="17" t="n">
         <v>33</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F15" s="17" t="n">
         <v>422</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="18">
         <f>IF($F15="","",$B$40+$B$41*$B15+$B$42*$C15+$B$43*$D15+$B$44*$E15)</f>
         <v/>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="18">
         <f>IF($G15="","",$F15-$G15)</f>
         <v/>
       </c>
-      <c r="J15" s="19">
+      <c r="J15" s="21">
         <f>C15</f>
         <v/>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="21">
         <f>D15</f>
         <v/>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="21">
         <f>E15</f>
         <v/>
       </c>
-      <c r="M15" s="19">
+      <c r="M15" s="21">
         <f>B15</f>
         <v/>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="21">
         <f>D15</f>
         <v/>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="21">
         <f>E15</f>
         <v/>
       </c>
-      <c r="P15" s="19">
+      <c r="P15" s="21">
         <f>B15</f>
         <v/>
       </c>
-      <c r="Q15" s="19">
+      <c r="Q15" s="21">
         <f>C15</f>
         <v/>
       </c>
-      <c r="R15" s="19">
+      <c r="R15" s="21">
         <f>E15</f>
         <v/>
       </c>
-      <c r="S15" s="19">
+      <c r="S15" s="21">
         <f>B15</f>
         <v/>
       </c>
-      <c r="T15" s="19">
+      <c r="T15" s="21">
         <f>C15</f>
         <v/>
       </c>
-      <c r="U15" s="19">
+      <c r="U15" s="21">
         <f>D15</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="15" t="n">
+      <c r="B16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="15" t="n">
+      <c r="F16" s="17" t="n">
         <v>452</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="18">
         <f>IF($F16="","",$B$40+$B$41*$B16+$B$42*$C16+$B$43*$D16+$B$44*$E16)</f>
         <v/>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="18">
         <f>IF($G16="","",$F16-$G16)</f>
         <v/>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="21">
         <f>C16</f>
         <v/>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="21">
         <f>D16</f>
         <v/>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="21">
         <f>E16</f>
         <v/>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="21">
         <f>B16</f>
         <v/>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="21">
         <f>D16</f>
         <v/>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="21">
         <f>E16</f>
         <v/>
       </c>
-      <c r="P16" s="19">
+      <c r="P16" s="21">
         <f>B16</f>
         <v/>
       </c>
-      <c r="Q16" s="19">
+      <c r="Q16" s="21">
         <f>C16</f>
         <v/>
       </c>
-      <c r="R16" s="19">
+      <c r="R16" s="21">
         <f>E16</f>
         <v/>
       </c>
-      <c r="S16" s="19">
+      <c r="S16" s="21">
         <f>B16</f>
         <v/>
       </c>
-      <c r="T16" s="19">
+      <c r="T16" s="21">
         <f>C16</f>
         <v/>
       </c>
-      <c r="U16" s="19">
+      <c r="U16" s="21">
         <f>D16</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="15" t="n">
+      <c r="B17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="17" t="n">
         <v>46</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="15" t="n">
+      <c r="F17" s="17" t="n">
         <v>374</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="18">
         <f>IF($F17="","",$B$40+$B$41*$B17+$B$42*$C17+$B$43*$D17+$B$44*$E17)</f>
         <v/>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="18">
         <f>IF($G17="","",$F17-$G17)</f>
         <v/>
       </c>
-      <c r="J17" s="19">
+      <c r="J17" s="21">
         <f>C17</f>
         <v/>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="21">
         <f>D17</f>
         <v/>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="21">
         <f>E17</f>
         <v/>
       </c>
-      <c r="M17" s="19">
+      <c r="M17" s="21">
         <f>B17</f>
         <v/>
       </c>
-      <c r="N17" s="19">
+      <c r="N17" s="21">
         <f>D17</f>
         <v/>
       </c>
-      <c r="O17" s="19">
+      <c r="O17" s="21">
         <f>E17</f>
         <v/>
       </c>
-      <c r="P17" s="19">
+      <c r="P17" s="21">
         <f>B17</f>
         <v/>
       </c>
-      <c r="Q17" s="19">
+      <c r="Q17" s="21">
         <f>C17</f>
         <v/>
       </c>
-      <c r="R17" s="19">
+      <c r="R17" s="21">
         <f>E17</f>
         <v/>
       </c>
-      <c r="S17" s="19">
+      <c r="S17" s="21">
         <f>B17</f>
         <v/>
       </c>
-      <c r="T17" s="19">
+      <c r="T17" s="21">
         <f>C17</f>
         <v/>
       </c>
-      <c r="U17" s="19">
+      <c r="U17" s="21">
         <f>D17</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15" t="n">
+      <c r="B18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="n">
+      <c r="E18" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="17" t="n">
         <v>451</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="18">
         <f>IF($F18="","",$B$40+$B$41*$B18+$B$42*$C18+$B$43*$D18+$B$44*$E18)</f>
         <v/>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="18">
         <f>IF($G18="","",$F18-$G18)</f>
         <v/>
       </c>
-      <c r="J18" s="19">
+      <c r="J18" s="21">
         <f>C18</f>
         <v/>
       </c>
-      <c r="K18" s="19">
+      <c r="K18" s="21">
         <f>D18</f>
         <v/>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="21">
         <f>E18</f>
         <v/>
       </c>
-      <c r="M18" s="19">
+      <c r="M18" s="21">
         <f>B18</f>
         <v/>
       </c>
-      <c r="N18" s="19">
+      <c r="N18" s="21">
         <f>D18</f>
         <v/>
       </c>
-      <c r="O18" s="19">
+      <c r="O18" s="21">
         <f>E18</f>
         <v/>
       </c>
-      <c r="P18" s="19">
+      <c r="P18" s="21">
         <f>B18</f>
         <v/>
       </c>
-      <c r="Q18" s="19">
+      <c r="Q18" s="21">
         <f>C18</f>
         <v/>
       </c>
-      <c r="R18" s="19">
+      <c r="R18" s="21">
         <f>E18</f>
         <v/>
       </c>
-      <c r="S18" s="19">
+      <c r="S18" s="21">
         <f>B18</f>
         <v/>
       </c>
-      <c r="T18" s="19">
+      <c r="T18" s="21">
         <f>C18</f>
         <v/>
       </c>
-      <c r="U18" s="19">
+      <c r="U18" s="21">
         <f>D18</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="15" t="n">
+      <c r="B19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="15" t="n">
+      <c r="E19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="17" t="n">
         <v>360</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="18">
         <f>IF($F19="","",$B$40+$B$41*$B19+$B$42*$C19+$B$43*$D19+$B$44*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="16">
+      <c r="H19" s="18">
         <f>IF($G19="","",$F19-$G19)</f>
         <v/>
       </c>
-      <c r="J19" s="19">
+      <c r="J19" s="21">
         <f>C19</f>
         <v/>
       </c>
-      <c r="K19" s="19">
+      <c r="K19" s="21">
         <f>D19</f>
         <v/>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="21">
         <f>E19</f>
         <v/>
       </c>
-      <c r="M19" s="19">
+      <c r="M19" s="21">
         <f>B19</f>
         <v/>
       </c>
-      <c r="N19" s="19">
+      <c r="N19" s="21">
         <f>D19</f>
         <v/>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="21">
         <f>E19</f>
         <v/>
       </c>
-      <c r="P19" s="19">
+      <c r="P19" s="21">
         <f>B19</f>
         <v/>
       </c>
-      <c r="Q19" s="19">
+      <c r="Q19" s="21">
         <f>C19</f>
         <v/>
       </c>
-      <c r="R19" s="19">
+      <c r="R19" s="21">
         <f>E19</f>
         <v/>
       </c>
-      <c r="S19" s="19">
+      <c r="S19" s="21">
         <f>B19</f>
         <v/>
       </c>
-      <c r="T19" s="19">
+      <c r="T19" s="21">
         <f>C19</f>
         <v/>
       </c>
-      <c r="U19" s="19">
+      <c r="U19" s="21">
         <f>D19</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="15" t="n">
+      <c r="B20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="15" t="n">
+      <c r="E20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="17" t="n">
         <v>260</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="18">
         <f>IF($F20="","",$B$40+$B$41*$B20+$B$42*$C20+$B$43*$D20+$B$44*$E20)</f>
         <v/>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="18">
         <f>IF($G20="","",$F20-$G20)</f>
         <v/>
       </c>
-      <c r="J20" s="19">
+      <c r="J20" s="21">
         <f>C20</f>
         <v/>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="21">
         <f>D20</f>
         <v/>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="21">
         <f>E20</f>
         <v/>
       </c>
-      <c r="M20" s="19">
+      <c r="M20" s="21">
         <f>B20</f>
         <v/>
       </c>
-      <c r="N20" s="19">
+      <c r="N20" s="21">
         <f>D20</f>
         <v/>
       </c>
-      <c r="O20" s="19">
+      <c r="O20" s="21">
         <f>E20</f>
         <v/>
       </c>
-      <c r="P20" s="19">
+      <c r="P20" s="21">
         <f>B20</f>
         <v/>
       </c>
-      <c r="Q20" s="19">
+      <c r="Q20" s="21">
         <f>C20</f>
         <v/>
       </c>
-      <c r="R20" s="19">
+      <c r="R20" s="21">
         <f>E20</f>
         <v/>
       </c>
-      <c r="S20" s="19">
+      <c r="S20" s="21">
         <f>B20</f>
         <v/>
       </c>
-      <c r="T20" s="19">
+      <c r="T20" s="21">
         <f>C20</f>
         <v/>
       </c>
-      <c r="U20" s="19">
+      <c r="U20" s="21">
         <f>D20</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15" t="n">
+      <c r="B21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="E21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="15" t="n">
+      <c r="E21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="17" t="n">
         <v>415</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="18">
         <f>IF($F21="","",$B$40+$B$41*$B21+$B$42*$C21+$B$43*$D21+$B$44*$E21)</f>
         <v/>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="18">
         <f>IF($G21="","",$F21-$G21)</f>
         <v/>
       </c>
-      <c r="J21" s="19">
+      <c r="J21" s="21">
         <f>C21</f>
         <v/>
       </c>
-      <c r="K21" s="19">
+      <c r="K21" s="21">
         <f>D21</f>
         <v/>
       </c>
-      <c r="L21" s="19">
+      <c r="L21" s="21">
         <f>E21</f>
         <v/>
       </c>
-      <c r="M21" s="19">
+      <c r="M21" s="21">
         <f>B21</f>
         <v/>
       </c>
-      <c r="N21" s="19">
+      <c r="N21" s="21">
         <f>D21</f>
         <v/>
       </c>
-      <c r="O21" s="19">
+      <c r="O21" s="21">
         <f>E21</f>
         <v/>
       </c>
-      <c r="P21" s="19">
+      <c r="P21" s="21">
         <f>B21</f>
         <v/>
       </c>
-      <c r="Q21" s="19">
+      <c r="Q21" s="21">
         <f>C21</f>
         <v/>
       </c>
-      <c r="R21" s="19">
+      <c r="R21" s="21">
         <f>E21</f>
         <v/>
       </c>
-      <c r="S21" s="19">
+      <c r="S21" s="21">
         <f>B21</f>
         <v/>
       </c>
-      <c r="T21" s="19">
+      <c r="T21" s="21">
         <f>C21</f>
         <v/>
       </c>
-      <c r="U21" s="19">
+      <c r="U21" s="21">
         <f>D21</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15" t="n">
+      <c r="B22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="15" t="n">
+      <c r="F22" s="17" t="n">
         <v>555</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="18">
         <f>IF($F22="","",$B$40+$B$41*$B22+$B$42*$C22+$B$43*$D22+$B$44*$E22)</f>
         <v/>
       </c>
-      <c r="H22" s="16">
+      <c r="H22" s="18">
         <f>IF($G22="","",$F22-$G22)</f>
         <v/>
       </c>
-      <c r="J22" s="19">
+      <c r="J22" s="21">
         <f>C22</f>
         <v/>
       </c>
-      <c r="K22" s="19">
+      <c r="K22" s="21">
         <f>D22</f>
         <v/>
       </c>
-      <c r="L22" s="19">
+      <c r="L22" s="21">
         <f>E22</f>
         <v/>
       </c>
-      <c r="M22" s="19">
+      <c r="M22" s="21">
         <f>B22</f>
         <v/>
       </c>
-      <c r="N22" s="19">
+      <c r="N22" s="21">
         <f>D22</f>
         <v/>
       </c>
-      <c r="O22" s="19">
+      <c r="O22" s="21">
         <f>E22</f>
         <v/>
       </c>
-      <c r="P22" s="19">
+      <c r="P22" s="21">
         <f>B22</f>
         <v/>
       </c>
-      <c r="Q22" s="19">
+      <c r="Q22" s="21">
         <f>C22</f>
         <v/>
       </c>
-      <c r="R22" s="19">
+      <c r="R22" s="21">
         <f>E22</f>
         <v/>
       </c>
-      <c r="S22" s="19">
+      <c r="S22" s="21">
         <f>B22</f>
         <v/>
       </c>
-      <c r="T22" s="19">
+      <c r="T22" s="21">
         <f>C22</f>
         <v/>
       </c>
-      <c r="U22" s="19">
+      <c r="U22" s="21">
         <f>D22</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="15" t="n">
+      <c r="B23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="15" t="n">
+      <c r="E23" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="17" t="n">
         <v>393</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="18">
         <f>IF($F23="","",$B$40+$B$41*$B23+$B$42*$C23+$B$43*$D23+$B$44*$E23)</f>
         <v/>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="18">
         <f>IF($G23="","",$F23-$G23)</f>
         <v/>
       </c>
-      <c r="J23" s="19">
+      <c r="J23" s="21">
         <f>C23</f>
         <v/>
       </c>
-      <c r="K23" s="19">
+      <c r="K23" s="21">
         <f>D23</f>
         <v/>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="21">
         <f>E23</f>
         <v/>
       </c>
-      <c r="M23" s="19">
+      <c r="M23" s="21">
         <f>B23</f>
         <v/>
       </c>
-      <c r="N23" s="19">
+      <c r="N23" s="21">
         <f>D23</f>
         <v/>
       </c>
-      <c r="O23" s="19">
+      <c r="O23" s="21">
         <f>E23</f>
         <v/>
       </c>
-      <c r="P23" s="19">
+      <c r="P23" s="21">
         <f>B23</f>
         <v/>
       </c>
-      <c r="Q23" s="19">
+      <c r="Q23" s="21">
         <f>C23</f>
         <v/>
       </c>
-      <c r="R23" s="19">
+      <c r="R23" s="21">
         <f>E23</f>
         <v/>
       </c>
-      <c r="S23" s="19">
+      <c r="S23" s="21">
         <f>B23</f>
         <v/>
       </c>
-      <c r="T23" s="19">
+      <c r="T23" s="21">
         <f>C23</f>
         <v/>
       </c>
-      <c r="U23" s="19">
+      <c r="U23" s="21">
         <f>D23</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="15" t="n">
+      <c r="B24" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="E24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="15" t="n">
+      <c r="E24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="17" t="n">
         <v>454</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="18">
         <f>IF($F24="","",$B$40+$B$41*$B24+$B$42*$C24+$B$43*$D24+$B$44*$E24)</f>
         <v/>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="18">
         <f>IF($G24="","",$F24-$G24)</f>
         <v/>
       </c>
-      <c r="J24" s="19">
+      <c r="J24" s="21">
         <f>C24</f>
         <v/>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="21">
         <f>D24</f>
         <v/>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="21">
         <f>E24</f>
         <v/>
       </c>
-      <c r="M24" s="19">
+      <c r="M24" s="21">
         <f>B24</f>
         <v/>
       </c>
-      <c r="N24" s="19">
+      <c r="N24" s="21">
         <f>D24</f>
         <v/>
       </c>
-      <c r="O24" s="19">
+      <c r="O24" s="21">
         <f>E24</f>
         <v/>
       </c>
-      <c r="P24" s="19">
+      <c r="P24" s="21">
         <f>B24</f>
         <v/>
       </c>
-      <c r="Q24" s="19">
+      <c r="Q24" s="21">
         <f>C24</f>
         <v/>
       </c>
-      <c r="R24" s="19">
+      <c r="R24" s="21">
         <f>E24</f>
         <v/>
       </c>
-      <c r="S24" s="19">
+      <c r="S24" s="21">
         <f>B24</f>
         <v/>
       </c>
-      <c r="T24" s="19">
+      <c r="T24" s="21">
         <f>C24</f>
         <v/>
       </c>
-      <c r="U24" s="19">
+      <c r="U24" s="21">
         <f>D24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="15" t="n">
+      <c r="B25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="E25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="15" t="n">
+      <c r="E25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="17" t="n">
         <v>257</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="18">
         <f>IF($F25="","",$B$40+$B$41*$B25+$B$42*$C25+$B$43*$D25+$B$44*$E25)</f>
         <v/>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="18">
         <f>IF($G25="","",$F25-$G25)</f>
         <v/>
       </c>
-      <c r="J25" s="19">
+      <c r="J25" s="21">
         <f>C25</f>
         <v/>
       </c>
-      <c r="K25" s="19">
+      <c r="K25" s="21">
         <f>D25</f>
         <v/>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="21">
         <f>E25</f>
         <v/>
       </c>
-      <c r="M25" s="19">
+      <c r="M25" s="21">
         <f>B25</f>
         <v/>
       </c>
-      <c r="N25" s="19">
+      <c r="N25" s="21">
         <f>D25</f>
         <v/>
       </c>
-      <c r="O25" s="19">
+      <c r="O25" s="21">
         <f>E25</f>
         <v/>
       </c>
-      <c r="P25" s="19">
+      <c r="P25" s="21">
         <f>B25</f>
         <v/>
       </c>
-      <c r="Q25" s="19">
+      <c r="Q25" s="21">
         <f>C25</f>
         <v/>
       </c>
-      <c r="R25" s="19">
+      <c r="R25" s="21">
         <f>E25</f>
         <v/>
       </c>
-      <c r="S25" s="19">
+      <c r="S25" s="21">
         <f>B25</f>
         <v/>
       </c>
-      <c r="T25" s="19">
+      <c r="T25" s="21">
         <f>C25</f>
         <v/>
       </c>
-      <c r="U25" s="19">
+      <c r="U25" s="21">
         <f>D25</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="88" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="15" t="n">
+      <c r="B26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="E26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="15" t="n">
+      <c r="E26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="17" t="n">
         <v>544</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="18">
         <f>IF($F26="","",$B$40+$B$41*$B26+$B$42*$C26+$B$43*$D26+$B$44*$E26)</f>
         <v/>
       </c>
-      <c r="H26" s="16">
+      <c r="H26" s="18">
         <f>IF($G26="","",$F26-$G26)</f>
         <v/>
       </c>
-      <c r="J26" s="19">
+      <c r="J26" s="21">
         <f>C26</f>
         <v/>
       </c>
-      <c r="K26" s="19">
+      <c r="K26" s="21">
         <f>D26</f>
         <v/>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="21">
         <f>E26</f>
         <v/>
       </c>
-      <c r="M26" s="19">
+      <c r="M26" s="21">
         <f>B26</f>
         <v/>
       </c>
-      <c r="N26" s="19">
+      <c r="N26" s="21">
         <f>D26</f>
         <v/>
       </c>
-      <c r="O26" s="19">
+      <c r="O26" s="21">
         <f>E26</f>
         <v/>
       </c>
-      <c r="P26" s="19">
+      <c r="P26" s="21">
         <f>B26</f>
         <v/>
       </c>
-      <c r="Q26" s="19">
+      <c r="Q26" s="21">
         <f>C26</f>
         <v/>
       </c>
-      <c r="R26" s="19">
+      <c r="R26" s="21">
         <f>E26</f>
         <v/>
       </c>
-      <c r="S26" s="19">
+      <c r="S26" s="21">
         <f>B26</f>
         <v/>
       </c>
-      <c r="T26" s="19">
+      <c r="T26" s="21">
         <f>C26</f>
         <v/>
       </c>
-      <c r="U26" s="19">
+      <c r="U26" s="21">
         <f>D26</f>
         <v/>
       </c>
-      <c r="Y26" s="20" t="inlineStr">
+      <c r="Y26" s="4" t="inlineStr">
         <is>
           <t>HOW TO READ IT.  Fitted values across, misses up and down, zero as the reference line. A shapeless band means the straight line is a fair description. A funnel means the error grows with the prediction, and a curve means you have fitted a line to something bent — in both cases the p-values above are not trustworthy. The 24 residuals here sit between roughly -100 and +100 seconds with no funnel and no curve.
 SO:  The model is safe to interpret, so go back to the coefficient table and act on the predictors whose intervals exclude zero — and only those. A clean residual plot licenses the p-values above it; it does not make a weak predictor worth acting on.</t>
@@ -3740,631 +3767,631 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15" t="n">
+      <c r="B27" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E27" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="15" t="n">
+      <c r="E27" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="17" t="n">
         <v>482</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="18">
         <f>IF($F27="","",$B$40+$B$41*$B27+$B$42*$C27+$B$43*$D27+$B$44*$E27)</f>
         <v/>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="18">
         <f>IF($G27="","",$F27-$G27)</f>
         <v/>
       </c>
-      <c r="J27" s="19">
+      <c r="J27" s="21">
         <f>C27</f>
         <v/>
       </c>
-      <c r="K27" s="19">
+      <c r="K27" s="21">
         <f>D27</f>
         <v/>
       </c>
-      <c r="L27" s="19">
+      <c r="L27" s="21">
         <f>E27</f>
         <v/>
       </c>
-      <c r="M27" s="19">
+      <c r="M27" s="21">
         <f>B27</f>
         <v/>
       </c>
-      <c r="N27" s="19">
+      <c r="N27" s="21">
         <f>D27</f>
         <v/>
       </c>
-      <c r="O27" s="19">
+      <c r="O27" s="21">
         <f>E27</f>
         <v/>
       </c>
-      <c r="P27" s="19">
+      <c r="P27" s="21">
         <f>B27</f>
         <v/>
       </c>
-      <c r="Q27" s="19">
+      <c r="Q27" s="21">
         <f>C27</f>
         <v/>
       </c>
-      <c r="R27" s="19">
+      <c r="R27" s="21">
         <f>E27</f>
         <v/>
       </c>
-      <c r="S27" s="19">
+      <c r="S27" s="21">
         <f>B27</f>
         <v/>
       </c>
-      <c r="T27" s="19">
+      <c r="T27" s="21">
         <f>C27</f>
         <v/>
       </c>
-      <c r="U27" s="19">
+      <c r="U27" s="21">
         <f>D27</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="15" t="n">
+      <c r="B28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="15" t="n">
+      <c r="E28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="17" t="n">
         <v>403</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="18">
         <f>IF($F28="","",$B$40+$B$41*$B28+$B$42*$C28+$B$43*$D28+$B$44*$E28)</f>
         <v/>
       </c>
-      <c r="H28" s="16">
+      <c r="H28" s="18">
         <f>IF($G28="","",$F28-$G28)</f>
         <v/>
       </c>
-      <c r="J28" s="19">
+      <c r="J28" s="21">
         <f>C28</f>
         <v/>
       </c>
-      <c r="K28" s="19">
+      <c r="K28" s="21">
         <f>D28</f>
         <v/>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="21">
         <f>E28</f>
         <v/>
       </c>
-      <c r="M28" s="19">
+      <c r="M28" s="21">
         <f>B28</f>
         <v/>
       </c>
-      <c r="N28" s="19">
+      <c r="N28" s="21">
         <f>D28</f>
         <v/>
       </c>
-      <c r="O28" s="19">
+      <c r="O28" s="21">
         <f>E28</f>
         <v/>
       </c>
-      <c r="P28" s="19">
+      <c r="P28" s="21">
         <f>B28</f>
         <v/>
       </c>
-      <c r="Q28" s="19">
+      <c r="Q28" s="21">
         <f>C28</f>
         <v/>
       </c>
-      <c r="R28" s="19">
+      <c r="R28" s="21">
         <f>E28</f>
         <v/>
       </c>
-      <c r="S28" s="19">
+      <c r="S28" s="21">
         <f>B28</f>
         <v/>
       </c>
-      <c r="T28" s="19">
+      <c r="T28" s="21">
         <f>C28</f>
         <v/>
       </c>
-      <c r="U28" s="19">
+      <c r="U28" s="21">
         <f>D28</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="15" t="n">
+      <c r="B29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="14" t="n">
+      <c r="E29" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F29" s="15" t="n">
+      <c r="F29" s="17" t="n">
         <v>433</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="18">
         <f>IF($F29="","",$B$40+$B$41*$B29+$B$42*$C29+$B$43*$D29+$B$44*$E29)</f>
         <v/>
       </c>
-      <c r="H29" s="16">
+      <c r="H29" s="18">
         <f>IF($G29="","",$F29-$G29)</f>
         <v/>
       </c>
-      <c r="J29" s="19">
+      <c r="J29" s="21">
         <f>C29</f>
         <v/>
       </c>
-      <c r="K29" s="19">
+      <c r="K29" s="21">
         <f>D29</f>
         <v/>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="21">
         <f>E29</f>
         <v/>
       </c>
-      <c r="M29" s="19">
+      <c r="M29" s="21">
         <f>B29</f>
         <v/>
       </c>
-      <c r="N29" s="19">
+      <c r="N29" s="21">
         <f>D29</f>
         <v/>
       </c>
-      <c r="O29" s="19">
+      <c r="O29" s="21">
         <f>E29</f>
         <v/>
       </c>
-      <c r="P29" s="19">
+      <c r="P29" s="21">
         <f>B29</f>
         <v/>
       </c>
-      <c r="Q29" s="19">
+      <c r="Q29" s="21">
         <f>C29</f>
         <v/>
       </c>
-      <c r="R29" s="19">
+      <c r="R29" s="21">
         <f>E29</f>
         <v/>
       </c>
-      <c r="S29" s="19">
+      <c r="S29" s="21">
         <f>B29</f>
         <v/>
       </c>
-      <c r="T29" s="19">
+      <c r="T29" s="21">
         <f>C29</f>
         <v/>
       </c>
-      <c r="U29" s="19">
+      <c r="U29" s="21">
         <f>D29</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="15" t="n">
+      <c r="B30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="15" t="n">
+      <c r="F30" s="17" t="n">
         <v>483</v>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="18">
         <f>IF($F30="","",$B$40+$B$41*$B30+$B$42*$C30+$B$43*$D30+$B$44*$E30)</f>
         <v/>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="18">
         <f>IF($G30="","",$F30-$G30)</f>
         <v/>
       </c>
-      <c r="J30" s="19">
+      <c r="J30" s="21">
         <f>C30</f>
         <v/>
       </c>
-      <c r="K30" s="19">
+      <c r="K30" s="21">
         <f>D30</f>
         <v/>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="21">
         <f>E30</f>
         <v/>
       </c>
-      <c r="M30" s="19">
+      <c r="M30" s="21">
         <f>B30</f>
         <v/>
       </c>
-      <c r="N30" s="19">
+      <c r="N30" s="21">
         <f>D30</f>
         <v/>
       </c>
-      <c r="O30" s="19">
+      <c r="O30" s="21">
         <f>E30</f>
         <v/>
       </c>
-      <c r="P30" s="19">
+      <c r="P30" s="21">
         <f>B30</f>
         <v/>
       </c>
-      <c r="Q30" s="19">
+      <c r="Q30" s="21">
         <f>C30</f>
         <v/>
       </c>
-      <c r="R30" s="19">
+      <c r="R30" s="21">
         <f>E30</f>
         <v/>
       </c>
-      <c r="S30" s="19">
+      <c r="S30" s="21">
         <f>B30</f>
         <v/>
       </c>
-      <c r="T30" s="19">
+      <c r="T30" s="21">
         <f>C30</f>
         <v/>
       </c>
-      <c r="U30" s="19">
+      <c r="U30" s="21">
         <f>D30</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="15" t="n">
+      <c r="B31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="15" t="n">
+      <c r="E31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="17" t="n">
         <v>261</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="18">
         <f>IF($F31="","",$B$40+$B$41*$B31+$B$42*$C31+$B$43*$D31+$B$44*$E31)</f>
         <v/>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="18">
         <f>IF($G31="","",$F31-$G31)</f>
         <v/>
       </c>
-      <c r="J31" s="19">
+      <c r="J31" s="21">
         <f>C31</f>
         <v/>
       </c>
-      <c r="K31" s="19">
+      <c r="K31" s="21">
         <f>D31</f>
         <v/>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="21">
         <f>E31</f>
         <v/>
       </c>
-      <c r="M31" s="19">
+      <c r="M31" s="21">
         <f>B31</f>
         <v/>
       </c>
-      <c r="N31" s="19">
+      <c r="N31" s="21">
         <f>D31</f>
         <v/>
       </c>
-      <c r="O31" s="19">
+      <c r="O31" s="21">
         <f>E31</f>
         <v/>
       </c>
-      <c r="P31" s="19">
+      <c r="P31" s="21">
         <f>B31</f>
         <v/>
       </c>
-      <c r="Q31" s="19">
+      <c r="Q31" s="21">
         <f>C31</f>
         <v/>
       </c>
-      <c r="R31" s="19">
+      <c r="R31" s="21">
         <f>E31</f>
         <v/>
       </c>
-      <c r="S31" s="19">
+      <c r="S31" s="21">
         <f>B31</f>
         <v/>
       </c>
-      <c r="T31" s="19">
+      <c r="T31" s="21">
         <f>C31</f>
         <v/>
       </c>
-      <c r="U31" s="19">
+      <c r="U31" s="21">
         <f>D31</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="15" t="n">
+      <c r="B32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="17" t="n">
         <v>53</v>
       </c>
-      <c r="E32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="15" t="n">
+      <c r="E32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="17" t="n">
         <v>424</v>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="18">
         <f>IF($F32="","",$B$40+$B$41*$B32+$B$42*$C32+$B$43*$D32+$B$44*$E32)</f>
         <v/>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="18">
         <f>IF($G32="","",$F32-$G32)</f>
         <v/>
       </c>
-      <c r="J32" s="19">
+      <c r="J32" s="21">
         <f>C32</f>
         <v/>
       </c>
-      <c r="K32" s="19">
+      <c r="K32" s="21">
         <f>D32</f>
         <v/>
       </c>
-      <c r="L32" s="19">
+      <c r="L32" s="21">
         <f>E32</f>
         <v/>
       </c>
-      <c r="M32" s="19">
+      <c r="M32" s="21">
         <f>B32</f>
         <v/>
       </c>
-      <c r="N32" s="19">
+      <c r="N32" s="21">
         <f>D32</f>
         <v/>
       </c>
-      <c r="O32" s="19">
+      <c r="O32" s="21">
         <f>E32</f>
         <v/>
       </c>
-      <c r="P32" s="19">
+      <c r="P32" s="21">
         <f>B32</f>
         <v/>
       </c>
-      <c r="Q32" s="19">
+      <c r="Q32" s="21">
         <f>C32</f>
         <v/>
       </c>
-      <c r="R32" s="19">
+      <c r="R32" s="21">
         <f>E32</f>
         <v/>
       </c>
-      <c r="S32" s="19">
+      <c r="S32" s="21">
         <f>B32</f>
         <v/>
       </c>
-      <c r="T32" s="19">
+      <c r="T32" s="21">
         <f>C32</f>
         <v/>
       </c>
-      <c r="U32" s="19">
+      <c r="U32" s="21">
         <f>D32</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="15" t="n">
+      <c r="B33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="E33" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="15" t="n">
+      <c r="E33" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="17" t="n">
         <v>359</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="18">
         <f>IF($F33="","",$B$40+$B$41*$B33+$B$42*$C33+$B$43*$D33+$B$44*$E33)</f>
         <v/>
       </c>
-      <c r="H33" s="16">
+      <c r="H33" s="18">
         <f>IF($G33="","",$F33-$G33)</f>
         <v/>
       </c>
-      <c r="J33" s="19">
+      <c r="J33" s="21">
         <f>C33</f>
         <v/>
       </c>
-      <c r="K33" s="19">
+      <c r="K33" s="21">
         <f>D33</f>
         <v/>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="21">
         <f>E33</f>
         <v/>
       </c>
-      <c r="M33" s="19">
+      <c r="M33" s="21">
         <f>B33</f>
         <v/>
       </c>
-      <c r="N33" s="19">
+      <c r="N33" s="21">
         <f>D33</f>
         <v/>
       </c>
-      <c r="O33" s="19">
+      <c r="O33" s="21">
         <f>E33</f>
         <v/>
       </c>
-      <c r="P33" s="19">
+      <c r="P33" s="21">
         <f>B33</f>
         <v/>
       </c>
-      <c r="Q33" s="19">
+      <c r="Q33" s="21">
         <f>C33</f>
         <v/>
       </c>
-      <c r="R33" s="19">
+      <c r="R33" s="21">
         <f>E33</f>
         <v/>
       </c>
-      <c r="S33" s="19">
+      <c r="S33" s="21">
         <f>B33</f>
         <v/>
       </c>
-      <c r="T33" s="19">
+      <c r="T33" s="21">
         <f>C33</f>
         <v/>
       </c>
-      <c r="U33" s="19">
+      <c r="U33" s="21">
         <f>D33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="15" t="n">
+      <c r="B34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="15" t="n">
+      <c r="E34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="17" t="n">
         <v>505</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="18">
         <f>IF($F34="","",$B$40+$B$41*$B34+$B$42*$C34+$B$43*$D34+$B$44*$E34)</f>
         <v/>
       </c>
-      <c r="H34" s="16">
+      <c r="H34" s="18">
         <f>IF($G34="","",$F34-$G34)</f>
         <v/>
       </c>
-      <c r="J34" s="19">
+      <c r="J34" s="21">
         <f>C34</f>
         <v/>
       </c>
-      <c r="K34" s="19">
+      <c r="K34" s="21">
         <f>D34</f>
         <v/>
       </c>
-      <c r="L34" s="19">
+      <c r="L34" s="21">
         <f>E34</f>
         <v/>
       </c>
-      <c r="M34" s="19">
+      <c r="M34" s="21">
         <f>B34</f>
         <v/>
       </c>
-      <c r="N34" s="19">
+      <c r="N34" s="21">
         <f>D34</f>
         <v/>
       </c>
-      <c r="O34" s="19">
+      <c r="O34" s="21">
         <f>E34</f>
         <v/>
       </c>
-      <c r="P34" s="19">
+      <c r="P34" s="21">
         <f>B34</f>
         <v/>
       </c>
-      <c r="Q34" s="19">
+      <c r="Q34" s="21">
         <f>C34</f>
         <v/>
       </c>
-      <c r="R34" s="19">
+      <c r="R34" s="21">
         <f>E34</f>
         <v/>
       </c>
-      <c r="S34" s="19">
+      <c r="S34" s="21">
         <f>B34</f>
         <v/>
       </c>
-      <c r="T34" s="19">
+      <c r="T34" s="21">
         <f>C34</f>
         <v/>
       </c>
-      <c r="U34" s="19">
+      <c r="U34" s="21">
         <f>D34</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Two of the four drivers are 1/0 flags, which is how you put a yes/no into a regression: the coefficient is then simply the seconds the flag adds. Fitted y and the residual are the model marking its own homework, and the residual column is what the second chart plots.</t>
         </is>
@@ -4372,8 +4399,8 @@
     </row>
     <row r="36"/>
     <row r="37"/>
-    <row r="38" ht="144" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="38" ht="120" customHeight="1">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>STEP 1 — the coefficients, and which of them you can act on  ·  Key:
 • Coefficient = how far the outcome moves for a one-unit change in that driver, with the other drivers held still
@@ -4381,250 +4408,250 @@
 • t-stat = the coefficient divided by its own standard error; roughly 2 or more is the usual signal
 • p-value = the chance of seeing a difference this big if nothing had really changed
 • VIF = variance inflation factor, how much two drivers move together; under 5 is fine, over 10 means drop one
-• Effect across the observed range = the coefficient multiplied by the full span of that driver in the data you actually have. A coefficient answers 'per one unit'; this answers 'over the range that exists', which is the size a process owner can act on. A large per-unit effect on a driver that barely varies moves nothing in practice, and only this column shows that</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
+• Effect across the observed range = the coefficient multiplied by the full span of that driver in the data you actually have.</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="9" t="n"/>
+      <c r="I38" s="9" t="n"/>
     </row>
     <row r="39" ht="46" customHeight="1">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Predictor</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>Coefficient</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>Std error</t>
         </is>
       </c>
-      <c r="D39" s="12" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>t-stat</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="F39" s="12" t="inlineStr">
+      <c r="F39" s="14" t="inlineStr">
         <is>
           <t>VIF</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr">
+      <c r="G39" s="14" t="inlineStr">
         <is>
           <t>Effect across the observed range</t>
         </is>
       </c>
-      <c r="H39" s="12" t="inlineStr">
+      <c r="H39" s="14" t="inlineStr">
         <is>
           <t>Act on it?</t>
         </is>
       </c>
-      <c r="I39" s="12" t="inlineStr">
+      <c r="I39" s="14" t="inlineStr">
         <is>
           <t>What it means</t>
         </is>
       </c>
     </row>
     <row r="40" ht="84" customHeight="1">
-      <c r="A40" s="28" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,5),"")</f>
         <v/>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,5),"")</f>
         <v/>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="30">
         <f>IFERROR($B40/$C40,"")</f>
         <v/>
       </c>
-      <c r="E40" s="30">
+      <c r="E40" s="31">
         <f>IFERROR(TDIST(ABS($D40),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="I40" s="31">
+      <c r="I40" s="32">
         <f>IF($B40="","","Predicted handle time for a contact with every driver at zero — before 17:00, under the limit, a brand-new agent, no transfers. Read it as the starting point the four effects are added to, not as a prediction.")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="28" t="inlineStr">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,4),"")</f>
         <v/>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,4),"")</f>
         <v/>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="30">
         <f>IFERROR($B41/$C41,"")</f>
         <v/>
       </c>
-      <c r="E41" s="30">
+      <c r="E41" s="31">
         <f>IFERROR(TDIST(ABS($D41),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F41" s="29">
+      <c r="F41" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($B$11:$B$34,$J$11:$L$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="33">
         <f>IFERROR($B41*(MAX($B$11:$B$34)-MIN($B$11:$B$34)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="26">
+      <c r="H41" s="27">
         <f>IF($E41="","",IF($E41&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G41)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="32">
         <f>IF($B41="","","Seconds the after-17:00 flag adds once the other three are held still. Compare it with the p-value beside it before you repeat it out loud.")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="28" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,3),"")</f>
         <v/>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,3),"")</f>
         <v/>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="30">
         <f>IFERROR($B42/$C42,"")</f>
         <v/>
       </c>
-      <c r="E42" s="30">
+      <c r="E42" s="31">
         <f>IFERROR(TDIST(ABS($D42),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F42" s="29">
+      <c r="F42" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($C$11:$C$34,$M$11:$O$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="33">
         <f>IFERROR($B42*(MAX($C$11:$C$34)-MIN($C$11:$C$34)),"")</f>
         <v/>
       </c>
-      <c r="H42" s="26">
+      <c r="H42" s="27">
         <f>IF($E42="","",IF($E42&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G42)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I42" s="31">
+      <c r="I42" s="32">
         <f>IF($B42="","","Seconds the $50 authority limit adds once the other three are held still. This is the queue, not the money.")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="28" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,2),"")</f>
         <v/>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,2),"")</f>
         <v/>
       </c>
-      <c r="D43" s="29">
+      <c r="D43" s="30">
         <f>IFERROR($B43/$C43,"")</f>
         <v/>
       </c>
-      <c r="E43" s="30">
+      <c r="E43" s="31">
         <f>IFERROR(TDIST(ABS($D43),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F43" s="29">
+      <c r="F43" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($D$11:$D$34,$P$11:$R$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="32">
+      <c r="G43" s="33">
         <f>IFERROR($B43*(MAX($D$11:$D$34)-MIN($D$11:$D$34)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="26">
+      <c r="H43" s="27">
         <f>IF($E43="","",IF($E43&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G43)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I43" s="31">
+      <c r="I43" s="32">
         <f>IF($B43="","","Seconds per extra month of tenure — negative means longer-serving agents are quicker. Small per month, so read the range column, not this one.")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="28" t="inlineStr">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),1,1),"")</f>
         <v/>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="30">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),2,1),"")</f>
         <v/>
       </c>
-      <c r="D44" s="29">
+      <c r="D44" s="30">
         <f>IFERROR($B44/$C44,"")</f>
         <v/>
       </c>
-      <c r="E44" s="30">
+      <c r="E44" s="31">
         <f>IFERROR(TDIST(ABS($D44),$B$55,2),"")</f>
         <v/>
       </c>
-      <c r="F44" s="29">
+      <c r="F44" s="30">
         <f>IFERROR(1/(1-INDEX(LINEST($E$11:$E$34,$S$11:$U$34,TRUE,TRUE),3,1)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="33">
         <f>IFERROR($B44*(MAX($E$11:$E$34)-MIN($E$11:$E$34)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="26">
+      <c r="H44" s="27">
         <f>IF($E44="","",IF($E44&gt;=0.05,"NOT PROVEN — cannot be separated from zero",IF(ABS($G44)&lt;$B$7,"REAL BUT TOO SMALL — under the "&amp;TEXT($B$7,"0")&amp;" seconds you set","ACT ON IT — real, and big enough to matter")))</f>
         <v/>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="32">
         <f>IF($B44="","","Seconds each extra transfer adds once the other three are held still. Compare it with the 50.7 seconds the single-driver tab gave you.")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="90" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>VIF is the one people skip, and it is why this table disagrees with the process owner. Two thirds of the after-17:00 adjustments here are also over the $50 limit, so the two columns carry much the same information and the model cannot say which of them is doing the work — it splits the credit and widens both standard errors. Under 5 is fine, 5 to 10 is a warning, over 10 means drop one of the pair or combine them, and re-fit. Nine of the eleven after-17:00 contacts here are also over the limit, which is where these VIFs come from.</t>
         </is>
@@ -4632,182 +4659,182 @@
     </row>
     <row r="46"/>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
         <is>
           <t>STEP 2 — the model as a whole</t>
         </is>
       </c>
-      <c r="B47" s="7" t="n"/>
-      <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7" t="n"/>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="7" t="n"/>
-      <c r="I47" s="7" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>Statistic</t>
         </is>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C48" s="12" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>What it tells you</t>
         </is>
       </c>
-      <c r="D48" s="12" t="inlineStr"/>
-      <c r="E48" s="12" t="inlineStr"/>
-      <c r="F48" s="12" t="inlineStr"/>
-      <c r="G48" s="12" t="inlineStr"/>
-      <c r="H48" s="12" t="inlineStr"/>
-      <c r="I48" s="12" t="inlineStr"/>
+      <c r="D48" s="14" t="inlineStr"/>
+      <c r="E48" s="14" t="inlineStr"/>
+      <c r="F48" s="14" t="inlineStr"/>
+      <c r="G48" s="14" t="inlineStr"/>
+      <c r="H48" s="14" t="inlineStr"/>
+      <c r="I48" s="14" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
+      <c r="A49" s="10" t="inlineStr">
         <is>
           <t>Contacts in the model (n)</t>
         </is>
       </c>
-      <c r="B49" s="21">
+      <c r="B49" s="22">
         <f>COUNT($F$11:$F$34)</f>
         <v/>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>COUNT(y). Four predictors on 24 rows is already thin. The rule of thumb is ten to fifteen rows per predictor before the coefficients settle down.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+      <c r="A50" s="10" t="inlineStr">
         <is>
           <t>Predictors (k)</t>
         </is>
       </c>
-      <c r="B50" s="21">
+      <c r="B50" s="22">
         <f>4</f>
         <v/>
       </c>
-      <c r="C50" s="10" t="inlineStr">
+      <c r="C50" s="12" t="inlineStr">
         <is>
           <t>How many x columns the model is fitting. Every one you add uses up a degree of freedom and lifts R² whether or not it means anything.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>R²</t>
         </is>
       </c>
-      <c r="B51" s="23">
+      <c r="B51" s="24">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,1),"")</f>
         <v/>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>INDEX(LINEST(...), 3, 1). The share of the spread in handle time all four drivers explain together.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Adjusted R²</t>
         </is>
       </c>
-      <c r="B52" s="23">
+      <c r="B52" s="24">
         <f>IFERROR(1-(1-$B$51)*($B$49-1)/($B$49-$B$50-1),"")</f>
         <v/>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>R² with a penalty for each predictor: 1 − (1 − R²)(n − 1)/(n − k − 1). If this sits well below R², some of your columns are paying their way in arithmetic rather than in meaning.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Standard error of the estimate</t>
         </is>
       </c>
-      <c r="B53" s="22">
+      <c r="B53" s="23">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),3,2),"")</f>
         <v/>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>INDEX(LINEST(...), 3, 2). The typical miss, in seconds. Quote a prediction as fitted ± roughly two of these, or do not quote it.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B54" s="22">
+      <c r="B54" s="23">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,1),"")</f>
         <v/>
       </c>
-      <c r="C54" s="10" t="inlineStr">
+      <c r="C54" s="12" t="inlineStr">
         <is>
           <t>INDEX(LINEST(...), 4, 1). Tests the whole model at once: is this set of four better than no model at all?</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>Degrees of freedom (residual)</t>
         </is>
       </c>
-      <c r="B55" s="21">
+      <c r="B55" s="22">
         <f>IFERROR(INDEX(LINEST($F$11:$F$34,$B$11:$E$34,TRUE,TRUE),4,2),"")</f>
         <v/>
       </c>
-      <c r="C55" s="10" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>INDEX(LINEST(...), 4, 2). n − k − 1. Every per-coefficient p-value on the table above reads this cell.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>p-value for F</t>
         </is>
       </c>
-      <c r="B56" s="25">
+      <c r="B56" s="26">
         <f>IFERROR(FDIST($B$54,$B$50,$B$55),"")</f>
         <v/>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>FDIST(F, k, df). Small means the four together explain something. It does NOT mean each of them does — that is what the p-values above are for.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="A57" s="10" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B57" s="17">
+      <c r="B57" s="19">
         <f>IF($B$56="","",IF($B$56&gt;=0.05,"NO MODEL — these four together explain nothing",IF($B$52&lt;0.3,"USABLE BUT WEAK — read the effect sizes, not the R²","USABLE — now go and look at the residual chart")))</f>
         <v/>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>Read this with the residual chart beside it. A model can pass every number here and still be unusable if the residuals have a shape.</t>
         </is>
@@ -4815,43 +4842,43 @@
     </row>
     <row r="58"/>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>THE DECISION RULE — what this model does and does not license</t>
         </is>
       </c>
-      <c r="B59" s="7" t="n"/>
-      <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
-      <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="n"/>
-      <c r="G59" s="7" t="n"/>
-      <c r="H59" s="7" t="n"/>
-      <c r="I59" s="7" t="n"/>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n"/>
+      <c r="H59" s="9" t="n"/>
+      <c r="I59" s="9" t="n"/>
     </row>
     <row r="60" ht="75" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
+      <c r="A60" s="12" t="inlineStr">
         <is>
           <t>Read the residual chart before you read anything else. Residuals against fitted values should be a shapeless cloud of even width around zero. A funnel that widens to the right means the model is least reliable exactly where the numbers are biggest, and the usual fix is to model log(y) instead. A curve means you have fitted a straight line to something bent. Either way the coefficients above are not safe to quote, however small their p-values are.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="75" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="A61" s="12" t="inlineStr">
         <is>
           <t>Adjusted R² is the number you report, not R². R² can only go up when you add a column, so a model with enough junk in it will always look better than the honest one. For support data an adjusted R² of 0.3 to 0.6 on a duration is a genuinely useful model; anything above 0.85 usually means something on the right-hand side is a repackaging of the left — check you have not put a component of the outcome in as a predictor.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="60" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>A tiny p-value on a tiny coefficient is not a finding. The 'Act on it?' column deliberately refuses to say yes on significance alone: it multiplies each coefficient by the range that predictor actually covers in your data, and compares that with the smallest effect you said was worth acting on. That comparison, not the p-value, is the one to take to a steering group.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="75" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>None of this is causation, and a coefficient is not a lever. The model cannot tell whether transfers lengthen contacts or whether hard contacts get transferred. Before you spend money on a change, either watch the mechanism at the gemba or run a designed experiment (24-doe-design-matrix.xlsx) — a regression on observational data can rank your suspects and it cannot convict one.</t>
         </is>
@@ -4921,22 +4948,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Logistic regression — the scoring sheet for a model fitted elsewhere</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
+      <c r="B1" s="6" t="n"/>
+      <c r="C1" s="6" t="n"/>
+      <c r="D1" s="6" t="n"/>
+      <c r="E1" s="6" t="n"/>
+      <c r="F1" s="6" t="n"/>
+      <c r="G1" s="6" t="n"/>
+      <c r="H1" s="6" t="n"/>
+      <c r="I1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Reopened yes/no is the outcome that actually matters, and a straight line is the wrong tool for it. Fit the model in Minitab, Python or R; paste the coefficient table here and this tab turns it into odds ratios, probabilities and a classification table you can argue about.</t>
         </is>
@@ -4944,29 +4971,29 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>READ THIS FIRST — what this tab does, and what it deliberately does not</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="I4" s="7" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="n"/>
     </row>
     <row r="5" ht="75" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>This sheet does NOT fit the model. Fitting a logistic regression is maximum likelihood: an iterative search that has no closed form, and no honest way to write it as a spreadsheet formula. Anything that claims to do it in plain Excel is either running a macro or lying to you. So the split is explicit — the tool fits, this sheet interprets. Everything below is arithmetic on numbers you paste in, and every step of that arithmetic is a formula you can click on.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="75" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Where to get the numbers. Minitab: Stat → Regression → Binary Logistic Regression → Fit Binary Logistic Model, and tick odds ratios in the Results dialog. Python: m = smf.logit('reopened ~ after17 + over50 + tenure + transfers', data=df).fit(); m.summary(). R: glm(reopened ~ ., family = binomial, data = df). Copy the coefficient column, the standard error column and the p-value column into the yellow cells below, in the same order as your predictors.</t>
         </is>
@@ -4974,7 +5001,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="84" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>STEP 1 — paste the coefficient table your tool produced  ·  Key:
 • Coefficient = how far the outcome moves for a one-unit change in that driver, with the other drivers held still
@@ -4984,230 +5011,230 @@
 • CI = confidence interval, the range the true value plausibly sits in</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="9" t="n"/>
+      <c r="I8" s="9" t="n"/>
     </row>
     <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>Coefficient (log-odds)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>Std error</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>p-value</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Odds ratio</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>Odds ratio 95% CI low</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Odds ratio 95% CI high</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>What it means</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
+      <c r="A10" s="29" t="inlineStr">
         <is>
           <t>Intercept</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n">
+      <c r="B10" s="34" t="n">
         <v>-3.05</v>
       </c>
-      <c r="C10" s="33" t="n">
+      <c r="C10" s="34" t="n">
         <v>0.24</v>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="36">
         <f>IFERROR(EXP($B10),"")</f>
         <v/>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="36">
         <f>IFERROR(EXP($B10-1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="G10" s="35">
+      <c r="G10" s="36">
         <f>IFERROR(EXP($B10+1.96*$C10),"")</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>"Baseline odds of a reopen with every driver at zero: "&amp;TEXT($E10,"0.000")&amp;" to 1, which is "&amp;TEXT($E10/(1+$E10),"0.0%")&amp;" probability."</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="B11" s="33" t="n">
+      <c r="B11" s="34" t="n">
         <v>1.16</v>
       </c>
-      <c r="C11" s="33" t="n">
+      <c r="C11" s="34" t="n">
         <v>0.21</v>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="36">
         <f>IFERROR(EXP($B11),"")</f>
         <v/>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="36">
         <f>IFERROR(EXP($B11-1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="36">
         <f>IFERROR(EXP($B11+1.96*$C11),"")</f>
         <v/>
       </c>
-      <c r="H11" s="31">
+      <c r="H11" s="32">
         <f>"Raising the adjustment after 17:00 multiplies the odds of a reopen by "&amp;TEXT($E11,"0.00")&amp;". This is the posting-batch effect, and it is the largest single driver in the model."</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="72" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="B12" s="33" t="n">
+      <c r="B12" s="34" t="n">
         <v>0.83</v>
       </c>
-      <c r="C12" s="33" t="n">
+      <c r="C12" s="34" t="n">
         <v>0.22</v>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="35" t="inlineStr">
         <is>
           <t>0.0002</t>
         </is>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="36">
         <f>IFERROR(EXP($B12),"")</f>
         <v/>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="36">
         <f>IFERROR(EXP($B12-1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="G12" s="35">
+      <c r="G12" s="36">
         <f>IFERROR(EXP($B12+1.96*$C12),"")</f>
         <v/>
       </c>
-      <c r="H12" s="31">
+      <c r="H12" s="32">
         <f>"Clearing the $50 authority limit multiplies the odds of a reopen by "&amp;TEXT($E12,"0.00")&amp;", because the case waits in a queue for approval."</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="84" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="B13" s="33" t="n">
+      <c r="B13" s="34" t="n">
         <v>-0.038</v>
       </c>
-      <c r="C13" s="33" t="n">
+      <c r="C13" s="34" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="D13" s="34" t="inlineStr">
+      <c r="D13" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="36">
         <f>IFERROR(EXP($B13),"")</f>
         <v/>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="36">
         <f>IFERROR(EXP($B13-1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="36">
         <f>IFERROR(EXP($B13+1.96*$C13),"")</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="32">
         <f>"Each extra month of tenure multiplies the odds by "&amp;TEXT($E13,"0.000")&amp;" — so a 24-month agent runs at "&amp;TEXT($E13^24,"0.00")&amp;" times the odds of a first-week agent."</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="72" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="B14" s="33" t="n">
+      <c r="B14" s="34" t="n">
         <v>0.61</v>
       </c>
-      <c r="C14" s="33" t="n">
+      <c r="C14" s="34" t="n">
         <v>0.12</v>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D14" s="35" t="inlineStr">
         <is>
           <t>&lt;0.0001</t>
         </is>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="36">
         <f>IFERROR(EXP($B14),"")</f>
         <v/>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="36">
         <f>IFERROR(EXP($B14-1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="G14" s="35">
+      <c r="G14" s="36">
         <f>IFERROR(EXP($B14+1.96*$C14),"")</f>
         <v/>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="32">
         <f>"Each extra transfer multiplies the odds of a reopen by "&amp;TEXT($E14,"0.00")&amp;". Multiply by how common transfers are before you rank it against the others."</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="75" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>An odds ratio of 1.00 means the driver changes nothing; below 1 it protects. The confidence interval is the number to argue about, not the point estimate — if it straddles 1.00 the driver has not earned a place in your improvement plan, whatever the coefficient says. And a p-value printed as &lt;0.0001 by the tool is pasted here as text on purpose: it is not a number you should be doing arithmetic on.</t>
         </is>
@@ -5215,933 +5242,933 @@
     </row>
     <row r="16"/>
     <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>STEP 2 — the same 24 contacts, scored with those coefficients. Contact ref is the case number and the time of day it was raised, which is where the 17:00 column comes from. The last two columns are the model's working: the logit it computes, then the same thing as a probability  ·  Key:
 • Logit = the log-odds the model works in, before it is turned back into a probability
 • Predicted probability = the model's chance that this particular row ends in the outcome</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="n"/>
-      <c r="G17" s="7" t="n"/>
-      <c r="H17" s="7" t="n"/>
-      <c r="I17" s="7" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
     </row>
     <row r="18" ht="46" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Contact ref</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Raised after 17:00 (1 = yes)</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>Over the $50 authority limit (1 = yes)</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Agent tenure in months</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Transfers before resolution</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>Reopened within 7 days (1 = yes)</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>Logit</t>
         </is>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>Predicted probability</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Flagged at your threshold (1 = yes)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>BA-2201 · 17:05</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="15" t="n">
+      <c r="B19" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="E19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="24">
+      <c r="E19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="25">
         <f>IF($B19="","",$B$10+$B$11*$B19+$B$12*$C19+$B$13*$D19+$B$14*$E19)</f>
         <v/>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="24">
         <f>IFERROR(1/(1+EXP(-$G19)),"")</f>
         <v/>
       </c>
-      <c r="I19" s="21">
+      <c r="I19" s="22">
         <f>IF($H19="","",IF($H19&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>BA-2202 · 17:20</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15" t="n">
+      <c r="B20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="E20" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="24">
+      <c r="E20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="25">
         <f>IF($B20="","",$B$10+$B$11*$B20+$B$12*$C20+$B$13*$D20+$B$14*$E20)</f>
         <v/>
       </c>
-      <c r="H20" s="23">
+      <c r="H20" s="24">
         <f>IFERROR(1/(1+EXP(-$G20)),"")</f>
         <v/>
       </c>
-      <c r="I20" s="21">
+      <c r="I20" s="22">
         <f>IF($H20="","",IF($H20&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>BA-2203 · 08:15</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15" t="n">
+      <c r="B21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="E21" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="24">
+      <c r="E21" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="25">
         <f>IF($B21="","",$B$10+$B$11*$B21+$B$12*$C21+$B$13*$D21+$B$14*$E21)</f>
         <v/>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="24">
         <f>IFERROR(1/(1+EXP(-$G21)),"")</f>
         <v/>
       </c>
-      <c r="I21" s="21">
+      <c r="I21" s="22">
         <f>IF($H21="","",IF($H21&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>BA-2204 · 17:45</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15" t="n">
+      <c r="B22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="E22" s="14" t="n">
+      <c r="E22" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="24">
+      <c r="F22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="25">
         <f>IF($B22="","",$B$10+$B$11*$B22+$B$12*$C22+$B$13*$D22+$B$14*$E22)</f>
         <v/>
       </c>
-      <c r="H22" s="23">
+      <c r="H22" s="24">
         <f>IFERROR(1/(1+EXP(-$G22)),"")</f>
         <v/>
       </c>
-      <c r="I22" s="21">
+      <c r="I22" s="22">
         <f>IF($H22="","",IF($H22&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>BA-2205 · 18:10</t>
         </is>
       </c>
-      <c r="B23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15" t="n">
+      <c r="B23" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="17" t="n">
         <v>33</v>
       </c>
-      <c r="E23" s="14" t="n">
+      <c r="E23" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="24">
+      <c r="F23" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="25">
         <f>IF($B23="","",$B$10+$B$11*$B23+$B$12*$C23+$B$13*$D23+$B$14*$E23)</f>
         <v/>
       </c>
-      <c r="H23" s="23">
+      <c r="H23" s="24">
         <f>IFERROR(1/(1+EXP(-$G23)),"")</f>
         <v/>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="22">
         <f>IF($H23="","",IF($H23&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>BA-2206 · 09:05</t>
         </is>
       </c>
-      <c r="B24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="15" t="n">
+      <c r="B24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E24" s="14" t="n">
+      <c r="E24" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="24">
+      <c r="F24" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="25">
         <f>IF($B24="","",$B$10+$B$11*$B24+$B$12*$C24+$B$13*$D24+$B$14*$E24)</f>
         <v/>
       </c>
-      <c r="H24" s="23">
+      <c r="H24" s="24">
         <f>IFERROR(1/(1+EXP(-$G24)),"")</f>
         <v/>
       </c>
-      <c r="I24" s="21">
+      <c r="I24" s="22">
         <f>IF($H24="","",IF($H24&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>BA-2207 · 09:40</t>
         </is>
       </c>
-      <c r="B25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="15" t="n">
+      <c r="B25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="17" t="n">
         <v>46</v>
       </c>
-      <c r="E25" s="14" t="n">
+      <c r="E25" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="24">
+      <c r="F25" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="25">
         <f>IF($B25="","",$B$10+$B$11*$B25+$B$12*$C25+$B$13*$D25+$B$14*$E25)</f>
         <v/>
       </c>
-      <c r="H25" s="23">
+      <c r="H25" s="24">
         <f>IFERROR(1/(1+EXP(-$G25)),"")</f>
         <v/>
       </c>
-      <c r="I25" s="21">
+      <c r="I25" s="22">
         <f>IF($H25="","",IF($H25&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>BA-2208 · 18:35</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="15" t="n">
+      <c r="B26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="24">
+      <c r="E26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="25">
         <f>IF($B26="","",$B$10+$B$11*$B26+$B$12*$C26+$B$13*$D26+$B$14*$E26)</f>
         <v/>
       </c>
-      <c r="H26" s="23">
+      <c r="H26" s="24">
         <f>IFERROR(1/(1+EXP(-$G26)),"")</f>
         <v/>
       </c>
-      <c r="I26" s="21">
+      <c r="I26" s="22">
         <f>IF($H26="","",IF($H26&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>BA-2209 · 10:20</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="15" t="n">
+      <c r="B27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="24">
+      <c r="E27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="25">
         <f>IF($B27="","",$B$10+$B$11*$B27+$B$12*$C27+$B$13*$D27+$B$14*$E27)</f>
         <v/>
       </c>
-      <c r="H27" s="23">
+      <c r="H27" s="24">
         <f>IFERROR(1/(1+EXP(-$G27)),"")</f>
         <v/>
       </c>
-      <c r="I27" s="21">
+      <c r="I27" s="22">
         <f>IF($H27="","",IF($H27&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>BA-2210 · 11:05</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="15" t="n">
+      <c r="B28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="E28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="24">
+      <c r="E28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="25">
         <f>IF($B28="","",$B$10+$B$11*$B28+$B$12*$C28+$B$13*$D28+$B$14*$E28)</f>
         <v/>
       </c>
-      <c r="H28" s="23">
+      <c r="H28" s="24">
         <f>IFERROR(1/(1+EXP(-$G28)),"")</f>
         <v/>
       </c>
-      <c r="I28" s="21">
+      <c r="I28" s="22">
         <f>IF($H28="","",IF($H28&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>BA-2211 · 11:35</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="15" t="n">
+      <c r="B29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="17" t="n">
         <v>28</v>
       </c>
-      <c r="E29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="24">
+      <c r="E29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="25">
         <f>IF($B29="","",$B$10+$B$11*$B29+$B$12*$C29+$B$13*$D29+$B$14*$E29)</f>
         <v/>
       </c>
-      <c r="H29" s="23">
+      <c r="H29" s="24">
         <f>IFERROR(1/(1+EXP(-$G29)),"")</f>
         <v/>
       </c>
-      <c r="I29" s="21">
+      <c r="I29" s="22">
         <f>IF($H29="","",IF($H29&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>BA-2212 · 19:00</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" s="15" t="n">
+      <c r="B30" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="24">
+      <c r="F30" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="25">
         <f>IF($B30="","",$B$10+$B$11*$B30+$B$12*$C30+$B$13*$D30+$B$14*$E30)</f>
         <v/>
       </c>
-      <c r="H30" s="23">
+      <c r="H30" s="24">
         <f>IFERROR(1/(1+EXP(-$G30)),"")</f>
         <v/>
       </c>
-      <c r="I30" s="21">
+      <c r="I30" s="22">
         <f>IF($H30="","",IF($H30&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>BA-2213 · 12:10</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="15" t="n">
+      <c r="B31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="24">
+      <c r="E31" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="25">
         <f>IF($B31="","",$B$10+$B$11*$B31+$B$12*$C31+$B$13*$D31+$B$14*$E31)</f>
         <v/>
       </c>
-      <c r="H31" s="23">
+      <c r="H31" s="24">
         <f>IFERROR(1/(1+EXP(-$G31)),"")</f>
         <v/>
       </c>
-      <c r="I31" s="21">
+      <c r="I31" s="22">
         <f>IF($H31="","",IF($H31&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>BA-2214 · 19:25</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="15" t="n">
+      <c r="B32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="17" t="n">
         <v>39</v>
       </c>
-      <c r="E32" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="24">
+      <c r="E32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="25">
         <f>IF($B32="","",$B$10+$B$11*$B32+$B$12*$C32+$B$13*$D32+$B$14*$E32)</f>
         <v/>
       </c>
-      <c r="H32" s="23">
+      <c r="H32" s="24">
         <f>IFERROR(1/(1+EXP(-$G32)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="21">
+      <c r="I32" s="22">
         <f>IF($H32="","",IF($H32&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>BA-2215 · 13:25</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="15" t="n">
+      <c r="B33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="E33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="24">
+      <c r="E33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="25">
         <f>IF($B33="","",$B$10+$B$11*$B33+$B$12*$C33+$B$13*$D33+$B$14*$E33)</f>
         <v/>
       </c>
-      <c r="H33" s="23">
+      <c r="H33" s="24">
         <f>IFERROR(1/(1+EXP(-$G33)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="22">
         <f>IF($H33="","",IF($H33&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>BA-2216 · 19:50</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="15" t="n">
+      <c r="B34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="E34" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="24">
+      <c r="E34" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="25">
         <f>IF($B34="","",$B$10+$B$11*$B34+$B$12*$C34+$B$13*$D34+$B$14*$E34)</f>
         <v/>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="24">
         <f>IFERROR(1/(1+EXP(-$G34)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="22">
         <f>IF($H34="","",IF($H34&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>BA-2217 · 20:15</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="15" t="n">
+      <c r="B35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E35" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="24">
+      <c r="E35" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="25">
         <f>IF($B35="","",$B$10+$B$11*$B35+$B$12*$C35+$B$13*$D35+$B$14*$E35)</f>
         <v/>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="24">
         <f>IFERROR(1/(1+EXP(-$G35)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="21">
+      <c r="I35" s="22">
         <f>IF($H35="","",IF($H35&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="13" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>BA-2218 · 14:00</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="15" t="n">
+      <c r="B36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="24">
+      <c r="E36" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="25">
         <f>IF($B36="","",$B$10+$B$11*$B36+$B$12*$C36+$B$13*$D36+$B$14*$E36)</f>
         <v/>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="24">
         <f>IFERROR(1/(1+EXP(-$G36)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="22">
         <f>IF($H36="","",IF($H36&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>BA-2219 · 20:40</t>
         </is>
       </c>
-      <c r="B37" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="15" t="n">
+      <c r="B37" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="14" t="n">
+      <c r="E37" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="24">
+      <c r="F37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="25">
         <f>IF($B37="","",$B$10+$B$11*$B37+$B$12*$C37+$B$13*$D37+$B$14*$E37)</f>
         <v/>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="24">
         <f>IFERROR(1/(1+EXP(-$G37)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="22">
         <f>IF($H37="","",IF($H37&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>BA-2220 · 14:35</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="15" t="n">
+      <c r="B38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="E38" s="14" t="n">
+      <c r="E38" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="24">
+      <c r="F38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="25">
         <f>IF($B38="","",$B$10+$B$11*$B38+$B$12*$C38+$B$13*$D38+$B$14*$E38)</f>
         <v/>
       </c>
-      <c r="H38" s="23">
+      <c r="H38" s="24">
         <f>IFERROR(1/(1+EXP(-$G38)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="21">
+      <c r="I38" s="22">
         <f>IF($H38="","",IF($H38&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>BA-2221 · 15:10</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="15" t="n">
+      <c r="B39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="E39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="24">
+      <c r="E39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="25">
         <f>IF($B39="","",$B$10+$B$11*$B39+$B$12*$C39+$B$13*$D39+$B$14*$E39)</f>
         <v/>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="24">
         <f>IFERROR(1/(1+EXP(-$G39)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="21">
+      <c r="I39" s="22">
         <f>IF($H39="","",IF($H39&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>BA-2222 · 15:50</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="15" t="n">
+      <c r="B40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="17" t="n">
         <v>53</v>
       </c>
-      <c r="E40" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="24">
+      <c r="E40" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="25">
         <f>IF($B40="","",$B$10+$B$11*$B40+$B$12*$C40+$B$13*$D40+$B$14*$E40)</f>
         <v/>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="24">
         <f>IFERROR(1/(1+EXP(-$G40)),"")</f>
         <v/>
       </c>
-      <c r="I40" s="21">
+      <c r="I40" s="22">
         <f>IF($H40="","",IF($H40&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>BA-2223 · 16:20</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="15" t="n">
+      <c r="B41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="E41" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="24">
+      <c r="E41" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="25">
         <f>IF($B41="","",$B$10+$B$11*$B41+$B$12*$C41+$B$13*$D41+$B$14*$E41)</f>
         <v/>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="24">
         <f>IFERROR(1/(1+EXP(-$G41)),"")</f>
         <v/>
       </c>
-      <c r="I41" s="21">
+      <c r="I41" s="22">
         <f>IF($H41="","",IF($H41&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>BA-2224 · 21:10</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="15" t="n">
+      <c r="B42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E42" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="24">
+      <c r="E42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="25">
         <f>IF($B42="","",$B$10+$B$11*$B42+$B$12*$C42+$B$13*$D42+$B$14*$E42)</f>
         <v/>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="24">
         <f>IFERROR(1/(1+EXP(-$G42)),"")</f>
         <v/>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="22">
         <f>IF($H42="","",IF($H42&gt;=$B$46,1,0))</f>
         <v/>
       </c>
     </row>
     <row r="43"/>
     <row r="44" ht="45" customHeight="1">
-      <c r="A44" s="10" t="inlineStr">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>The logit is the straight-line part — intercept plus each coefficient times its column. The probability is that logit squashed into 0-1 by 1/(1+EXP(−logit)), which is the whole reason this is not a linear regression: a line would happily predict a 130% chance of reopening.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>STEP 3 — the threshold you choose, and what it costs you</t>
         </is>
       </c>
-      <c r="B45" s="7" t="n"/>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="n"/>
-      <c r="G45" s="7" t="n"/>
-      <c r="H45" s="7" t="n"/>
-      <c r="I45" s="7" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
     </row>
     <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>Flag a contact at this probability or above</t>
         </is>
       </c>
-      <c r="B46" s="36" t="n">
+      <c r="B46" s="37" t="n">
         <v>0.2</v>
       </c>
-      <c r="C46" s="10" t="inlineStr">
+      <c r="C46" s="12" t="inlineStr">
         <is>
           <t>Not 0.5. Roughly one billing adjustment in seven reopens, so at 0.5 the model flags nobody and still beats the base rate by predicting 'no' every time. Set the threshold from what a flag COSTS you: a quality check on a flagged contact takes about four minutes, so you can afford to be wrong often.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="45" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>AUC the tool reported</t>
         </is>
       </c>
-      <c r="B47" s="37" t="n">
+      <c r="B47" s="38" t="n">
         <v>0.74</v>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>Straight off the tool's output — Minitab calls it the concordance or the area under the ROC curve. It is threshold-free: 0.5 is a coin toss, 0.7 is useful for targeting, 0.8 is strong for support data. It says nothing about whether the probabilities themselves are calibrated.</t>
         </is>
@@ -6149,106 +6176,106 @@
     </row>
     <row r="48"/>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>STEP 4 — the classification table at that threshold</t>
         </is>
       </c>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="n"/>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="7" t="n"/>
-      <c r="I49" s="7" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="9" t="n"/>
+      <c r="I49" s="9" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>What the model said</t>
         </is>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>Actually reopened</t>
         </is>
       </c>
-      <c r="C50" s="12" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>Did not reopen</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr"/>
-      <c r="F50" s="12" t="inlineStr"/>
-      <c r="G50" s="12" t="inlineStr"/>
-      <c r="H50" s="12" t="inlineStr"/>
-      <c r="I50" s="12" t="inlineStr"/>
+      <c r="E50" s="14" t="inlineStr"/>
+      <c r="F50" s="14" t="inlineStr"/>
+      <c r="G50" s="14" t="inlineStr"/>
+      <c r="H50" s="14" t="inlineStr"/>
+      <c r="I50" s="14" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>Flagged — predicted reopen</t>
         </is>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="18">
         <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=1))</f>
         <v/>
       </c>
-      <c r="C51" s="16">
+      <c r="C51" s="18">
         <f>SUMPRODUCT(($I$19:$I$42=1)*($F$19:$F$42=0))</f>
         <v/>
       </c>
-      <c r="D51" s="16">
+      <c r="D51" s="18">
         <f>SUM($B51:$C51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="8" t="inlineStr">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Not flagged</t>
         </is>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="18">
         <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=1))</f>
         <v/>
       </c>
-      <c r="C52" s="16">
+      <c r="C52" s="18">
         <f>SUMPRODUCT(($I$19:$I$42=0)*($F$19:$F$42=0))</f>
         <v/>
       </c>
-      <c r="D52" s="16">
+      <c r="D52" s="18">
         <f>SUM($B52:$C52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="18">
         <f>SUM($B$51:$B$52)</f>
         <v/>
       </c>
-      <c r="C53" s="16">
+      <c r="C53" s="18">
         <f>SUM($C$51:$C$52)</f>
         <v/>
       </c>
-      <c r="D53" s="16">
+      <c r="D53" s="18">
         <f>SUM($D$51:$D$52)</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="10" t="inlineStr">
+      <c r="A54" s="12" t="inlineStr">
         <is>
           <t>Top left is a contact you flagged that did reopen; top right is a false alarm; bottom left is the one you missed. There is no threshold that empties both off-diagonal cells, and choosing which of them to fill is a business decision, not a statistical one.</t>
         </is>
@@ -6256,134 +6283,134 @@
     </row>
     <row r="55"/>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>STEP 5 — what that table says about the model</t>
         </is>
       </c>
-      <c r="B56" s="7" t="n"/>
-      <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
-      <c r="E56" s="7" t="n"/>
-      <c r="F56" s="7" t="n"/>
-      <c r="G56" s="7" t="n"/>
-      <c r="H56" s="7" t="n"/>
-      <c r="I56" s="7" t="n"/>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="9" t="n"/>
+      <c r="D56" s="9" t="n"/>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="9" t="n"/>
+      <c r="G56" s="9" t="n"/>
+      <c r="H56" s="9" t="n"/>
+      <c r="I56" s="9" t="n"/>
     </row>
     <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="12" t="inlineStr">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B57" s="12" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>What it tells you</t>
         </is>
       </c>
-      <c r="D57" s="12" t="inlineStr"/>
-      <c r="E57" s="12" t="inlineStr"/>
-      <c r="F57" s="12" t="inlineStr"/>
-      <c r="G57" s="12" t="inlineStr"/>
-      <c r="H57" s="12" t="inlineStr"/>
-      <c r="I57" s="12" t="inlineStr"/>
+      <c r="D57" s="14" t="inlineStr"/>
+      <c r="E57" s="14" t="inlineStr"/>
+      <c r="F57" s="14" t="inlineStr"/>
+      <c r="G57" s="14" t="inlineStr"/>
+      <c r="H57" s="14" t="inlineStr"/>
+      <c r="I57" s="14" t="inlineStr"/>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="8" t="inlineStr">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>Sensitivity — reopens you caught</t>
         </is>
       </c>
-      <c r="B58" s="23">
+      <c r="B58" s="24">
         <f>IFERROR($B$51/($B$51+$B$52),"")</f>
         <v/>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C58" s="12" t="inlineStr">
         <is>
           <t>Of the contacts that did reopen, the share the model flagged. This is the number the improvement is actually paid on: a reopen you never flagged is a reopen you never prevented.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>Specificity — quiet contacts left alone</t>
         </is>
       </c>
-      <c r="B59" s="23">
+      <c r="B59" s="24">
         <f>IFERROR($C$52/($C$52+$C$51),"")</f>
         <v/>
       </c>
-      <c r="C59" s="10" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>Of the contacts that did not reopen, the share the model correctly left alone. Falls as you lower the threshold; that is the trade.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>Precision — flags that were right</t>
         </is>
       </c>
-      <c r="B60" s="23">
+      <c r="B60" s="24">
         <f>IFERROR($B$51/($B$51+$C$51),"")</f>
         <v/>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C60" s="12" t="inlineStr">
         <is>
           <t>Of the contacts you flagged, the share that really reopened. At a 14% base rate this is always the ugly number, and it is the one that decides whether the team trusts the flag.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>Accuracy — rows called correctly</t>
         </is>
       </c>
-      <c r="B61" s="23">
+      <c r="B61" s="24">
         <f>IFERROR(($B$51+$C$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
         <v/>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr">
         <is>
           <t>The share of all rows called right. Almost useless on its own: predicting 'never reopens' for every row scores whatever the base rate below leaves it, and prevents nothing. Quote it only beside that base rate.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>Base rate — share that actually reopened</t>
         </is>
       </c>
-      <c r="B62" s="23">
+      <c r="B62" s="24">
         <f>IFERROR(($B$51+$B$52)/($B$51+$C$51+$B$52+$C$52),"")</f>
         <v/>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C62" s="12" t="inlineStr">
         <is>
           <t>What you would score by always guessing 'no'. Accuracy has to beat this by a wide margin before it means anything at all.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>Verdict at this threshold</t>
         </is>
       </c>
-      <c r="B63" s="17">
+      <c r="B63" s="19">
         <f>IF($B$51+$B$52=0,"NO REOPENS IN THE SAMPLE",IF($B$51/($B$51+$B$52)&lt;0.5,"MISSES MORE THAN HALF — lower the threshold",IF($B$51/($B$51+$C$51)&lt;0.2,"TOO MANY FALSE ALARMS — raise the threshold","USABLE FOR TARGETING — check it against the cost of a flag")))</f>
         <v/>
       </c>
-      <c r="C63" s="10" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr">
         <is>
           <t>Sensitivity is what the model buys you; precision is what it costs the team. Move the threshold in step 3 and watch both move.</t>
         </is>
@@ -6391,43 +6418,43 @@
     </row>
     <row r="64"/>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
         <is>
           <t>THE DECISION RULE — before this leaves the room</t>
         </is>
       </c>
-      <c r="B65" s="7" t="n"/>
-      <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
-      <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="n"/>
-      <c r="G65" s="7" t="n"/>
-      <c r="H65" s="7" t="n"/>
-      <c r="I65" s="7" t="n"/>
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="9" t="n"/>
+      <c r="H65" s="9" t="n"/>
+      <c r="I65" s="9" t="n"/>
     </row>
     <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="10" t="inlineStr">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>Never fit a straight line to a yes/no outcome. Linear regression on a 0/1 column predicts probabilities above 1 and below 0, and gets the error structure wrong on top of it. If your outcome is reopened, escalated, breached or churned, it is this tab or nothing.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="10" t="inlineStr">
+      <c r="A67" s="12" t="inlineStr">
         <is>
           <t>Report odds ratios with their confidence intervals, never raw log-odds. 'Each transfer multiplies the odds of a reopen by 1.84 (95% CI 1.46 to 2.33)' is a sentence the Improve phase can act on. '0.61' is not. And an interval that includes 1.00 means you have not shown anything, however confident the point estimate looks.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="10" t="inlineStr">
+      <c r="A68" s="12" t="inlineStr">
         <is>
           <t>The biggest odds ratio is not the biggest opportunity. Multiply each odds ratio by how COMMON that driver is. After-17:00 has the largest ratio here and applies to 46% of contacts; a rare driver with an odds ratio of 5 that touches 2% of volume moves almost nothing. Rank by ratio times prevalence and you will usually reorder the list.</t>
         </is>
       </c>
     </row>
     <row r="69" ht="75" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="A69" s="12" t="inlineStr">
         <is>
           <t>AUC and accuracy are not the same question, and neither is causation. AUC asks whether the model RANKS reopens above non-reopens; accuracy asks how many rows it called right at one threshold; and neither says the drivers cause the reopens. Before you change the 17:00 cut-off, confirm the posting-batch mechanism at the gemba or pilot the change against a control group (16-pilot-protocol.md) — the model chose your suspect, the pilot convicts it.</t>
         </is>
